--- a/Översikt MARK.xlsx
+++ b/Översikt MARK.xlsx
@@ -601,7 +601,7 @@
         <v>45497</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45617</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45222</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>45137</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>45348</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>45285</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>44482</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>45001</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>45638</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>45342</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>45154</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>45973</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>46001</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>46006</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>45137</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>45618</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>44950</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>46273</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>45673</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>46266</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>44792</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>44846</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>45091</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>45412</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>45191</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>45169</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>45810</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45896</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>45905</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>45271</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>46027</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>45134</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>45324</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>45936</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>45288</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>45306</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>45841</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>45596</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>46203</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>45751</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>44908</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>45849</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>46233</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
         <v>46268</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>45792</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>45786</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>46048</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>46107</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         <v>44881</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>44469</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>44474</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         <v>44843</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>44462</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>44531</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>44518</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         <v>44750</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>44764</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>44523</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>44720</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>44696</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>44869</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>44764</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         <v>44607</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         <v>44811</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>44714</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>44722</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>44510</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>44816</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         <v>44474</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         <v>44684</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>44725</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         <v>44874</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>44564</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         <v>44467</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>44564</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>44696</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>44615</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         <v>44725</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>44609</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>44609</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         <v>44733</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>44580</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         <v>44840</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>44497</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>44533</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>44680</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>44784</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>44699</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>44473</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>44491</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>44652</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>44781</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>44469</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>44571</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44473</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>44473</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>44539</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>44622</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>44725</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         <v>44470</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>44462</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         <v>44692</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>44462</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>44982</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
         <v>45342</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
         <v>45359</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>45475</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>45030</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>45568</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>45093</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10286,7 +10286,7 @@
         <v>44902</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>44631</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>44585</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>45093</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10583,7 +10583,7 @@
         <v>45106</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>44630</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>45681</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>44937</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>44632</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>45684</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>45183</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         <v>45745</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>45428</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
         <v>44715</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>44599</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>45294</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>44473</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>45376</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>44460</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>44607</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>45631</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11834,7 +11834,7 @@
         <v>44810</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>45137</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11980,7 +11980,7 @@
         <v>45611</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>45022</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>45406</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
         <v>45189</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>44935</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12345,7 +12345,7 @@
         <v>45358</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
         <v>44987</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>45604</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12564,7 +12564,7 @@
         <v>45332</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
         <v>45332</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>45135</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12783,7 +12783,7 @@
         <v>45231</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12856,7 +12856,7 @@
         <v>44474</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>44950</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>45016</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>45422</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
         <v>44734</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13221,7 +13221,7 @@
         <v>44610</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13294,7 +13294,7 @@
         <v>45624</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13367,7 +13367,7 @@
         <v>45587</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         <v>45624</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>44982</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>45244</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>44762</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>44760</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>45751</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>44973</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>45244</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>44574</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>45030</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>44588</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14248,7 +14248,7 @@
         <v>44588</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>45343</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         <v>45261</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>45355</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>44896</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>45397</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>44580</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>45471</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>45750</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14905,7 +14905,7 @@
         <v>45183</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>45098</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         <v>45098</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>45631</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>45212</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
         <v>44882</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>45629</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>45104</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>45281</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15562,7 +15562,7 @@
         <v>45637</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>45021</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>44615</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>45202</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>44467</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>44982</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16000,7 +16000,7 @@
         <v>45719</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>45397</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>45373</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>45059</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>45160</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>45490</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16443,7 +16443,7 @@
         <v>45490</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>45490</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>45855</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>45063</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>45884</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16808,7 +16808,7 @@
         <v>45817</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>45121</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16954,7 +16954,7 @@
         <v>45091</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17027,7 +17027,7 @@
         <v>44798</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>45888</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>44994</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>45888</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>45889</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>44715</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>45884</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>45343</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>45891</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17689,7 +17689,7 @@
         <v>45356</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>45356</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>45134</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>45895</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>45811</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>45896</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>45798</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         <v>45896</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>45896</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>45898</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>45898</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18492,7 +18492,7 @@
         <v>45855</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>45855</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>45322</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>45755</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>45897</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18857,7 +18857,7 @@
         <v>45450</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>45370</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>45901</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>44624</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>45540</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>45868</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>45477</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19368,7 +19368,7 @@
         <v>45905</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>45909</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>45595</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19587,7 +19587,7 @@
         <v>45684</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>45918</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19733,7 +19733,7 @@
         <v>44978</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19806,7 +19806,7 @@
         <v>45335</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19879,7 +19879,7 @@
         <v>44971</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19952,7 +19952,7 @@
         <v>44694</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20025,7 +20025,7 @@
         <v>45916</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20098,7 +20098,7 @@
         <v>45137</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>45075</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20244,7 +20244,7 @@
         <v>45629</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>44648</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>45923</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>45923</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20536,7 +20536,7 @@
         <v>45925</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>44834</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>45925</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20755,7 +20755,7 @@
         <v>45925</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20828,7 +20828,7 @@
         <v>45925</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>45925</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>45925</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>45924</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>44928</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21193,7 +21193,7 @@
         <v>44838</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
         <v>45931</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21339,7 +21339,7 @@
         <v>45106</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>45106</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21495,7 +21495,7 @@
         <v>44713</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>45680</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21641,7 +21641,7 @@
         <v>46146</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21714,7 +21714,7 @@
         <v>45755</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21787,7 +21787,7 @@
         <v>45755</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>45755</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21933,7 +21933,7 @@
         <v>46147</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>45349</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>45937</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>45937</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22225,7 +22225,7 @@
         <v>44935</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22298,7 +22298,7 @@
         <v>45484</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22371,7 +22371,7 @@
         <v>45937</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>45224</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>45922</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>45922</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>45943</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>45194</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>45943</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>45264</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>45264</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>44714</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>46153</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>44950</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>45953</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23325,7 +23325,7 @@
         <v>45953</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>45555</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>45419</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>45137</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>45959</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23690,7 +23690,7 @@
         <v>45959</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>45442</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>44712</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>45268</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>45414</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>45965</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24133,7 +24133,7 @@
         <v>45964</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>45288</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24279,7 +24279,7 @@
         <v>45392</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24352,7 +24352,7 @@
         <v>45490</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24425,7 +24425,7 @@
         <v>45750</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24498,7 +24498,7 @@
         <v>45342</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24571,7 +24571,7 @@
         <v>45629</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24644,7 +24644,7 @@
         <v>45432</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>45419</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>45978</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>45978</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>44768</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>45342</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>45533</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>45980</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>45140</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>45667</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25379,7 +25379,7 @@
         <v>45982</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>45356</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>45986</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>46120</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>45776</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         <v>44803</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>46162</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>45755</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>44489</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>44971</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>45260</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26182,7 +26182,7 @@
         <v>45999</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>45996</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>46165</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>46000</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>46001</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26552,7 +26552,7 @@
         <v>46001</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26625,7 +26625,7 @@
         <v>44834</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>46000</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26771,7 +26771,7 @@
         <v>44806</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26844,7 +26844,7 @@
         <v>45154</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26917,7 +26917,7 @@
         <v>46000</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>46000</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>44896</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>46007</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>46006</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27282,7 +27282,7 @@
         <v>45552</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27355,7 +27355,7 @@
         <v>46006</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27428,7 +27428,7 @@
         <v>46008</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>46009</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27574,7 +27574,7 @@
         <v>45076</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27647,7 +27647,7 @@
         <v>45137</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>46013</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27793,7 +27793,7 @@
         <v>45264</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27866,7 +27866,7 @@
         <v>46013</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27939,7 +27939,7 @@
         <v>44952</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         <v>45724</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>45443</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28158,7 +28158,7 @@
         <v>45707</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28231,7 +28231,7 @@
         <v>45714</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28304,7 +28304,7 @@
         <v>45714</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>45713</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28450,7 +28450,7 @@
         <v>45839</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28528,7 +28528,7 @@
         <v>45238</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28601,7 +28601,7 @@
         <v>45693</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>45710</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28747,7 +28747,7 @@
         <v>45709</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>45691</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>45526</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28966,7 +28966,7 @@
         <v>45776</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29039,7 +29039,7 @@
         <v>46169</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29112,7 +29112,7 @@
         <v>45236</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29185,7 +29185,7 @@
         <v>45154</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>44660</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29331,7 +29331,7 @@
         <v>45301</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29404,7 +29404,7 @@
         <v>44588</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29477,7 +29477,7 @@
         <v>44732</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29550,7 +29550,7 @@
         <v>46030</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>45021</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>46030</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29769,7 +29769,7 @@
         <v>45275</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>45275</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>46034</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>45604</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>46034</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>46034</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30207,7 +30207,7 @@
         <v>44978</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>46037</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>46037</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>46037</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>46037</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>46038</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>46038</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30723,7 +30723,7 @@
         <v>45386</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30796,7 +30796,7 @@
         <v>44963</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30869,7 +30869,7 @@
         <v>46048</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>46048</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31015,7 +31015,7 @@
         <v>46048</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31088,7 +31088,7 @@
         <v>46046</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>46048</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>46177</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31312,7 +31312,7 @@
         <v>44902</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31385,7 +31385,7 @@
         <v>45379</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>46055</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31531,7 +31531,7 @@
         <v>46052</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31609,7 +31609,7 @@
         <v>46055</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31682,7 +31682,7 @@
         <v>46056</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31760,7 +31760,7 @@
         <v>45251</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>45251</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31906,7 +31906,7 @@
         <v>46057</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>46056</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32052,7 +32052,7 @@
         <v>45135</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32125,7 +32125,7 @@
         <v>46058</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
         <v>46062</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32276,7 +32276,7 @@
         <v>46064</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32349,7 +32349,7 @@
         <v>45251</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32422,7 +32422,7 @@
         <v>45686</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32495,7 +32495,7 @@
         <v>45119</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32568,7 +32568,7 @@
         <v>44813</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32641,7 +32641,7 @@
         <v>45518</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32719,7 +32719,7 @@
         <v>46182</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32792,7 +32792,7 @@
         <v>44909</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32865,7 +32865,7 @@
         <v>46181</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32938,7 +32938,7 @@
         <v>45672</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33011,7 +33011,7 @@
         <v>45672</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>44637</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>45230</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33230,7 +33230,7 @@
         <v>45699</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>46084</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33376,7 +33376,7 @@
         <v>46084</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33449,7 +33449,7 @@
         <v>46084</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>46045</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33595,7 +33595,7 @@
         <v>45210</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33668,7 +33668,7 @@
         <v>45218</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>45204</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>46084</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33887,7 +33887,7 @@
         <v>45233</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33965,7 +33965,7 @@
         <v>46085</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>45233</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34116,7 +34116,7 @@
         <v>45107</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34189,7 +34189,7 @@
         <v>45225</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34262,7 +34262,7 @@
         <v>45378</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34335,7 +34335,7 @@
         <v>45523</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34408,7 +34408,7 @@
         <v>46191</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34481,7 +34481,7 @@
         <v>45686</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>46190</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34627,7 +34627,7 @@
         <v>46092</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34700,7 +34700,7 @@
         <v>46189</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>44813</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>46190</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>46097</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>46096</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35065,7 +35065,7 @@
         <v>46191</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35138,7 +35138,7 @@
         <v>46195</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35211,7 +35211,7 @@
         <v>46195</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>46195</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35357,7 +35357,7 @@
         <v>46195</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35430,7 +35430,7 @@
         <v>46100</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35503,7 +35503,7 @@
         <v>46195</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35576,7 +35576,7 @@
         <v>46195</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35649,7 +35649,7 @@
         <v>46198</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35722,7 +35722,7 @@
         <v>44531</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35795,7 +35795,7 @@
         <v>46199</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35873,7 +35873,7 @@
         <v>45254</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35946,7 +35946,7 @@
         <v>44994</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36019,7 +36019,7 @@
         <v>45373</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36092,7 +36092,7 @@
         <v>46114</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36165,7 +36165,7 @@
         <v>45070</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36238,7 +36238,7 @@
         <v>45264</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36311,7 +36311,7 @@
         <v>44764</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36384,7 +36384,7 @@
         <v>45911</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36457,7 +36457,7 @@
         <v>44588</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>45370</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36603,7 +36603,7 @@
         <v>45352</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36676,7 +36676,7 @@
         <v>44897</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>46127</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36822,7 +36822,7 @@
         <v>45202</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36895,7 +36895,7 @@
         <v>44881</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36968,7 +36968,7 @@
         <v>45156</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37041,7 +37041,7 @@
         <v>45369</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37114,7 +37114,7 @@
         <v>44673</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>45455</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37260,7 +37260,7 @@
         <v>46203</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37333,7 +37333,7 @@
         <v>45629</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37406,7 +37406,7 @@
         <v>45281</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37479,7 +37479,7 @@
         <v>45358</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37552,7 +37552,7 @@
         <v>45134</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37625,7 +37625,7 @@
         <v>46134</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>45099</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37771,7 +37771,7 @@
         <v>45474</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37849,7 +37849,7 @@
         <v>45569</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37922,7 +37922,7 @@
         <v>45197</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>45825</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38068,7 +38068,7 @@
         <v>44469</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38141,7 +38141,7 @@
         <v>45415</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38214,7 +38214,7 @@
         <v>45637</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38287,7 +38287,7 @@
         <v>44501</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38360,7 +38360,7 @@
         <v>45819</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38433,7 +38433,7 @@
         <v>45791</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38506,7 +38506,7 @@
         <v>45264</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>45188</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38652,7 +38652,7 @@
         <v>45093</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38725,7 +38725,7 @@
         <v>46204</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38798,7 +38798,7 @@
         <v>44589</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38871,7 +38871,7 @@
         <v>45030</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38944,7 +38944,7 @@
         <v>45379</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39017,7 +39017,7 @@
         <v>45475</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39090,7 +39090,7 @@
         <v>44652</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39163,7 +39163,7 @@
         <v>45274</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39236,7 +39236,7 @@
         <v>45370</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39309,7 +39309,7 @@
         <v>44888</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39382,7 +39382,7 @@
         <v>45092</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39455,7 +39455,7 @@
         <v>45359</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39528,7 +39528,7 @@
         <v>45359</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39601,7 +39601,7 @@
         <v>45763</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39674,7 +39674,7 @@
         <v>45763</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39747,7 +39747,7 @@
         <v>45763</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39820,7 +39820,7 @@
         <v>45490</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39893,7 +39893,7 @@
         <v>45077</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39966,7 +39966,7 @@
         <v>45534</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40039,7 +40039,7 @@
         <v>44924</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40112,7 +40112,7 @@
         <v>45631</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40185,7 +40185,7 @@
         <v>45251</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40258,7 +40258,7 @@
         <v>45119</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40331,7 +40331,7 @@
         <v>45565</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40404,7 +40404,7 @@
         <v>45332</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40477,7 +40477,7 @@
         <v>45210</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40550,7 +40550,7 @@
         <v>44897</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40623,7 +40623,7 @@
         <v>45219</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40696,7 +40696,7 @@
         <v>45299</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40769,7 +40769,7 @@
         <v>45490</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40842,7 +40842,7 @@
         <v>45147</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40915,7 +40915,7 @@
         <v>45261</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40988,7 +40988,7 @@
         <v>45474</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41061,7 +41061,7 @@
         <v>45611</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41134,7 +41134,7 @@
         <v>46211</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41207,7 +41207,7 @@
         <v>45093</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41280,7 +41280,7 @@
         <v>45688</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>46216</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41426,7 +41426,7 @@
         <v>44936</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41499,7 +41499,7 @@
         <v>44603</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41572,7 +41572,7 @@
         <v>45147</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41645,7 +41645,7 @@
         <v>46259</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41718,7 +41718,7 @@
         <v>45740</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>44720</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41864,7 +41864,7 @@
         <v>44579</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41942,7 +41942,7 @@
         <v>44973</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42015,7 +42015,7 @@
         <v>45474</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42093,7 +42093,7 @@
         <v>46195</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42166,7 +42166,7 @@
         <v>44603</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42239,7 +42239,7 @@
         <v>45306</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42312,7 +42312,7 @@
         <v>46195</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42385,7 +42385,7 @@
         <v>44596</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42458,7 +42458,7 @@
         <v>44790</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42531,7 +42531,7 @@
         <v>45646</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42604,7 +42604,7 @@
         <v>44993</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42677,7 +42677,7 @@
         <v>45572</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42750,7 +42750,7 @@
         <v>45377</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42828,7 +42828,7 @@
         <v>45254</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42901,7 +42901,7 @@
         <v>45713</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42974,7 +42974,7 @@
         <v>45056</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43047,7 +43047,7 @@
         <v>45534</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43120,7 +43120,7 @@
         <v>44950</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43193,7 +43193,7 @@
         <v>46269</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43266,7 +43266,7 @@
         <v>45763</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43339,7 +43339,7 @@
         <v>46273</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43412,7 +43412,7 @@
         <v>45779</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43485,7 +43485,7 @@
         <v>46273</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43558,7 +43558,7 @@
         <v>45784</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43631,7 +43631,7 @@
         <v>46274</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43704,7 +43704,7 @@
         <v>46231</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43782,7 +43782,7 @@
         <v>46233</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43855,7 +43855,7 @@
         <v>46275</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43928,7 +43928,7 @@
         <v>44586</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44001,7 +44001,7 @@
         <v>46274</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44074,7 +44074,7 @@
         <v>45443</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44147,7 +44147,7 @@
         <v>46233</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44220,7 +44220,7 @@
         <v>46232</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44298,7 +44298,7 @@
         <v>46233</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44371,7 +44371,7 @@
         <v>45784</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44444,7 +44444,7 @@
         <v>46276</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>46233</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44590,7 +44590,7 @@
         <v>45418</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44663,7 +44663,7 @@
         <v>45434</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44736,7 +44736,7 @@
         <v>46279</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44809,7 +44809,7 @@
         <v>45443</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44887,7 +44887,7 @@
         <v>45713</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44960,7 +44960,7 @@
         <v>45672</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45033,7 +45033,7 @@
         <v>46237</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45106,7 +45106,7 @@
         <v>46237</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45179,7 +45179,7 @@
         <v>45724</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45252,7 +45252,7 @@
         <v>45721</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45325,7 +45325,7 @@
         <v>46237</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45398,7 +45398,7 @@
         <v>46237</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45471,7 +45471,7 @@
         <v>45792</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45544,7 +45544,7 @@
         <v>45792</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45617,7 +45617,7 @@
         <v>44971</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45690,7 +45690,7 @@
         <v>46283</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45763,7 +45763,7 @@
         <v>46283</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45836,7 +45836,7 @@
         <v>46282</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>45799</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45982,7 +45982,7 @@
         <v>46281</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         <v>45799</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46128,7 +46128,7 @@
         <v>45805</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46201,7 +46201,7 @@
         <v>45807</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46274,7 +46274,7 @@
         <v>45611</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46347,7 +46347,7 @@
         <v>44685</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46420,7 +46420,7 @@
         <v>45574</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46493,7 +46493,7 @@
         <v>45397</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46566,7 +46566,7 @@
         <v>45819</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46639,7 +46639,7 @@
         <v>45751</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46712,7 +46712,7 @@
         <v>45749</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46785,7 +46785,7 @@
         <v>45818</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46858,7 +46858,7 @@
         <v>45775</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46931,7 +46931,7 @@
         <v>45721</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47004,7 +47004,7 @@
         <v>45716</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47077,7 +47077,7 @@
         <v>45743</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47150,7 +47150,7 @@
         <v>45743</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47223,7 +47223,7 @@
         <v>45737</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>45728</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47369,7 +47369,7 @@
         <v>45743</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47442,7 +47442,7 @@
         <v>45826</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47520,7 +47520,7 @@
         <v>45737</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47593,7 +47593,7 @@
         <v>45740</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47666,7 +47666,7 @@
         <v>45743</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47739,7 +47739,7 @@
         <v>45741</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47817,7 +47817,7 @@
         <v>45831</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47890,7 +47890,7 @@
         <v>45833</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47963,7 +47963,7 @@
         <v>45833</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48036,7 +48036,7 @@
         <v>45834</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48109,7 +48109,7 @@
         <v>45838</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48182,7 +48182,7 @@
         <v>45839</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48260,7 +48260,7 @@
         <v>45838</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48333,7 +48333,7 @@
         <v>45841</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48406,7 +48406,7 @@
         <v>45841</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>45841</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48552,7 +48552,7 @@
         <v>45841</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48625,7 +48625,7 @@
         <v>45841</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48698,7 +48698,7 @@
         <v>45841</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48771,7 +48771,7 @@
         <v>45281</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48844,7 +48844,7 @@
         <v>45188</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48917,7 +48917,7 @@
         <v>45845</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48990,7 +48990,7 @@
         <v>45789</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49063,7 +49063,7 @@
         <v>45631</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49136,7 +49136,7 @@
         <v>45847</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49209,7 +49209,7 @@
         <v>45845</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49282,7 +49282,7 @@
         <v>45642</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>45849</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49428,7 +49428,7 @@
         <v>45807</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49501,7 +49501,7 @@
         <v>45734</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>45855</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49647,7 +49647,7 @@
         <v>45855</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49720,7 +49720,7 @@
         <v>45854</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49793,7 +49793,7 @@
         <v>45855</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49866,7 +49866,7 @@
         <v>44531</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49939,7 +49939,7 @@
         <v>45855</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50012,7 +50012,7 @@
         <v>45838</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50085,7 +50085,7 @@
         <v>45862</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50158,7 +50158,7 @@
         <v>45867</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50231,7 +50231,7 @@
         <v>45867</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50304,7 +50304,7 @@
         <v>45568</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50377,7 +50377,7 @@
         <v>45124</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50450,7 +50450,7 @@
         <v>45127</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50523,7 +50523,7 @@
         <v>44804</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50596,7 +50596,7 @@
         <v>44901</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50669,7 +50669,7 @@
         <v>44928</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50742,7 +50742,7 @@
         <v>45272</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50815,7 +50815,7 @@
         <v>45076</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50888,7 +50888,7 @@
         <v>44869</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50961,7 +50961,7 @@
         <v>44901</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51034,7 +51034,7 @@
         <v>45580</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51107,7 +51107,7 @@
         <v>44998</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51180,7 +51180,7 @@
         <v>45821</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51253,7 +51253,7 @@
         <v>45029</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51326,7 +51326,7 @@
         <v>45029</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51399,7 +51399,7 @@
         <v>45324</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51472,7 +51472,7 @@
         <v>44944</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51545,7 +51545,7 @@
         <v>45358</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51618,7 +51618,7 @@
         <v>44904</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51691,7 +51691,7 @@
         <v>45872</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51764,7 +51764,7 @@
         <v>44869</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51837,7 +51837,7 @@
         <v>45316</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51910,7 +51910,7 @@
         <v>45209</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51983,7 +51983,7 @@
         <v>45875</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52056,7 +52056,7 @@
         <v>45875</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52129,7 +52129,7 @@
         <v>45875</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52202,7 +52202,7 @@
         <v>45875</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52275,7 +52275,7 @@
         <v>45880</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52346,7 +52346,7 @@
         <v>44088</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52419,7 +52419,7 @@
         <v>44470</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52492,7 +52492,7 @@
         <v>44711</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52565,7 +52565,7 @@
         <v>44966</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52643,7 +52643,7 @@
         <v>45343</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52716,7 +52716,7 @@
         <v>44966</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52794,7 +52794,7 @@
         <v>45785</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52867,7 +52867,7 @@
         <v>45839</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52945,7 +52945,7 @@
         <v>45841</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53018,7 +53018,7 @@
         <v>45705</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53091,7 +53091,7 @@
         <v>45261</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53164,7 +53164,7 @@
         <v>45022</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53237,7 +53237,7 @@
         <v>46042</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53310,7 +53310,7 @@
         <v>46107</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53383,7 +53383,7 @@
         <v>46132</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53456,7 +53456,7 @@
         <v>46258</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>

--- a/Översikt MARK.xlsx
+++ b/Översikt MARK.xlsx
@@ -601,7 +601,7 @@
         <v>45497</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45617</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45137</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>45222</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>45348</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>45285</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>44482</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>45342</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44950</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>45618</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>45973</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>46001</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>46006</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>45638</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>46273</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>45137</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>45001</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>45154</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>45673</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>46266</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>44792</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>44846</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>45091</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>45271</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>46027</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45896</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>45324</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>45306</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>45596</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>45810</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>45841</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>45751</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>45191</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>45169</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>46203</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>45134</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>45849</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>46233</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>46268</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>45288</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>45936</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>45412</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         <v>44908</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>45792</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         <v>45786</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>46048</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>46107</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>44881</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>44469</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>44474</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>44843</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>44531</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>44750</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44764</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>44518</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>44523</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>44720</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>44869</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>44696</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>44764</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>44607</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>44811</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>44714</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>44722</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>44510</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>44816</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>44474</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>44684</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>44725</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>44874</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>44564</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>44467</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>44564</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44696</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>44615</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>44733</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>44609</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>44609</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>44725</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>44580</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>44497</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         <v>44840</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>44533</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>44680</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>44784</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>44699</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>44473</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         <v>44491</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>44652</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>44781</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>44469</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>44571</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>44473</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44473</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>44622</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>44539</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44725</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44470</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44692</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>45160</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>44768</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>44834</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>45415</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>44474</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>45212</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>45335</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>45254</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>45406</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>45135</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>45137</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>45106</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>45419</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>45414</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>45745</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>45397</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>45471</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
         <v>44882</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>45376</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         <v>45093</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         <v>45450</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>45233</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>45386</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>44902</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>44790</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>45210</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>45202</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>45322</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>45490</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>45490</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>45490</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>45147</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>45533</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         <v>46013</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>45724</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         <v>45714</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>45707</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>44971</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>45691</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>45713</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>45693</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>45134</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
         <v>45135</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>45119</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>45884</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>45342</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>46030</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>44952</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12956,7 +12956,7 @@
         <v>46034</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>44971</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>46034</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>45059</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         <v>45275</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         <v>45275</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>46030</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>46034</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>45888</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>45888</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>44978</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>45604</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>45855</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>45855</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         <v>45855</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         <v>45798</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14124,7 +14124,7 @@
         <v>44936</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>46037</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>45889</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>46038</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>45799</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         <v>46037</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>46037</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>45799</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
         <v>46037</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>45891</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>46038</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14932,7 +14932,7 @@
         <v>45896</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         <v>45895</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>45896</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15151,7 +15151,7 @@
         <v>45896</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15224,7 +15224,7 @@
         <v>45523</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15297,7 +15297,7 @@
         <v>45897</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>44896</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>44531</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15516,7 +15516,7 @@
         <v>45898</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>46048</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>46048</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15735,7 +15735,7 @@
         <v>46048</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15813,7 +15813,7 @@
         <v>46048</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>45518</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>45901</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>46046</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>46052</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>45905</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>45021</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>45909</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>46055</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>46055</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>46056</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>44603</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>46056</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>44924</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16850,7 +16850,7 @@
         <v>46058</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16923,7 +16923,7 @@
         <v>46057</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>45490</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>45490</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>45916</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>45667</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17288,7 +17288,7 @@
         <v>44574</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>46062</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>46064</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>45359</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>45924</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>45923</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>45923</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17804,7 +17804,7 @@
         <v>45379</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>44902</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>45925</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>45925</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>45264</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>45264</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>44896</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>45569</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18388,7 +18388,7 @@
         <v>45370</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>45925</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>44950</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>45261</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>45565</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>45925</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>45925</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18904,7 +18904,7 @@
         <v>45925</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>45699</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>46084</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>45805</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19196,7 +19196,7 @@
         <v>46045</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>46084</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>46084</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>45931</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>46084</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>45587</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>45611</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19707,7 +19707,7 @@
         <v>45534</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>46085</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>44950</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>44660</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         <v>44596</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>45419</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20150,7 +20150,7 @@
         <v>44467</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>45937</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>44673</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>44732</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>45807</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>45261</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20588,7 +20588,7 @@
         <v>45686</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20661,7 +20661,7 @@
         <v>45937</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>44589</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>44982</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20880,7 +20880,7 @@
         <v>45937</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>46092</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21026,7 +21026,7 @@
         <v>45943</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>46097</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>45943</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21245,7 +21245,7 @@
         <v>45922</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>45392</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21391,7 +21391,7 @@
         <v>45922</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
         <v>45268</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>46100</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>44993</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         <v>44897</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>45953</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>45075</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>45274</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>45953</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>44834</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>45294</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22194,7 +22194,7 @@
         <v>44909</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>46114</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>45959</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>45959</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>45964</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>45624</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>45624</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>45965</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22778,7 +22778,7 @@
         <v>44764</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>46127</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>44685</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22997,7 +22997,7 @@
         <v>45749</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>45978</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>45672</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>45672</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>44973</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>45397</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23435,7 +23435,7 @@
         <v>45818</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>45978</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>44881</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>45911</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>45119</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>45980</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45646</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>45751</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>45455</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>45982</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>46134</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>45137</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24311,7 +24311,7 @@
         <v>45574</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>45986</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>45684</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24535,7 +24535,7 @@
         <v>45631</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>45629</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24681,7 +24681,7 @@
         <v>44720</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>45681</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24827,7 +24827,7 @@
         <v>45099</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24900,7 +24900,7 @@
         <v>45197</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>44694</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>45030</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
         <v>45030</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25192,7 +25192,7 @@
         <v>45996</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25265,7 +25265,7 @@
         <v>45063</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>44762</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>45999</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>45140</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>45183</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>46000</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>46000</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>44806</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>45817</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>46000</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>46001</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>46000</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>46001</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26214,7 +26214,7 @@
         <v>45791</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>44501</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>46006</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>45091</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>46006</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>46008</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>45637</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>46007</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         <v>45719</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>45819</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>46009</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>45819</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>45868</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>45714</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27241,7 +27241,7 @@
         <v>45637</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27314,7 +27314,7 @@
         <v>45238</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>45839</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>45709</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27538,7 +27538,7 @@
         <v>45811</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27611,7 +27611,7 @@
         <v>46013</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>45775</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>45825</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>45918</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>45750</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>45826</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>45022</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>45107</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28200,7 +28200,7 @@
         <v>45751</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>45740</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>45721</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28419,7 +28419,7 @@
         <v>45737</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28492,7 +28492,7 @@
         <v>45741</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28570,7 +28570,7 @@
         <v>45743</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28643,7 +28643,7 @@
         <v>45728</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>45743</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28789,7 +28789,7 @@
         <v>45306</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28862,7 +28862,7 @@
         <v>45475</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>45716</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29008,7 +29008,7 @@
         <v>45743</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>45743</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>45264</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29227,7 +29227,7 @@
         <v>45737</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>44928</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29373,7 +29373,7 @@
         <v>44473</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29446,7 +29446,7 @@
         <v>45831</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29519,7 +29519,7 @@
         <v>46146</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29592,7 +29592,7 @@
         <v>45763</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29665,7 +29665,7 @@
         <v>45763</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>46147</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29811,7 +29811,7 @@
         <v>44713</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>44469</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>44714</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30030,7 +30030,7 @@
         <v>44637</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>45260</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30176,7 +30176,7 @@
         <v>46153</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>45833</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30322,7 +30322,7 @@
         <v>45834</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>45833</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30468,7 +30468,7 @@
         <v>45093</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30541,7 +30541,7 @@
         <v>45838</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30614,7 +30614,7 @@
         <v>45740</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>44588</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>45233</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30833,7 +30833,7 @@
         <v>45838</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30906,7 +30906,7 @@
         <v>45218</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30979,7 +30979,7 @@
         <v>45056</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>45776</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31125,7 +31125,7 @@
         <v>46120</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>45156</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31271,7 +31271,7 @@
         <v>45839</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>45841</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31422,7 +31422,7 @@
         <v>45841</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>45841</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>45841</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31641,7 +31641,7 @@
         <v>45841</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31714,7 +31714,7 @@
         <v>45104</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31787,7 +31787,7 @@
         <v>45841</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31860,7 +31860,7 @@
         <v>45121</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>45281</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32006,7 +32006,7 @@
         <v>46162</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>44489</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>45845</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         <v>45845</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>45188</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>45789</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32444,7 +32444,7 @@
         <v>45288</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>45358</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32590,7 +32590,7 @@
         <v>46165</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32668,7 +32668,7 @@
         <v>45370</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>45847</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32814,7 +32814,7 @@
         <v>45631</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>45642</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32960,7 +32960,7 @@
         <v>45734</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33033,7 +33033,7 @@
         <v>45776</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>45807</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>45093</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33252,7 +33252,7 @@
         <v>45849</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33325,7 +33325,7 @@
         <v>45093</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33398,7 +33398,7 @@
         <v>44531</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>45854</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33544,7 +33544,7 @@
         <v>45352</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>45838</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33690,7 +33690,7 @@
         <v>45855</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33763,7 +33763,7 @@
         <v>45855</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33836,7 +33836,7 @@
         <v>45855</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33909,7 +33909,7 @@
         <v>46169</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>45855</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34055,7 +34055,7 @@
         <v>45281</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34128,7 +34128,7 @@
         <v>45862</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34201,7 +34201,7 @@
         <v>44971</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         <v>45867</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34347,7 +34347,7 @@
         <v>46177</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>45251</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>45251</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>45867</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34639,7 +34639,7 @@
         <v>45106</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34717,7 +34717,7 @@
         <v>45106</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34795,7 +34795,7 @@
         <v>46181</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34868,7 +34868,7 @@
         <v>45629</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34941,7 +34941,7 @@
         <v>44928</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35014,7 +35014,7 @@
         <v>45029</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35087,7 +35087,7 @@
         <v>45029</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>44901</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>44904</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>44869</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>45324</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35452,7 +35452,7 @@
         <v>45358</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>45209</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35598,7 +35598,7 @@
         <v>45580</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35671,7 +35671,7 @@
         <v>45124</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35744,7 +35744,7 @@
         <v>44944</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35817,7 +35817,7 @@
         <v>44901</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35890,7 +35890,7 @@
         <v>45272</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>45127</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>46182</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36109,7 +36109,7 @@
         <v>45076</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>45872</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>44580</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36328,7 +36328,7 @@
         <v>45443</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36401,7 +36401,7 @@
         <v>44869</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36474,7 +36474,7 @@
         <v>44973</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36547,7 +36547,7 @@
         <v>44998</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36620,7 +36620,7 @@
         <v>44607</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36693,7 +36693,7 @@
         <v>45629</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36766,7 +36766,7 @@
         <v>46189</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>45568</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36912,7 +36912,7 @@
         <v>44804</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36985,7 +36985,7 @@
         <v>44599</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>44585</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37136,7 +37136,7 @@
         <v>46190</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37209,7 +37209,7 @@
         <v>45316</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37282,7 +37282,7 @@
         <v>45821</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37355,7 +37355,7 @@
         <v>45875</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37428,7 +37428,7 @@
         <v>45356</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37501,7 +37501,7 @@
         <v>45356</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37574,7 +37574,7 @@
         <v>46191</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37647,7 +37647,7 @@
         <v>46190</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37720,7 +37720,7 @@
         <v>45555</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
         <v>46195</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>46195</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37939,7 +37939,7 @@
         <v>45875</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38012,7 +38012,7 @@
         <v>45875</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>46195</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38158,7 +38158,7 @@
         <v>45332</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>46195</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38304,7 +38304,7 @@
         <v>45875</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38377,7 +38377,7 @@
         <v>46195</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38450,7 +38450,7 @@
         <v>46195</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38523,7 +38523,7 @@
         <v>45188</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38596,7 +38596,7 @@
         <v>45631</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38669,7 +38669,7 @@
         <v>44588</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38742,7 +38742,7 @@
         <v>45880</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>45189</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38888,7 +38888,7 @@
         <v>46199</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38966,7 +38966,7 @@
         <v>46198</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         <v>44648</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39112,7 +39112,7 @@
         <v>46203</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39185,7 +39185,7 @@
         <v>44798</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>45225</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39336,7 +39336,7 @@
         <v>45884</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>46204</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39482,7 +39482,7 @@
         <v>45373</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39555,7 +39555,7 @@
         <v>45076</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39628,7 +39628,7 @@
         <v>45763</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39701,7 +39701,7 @@
         <v>45194</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39774,7 +39774,7 @@
         <v>45236</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>45070</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39920,7 +39920,7 @@
         <v>45098</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39993,7 +39993,7 @@
         <v>45098</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>45572</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>46211</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40212,7 +40212,7 @@
         <v>45231</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>44734</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40358,7 +40358,7 @@
         <v>44624</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40431,7 +40431,7 @@
         <v>45713</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>45154</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40577,7 +40577,7 @@
         <v>45568</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40650,7 +40650,7 @@
         <v>45183</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40723,7 +40723,7 @@
         <v>44838</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40796,7 +40796,7 @@
         <v>45137</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40869,7 +40869,7 @@
         <v>46216</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40942,7 +40942,7 @@
         <v>46259</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41015,7 +41015,7 @@
         <v>45244</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41088,7 +41088,7 @@
         <v>46195</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>44715</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41234,7 +41234,7 @@
         <v>45422</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>46195</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>45474</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41458,7 +41458,7 @@
         <v>45251</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41531,7 +41531,7 @@
         <v>45299</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41604,7 +41604,7 @@
         <v>45373</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>44935</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>46269</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41823,7 +41823,7 @@
         <v>45750</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41896,7 +41896,7 @@
         <v>44888</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41969,7 +41969,7 @@
         <v>45379</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>46273</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>45763</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>46231</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42266,7 +42266,7 @@
         <v>46274</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42339,7 +42339,7 @@
         <v>45356</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42412,7 +42412,7 @@
         <v>46273</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42485,7 +42485,7 @@
         <v>45755</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42558,7 +42558,7 @@
         <v>45755</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>46274</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42704,7 +42704,7 @@
         <v>44987</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42777,7 +42777,7 @@
         <v>46233</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>45281</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45264</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>46232</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43074,7 +43074,7 @@
         <v>45251</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43147,7 +43147,7 @@
         <v>46233</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>46276</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>46275</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43366,7 +43366,7 @@
         <v>45684</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43439,7 +43439,7 @@
         <v>46237</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43512,7 +43512,7 @@
         <v>46237</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43585,7 +43585,7 @@
         <v>46233</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>45343</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>45397</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43804,7 +43804,7 @@
         <v>46279</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43877,7 +43877,7 @@
         <v>46237</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43950,7 +43950,7 @@
         <v>46237</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44023,7 +44023,7 @@
         <v>45254</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44096,7 +44096,7 @@
         <v>46233</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44169,7 +44169,7 @@
         <v>45230</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45428</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44315,7 +44315,7 @@
         <v>45137</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>46282</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>46281</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44534,7 +44534,7 @@
         <v>46283</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44607,7 +44607,7 @@
         <v>46286</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44680,7 +44680,7 @@
         <v>45552</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         <v>44897</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44826,7 +44826,7 @@
         <v>44935</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44899,7 +44899,7 @@
         <v>46283</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44972,7 +44972,7 @@
         <v>44610</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45045,7 +45045,7 @@
         <v>45432</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45123,7 +45123,7 @@
         <v>44603</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45196,7 +45196,7 @@
         <v>44615</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>45369</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>45475</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45415,7 +45415,7 @@
         <v>44588</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45488,7 +45488,7 @@
         <v>44588</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45561,7 +45561,7 @@
         <v>45147</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45634,7 +45634,7 @@
         <v>44937</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45707,7 +45707,7 @@
         <v>45710</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45780,7 +45780,7 @@
         <v>45332</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45853,7 +45853,7 @@
         <v>45898</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45926,7 +45926,7 @@
         <v>45595</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45999,7 +45999,7 @@
         <v>44760</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46072,7 +46072,7 @@
         <v>44631</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46145,7 +46145,7 @@
         <v>44994</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>44652</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46291,7 +46291,7 @@
         <v>44715</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>44982</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>45688</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46510,7 +46510,7 @@
         <v>45755</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
         <v>44630</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46661,7 +46661,7 @@
         <v>44978</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>45370</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46807,7 +46807,7 @@
         <v>44963</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>45474</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46953,7 +46953,7 @@
         <v>45134</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47026,7 +47026,7 @@
         <v>45224</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>45540</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47172,7 +47172,7 @@
         <v>45686</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47245,7 +47245,7 @@
         <v>45377</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45442</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>45204</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47469,7 +47469,7 @@
         <v>45154</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47542,7 +47542,7 @@
         <v>44950</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>44712</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47688,7 +47688,7 @@
         <v>45244</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47761,7 +47761,7 @@
         <v>45534</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>45484</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47907,7 +47907,7 @@
         <v>45016</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47980,7 +47980,7 @@
         <v>45342</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48053,7 +48053,7 @@
         <v>44803</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48126,7 +48126,7 @@
         <v>45526</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48199,7 +48199,7 @@
         <v>45202</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48272,7 +48272,7 @@
         <v>45021</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48345,7 +48345,7 @@
         <v>45611</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48418,7 +48418,7 @@
         <v>45611</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45342</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48564,7 +48564,7 @@
         <v>45210</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48637,7 +48637,7 @@
         <v>44813</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48710,7 +48710,7 @@
         <v>44813</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48783,7 +48783,7 @@
         <v>45680</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48856,7 +48856,7 @@
         <v>45355</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48929,7 +48929,7 @@
         <v>45264</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49002,7 +49002,7 @@
         <v>45474</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49080,7 +49080,7 @@
         <v>45604</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49153,7 +49153,7 @@
         <v>44632</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49226,7 +49226,7 @@
         <v>44994</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49299,7 +49299,7 @@
         <v>45030</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>44579</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49455,7 +49455,7 @@
         <v>45219</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49528,7 +49528,7 @@
         <v>44810</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49601,7 +49601,7 @@
         <v>45477</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49674,7 +49674,7 @@
         <v>45359</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49747,7 +49747,7 @@
         <v>45359</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49820,7 +49820,7 @@
         <v>44982</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49893,7 +49893,7 @@
         <v>45092</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49966,7 +49966,7 @@
         <v>45077</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50039,7 +50039,7 @@
         <v>45378</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50112,7 +50112,7 @@
         <v>45332</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50185,7 +50185,7 @@
         <v>45343</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50258,7 +50258,7 @@
         <v>45349</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50331,7 +50331,7 @@
         <v>45490</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50404,7 +50404,7 @@
         <v>45358</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50477,7 +50477,7 @@
         <v>45631</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>45629</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50623,7 +50623,7 @@
         <v>45301</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50696,7 +50696,7 @@
         <v>45779</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50769,7 +50769,7 @@
         <v>45784</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50842,7 +50842,7 @@
         <v>45443</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50915,7 +50915,7 @@
         <v>45784</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50988,7 +50988,7 @@
         <v>45443</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51066,7 +51066,7 @@
         <v>44586</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51139,7 +51139,7 @@
         <v>45672</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51212,7 +51212,7 @@
         <v>45713</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51285,7 +51285,7 @@
         <v>45418</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51358,7 +51358,7 @@
         <v>45434</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51431,7 +51431,7 @@
         <v>45724</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51504,7 +51504,7 @@
         <v>45792</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51577,7 +51577,7 @@
         <v>45792</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51650,7 +51650,7 @@
         <v>45721</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51721,7 +51721,7 @@
         <v>44088</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51794,7 +51794,7 @@
         <v>44711</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51867,7 +51867,7 @@
         <v>44470</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51940,7 +51940,7 @@
         <v>44966</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52018,7 +52018,7 @@
         <v>45343</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52091,7 +52091,7 @@
         <v>44966</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52169,7 +52169,7 @@
         <v>45785</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52242,7 +52242,7 @@
         <v>45839</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52320,7 +52320,7 @@
         <v>45841</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52393,7 +52393,7 @@
         <v>45705</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52466,7 +52466,7 @@
         <v>45261</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52539,7 +52539,7 @@
         <v>45022</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52612,7 +52612,7 @@
         <v>46042</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52685,7 +52685,7 @@
         <v>46107</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52758,7 +52758,7 @@
         <v>46132</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52831,7 +52831,7 @@
         <v>46258</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>

--- a/Översikt MARK.xlsx
+++ b/Översikt MARK.xlsx
@@ -601,7 +601,7 @@
         <v>45497</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45617</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45137</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>45222</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>45348</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>45285</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>44482</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>45342</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44950</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>45618</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>45973</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>46001</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>46006</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>45638</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>46273</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>45137</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>45001</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>45154</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>45673</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>46266</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>44792</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>44846</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>45091</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>45271</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>46027</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45896</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>45324</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>45306</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>45596</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>45810</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>45841</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>45751</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>45191</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>45169</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>46203</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>45134</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>45849</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>46233</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>46268</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>45288</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>45936</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>45412</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         <v>44908</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>45792</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         <v>45786</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>46048</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>46107</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>44881</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>44469</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>44474</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>44843</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>44531</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>44750</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44764</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>44518</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>44523</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>44720</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>44869</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>44696</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>44764</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>44607</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>44811</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>44714</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>44722</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>44510</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>44816</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>44474</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>44684</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>44725</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>44874</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>44564</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>44467</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>44564</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44696</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>44615</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>44733</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>44609</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>44609</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>44725</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>44580</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>44497</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         <v>44840</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>44533</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>44680</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>44784</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>44699</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>44473</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         <v>44491</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>44652</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>44781</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>44469</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>44571</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>44473</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44473</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>44622</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>44539</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44725</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44470</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44692</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>45160</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>44768</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>44834</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>45415</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>44474</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>45212</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>45335</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>45254</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>45406</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>45135</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>45137</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>45106</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>45419</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>45414</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>45745</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>45397</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>45471</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
         <v>44882</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>45376</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         <v>45093</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         <v>45450</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>45233</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>45386</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>44902</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>44790</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>45210</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>45202</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>45322</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>45490</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>45490</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>45490</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>45147</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>45533</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         <v>46013</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>45724</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         <v>45714</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>45707</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>44971</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>45691</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>45713</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>45693</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>45134</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
         <v>45135</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>45119</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>45884</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>45342</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>46030</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>44952</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12956,7 +12956,7 @@
         <v>46034</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>44971</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>46034</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>45059</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         <v>45275</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         <v>45275</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>46030</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>46034</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>45888</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>45888</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>44978</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>45604</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>45855</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>45855</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         <v>45855</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         <v>45798</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14124,7 +14124,7 @@
         <v>44936</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>46037</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>45889</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>46038</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>45799</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         <v>46037</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>46037</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>45799</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
         <v>46037</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>45891</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>46038</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14932,7 +14932,7 @@
         <v>45896</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         <v>45895</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>45896</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15151,7 +15151,7 @@
         <v>45896</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15224,7 +15224,7 @@
         <v>45523</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15297,7 +15297,7 @@
         <v>45897</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>44896</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>44531</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15516,7 +15516,7 @@
         <v>45898</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>46048</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>46048</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15735,7 +15735,7 @@
         <v>46048</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15813,7 +15813,7 @@
         <v>46048</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>45518</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>45901</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>46046</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>46052</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>45905</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>45021</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>45909</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>46055</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>46055</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>46056</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>44603</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>46056</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>44924</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16850,7 +16850,7 @@
         <v>46058</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16923,7 +16923,7 @@
         <v>46057</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>45490</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>45490</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>45916</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>45667</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17288,7 +17288,7 @@
         <v>44574</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>46062</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>46064</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>45359</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>45924</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>45923</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>45923</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17804,7 +17804,7 @@
         <v>45379</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>44902</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>45925</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>45925</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>45264</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>45264</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>44896</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>45569</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18388,7 +18388,7 @@
         <v>45370</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>45925</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>44950</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>45261</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>45565</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>45925</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>45925</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18904,7 +18904,7 @@
         <v>45925</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>45699</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>46084</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>45805</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19196,7 +19196,7 @@
         <v>46045</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>46084</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>46084</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>45931</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>46084</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>45587</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>45611</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19707,7 +19707,7 @@
         <v>45534</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>46085</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>44950</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>44660</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         <v>44596</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>45419</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20150,7 +20150,7 @@
         <v>44467</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>45937</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>44673</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>44732</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>45807</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>45261</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20588,7 +20588,7 @@
         <v>45686</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20661,7 +20661,7 @@
         <v>45937</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>44589</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>44982</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20880,7 +20880,7 @@
         <v>45937</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>46092</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21026,7 +21026,7 @@
         <v>45943</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>46097</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>45943</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21245,7 +21245,7 @@
         <v>45922</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>45392</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21391,7 +21391,7 @@
         <v>45922</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
         <v>45268</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>46100</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>44993</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         <v>44897</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>45953</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>45075</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>45274</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>45953</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>44834</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>45294</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22194,7 +22194,7 @@
         <v>44909</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>46114</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>45959</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>45959</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>45964</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>45624</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>45624</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>45965</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22778,7 +22778,7 @@
         <v>44764</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>46127</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>44685</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22997,7 +22997,7 @@
         <v>45749</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>45978</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>45672</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>45672</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>44973</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>45397</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23435,7 +23435,7 @@
         <v>45818</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>45978</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>44881</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>45911</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>45119</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>45980</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45646</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>45751</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>45455</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>45982</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>46134</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>45137</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24311,7 +24311,7 @@
         <v>45574</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>45986</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>45684</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24535,7 +24535,7 @@
         <v>45631</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>45629</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24681,7 +24681,7 @@
         <v>44720</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>45681</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24827,7 +24827,7 @@
         <v>45099</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24900,7 +24900,7 @@
         <v>45197</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>44694</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>45030</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
         <v>45030</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25192,7 +25192,7 @@
         <v>45996</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25265,7 +25265,7 @@
         <v>45063</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>44762</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>45999</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>45140</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>45183</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>46000</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>46000</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>44806</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>45817</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>46000</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>46001</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>46000</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>46001</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26214,7 +26214,7 @@
         <v>45791</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>44501</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>46006</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>45091</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>46006</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>46008</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>45637</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>46007</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         <v>45719</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>45819</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>46009</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>45819</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>45868</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>45714</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27241,7 +27241,7 @@
         <v>45637</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27314,7 +27314,7 @@
         <v>45238</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>45839</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>45709</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27538,7 +27538,7 @@
         <v>45811</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27611,7 +27611,7 @@
         <v>46013</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>45775</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>45825</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>45918</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>45750</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>45826</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>45022</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>45107</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28200,7 +28200,7 @@
         <v>45751</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>45740</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>45721</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28419,7 +28419,7 @@
         <v>45737</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28492,7 +28492,7 @@
         <v>45741</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28570,7 +28570,7 @@
         <v>45743</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28643,7 +28643,7 @@
         <v>45728</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>45743</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28789,7 +28789,7 @@
         <v>45306</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28862,7 +28862,7 @@
         <v>45475</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>45716</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29008,7 +29008,7 @@
         <v>45743</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>45743</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>45264</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29227,7 +29227,7 @@
         <v>45737</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>44928</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29373,7 +29373,7 @@
         <v>44473</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29446,7 +29446,7 @@
         <v>45831</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29519,7 +29519,7 @@
         <v>46146</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29592,7 +29592,7 @@
         <v>45763</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29665,7 +29665,7 @@
         <v>45763</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>46147</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29811,7 +29811,7 @@
         <v>44713</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>44469</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>44714</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30030,7 +30030,7 @@
         <v>44637</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>45260</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30176,7 +30176,7 @@
         <v>46153</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>45833</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30322,7 +30322,7 @@
         <v>45834</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>45833</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30468,7 +30468,7 @@
         <v>45093</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30541,7 +30541,7 @@
         <v>45838</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30614,7 +30614,7 @@
         <v>45740</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>44588</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>45233</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30833,7 +30833,7 @@
         <v>45838</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30906,7 +30906,7 @@
         <v>45218</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30979,7 +30979,7 @@
         <v>45056</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>45776</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31125,7 +31125,7 @@
         <v>46120</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>45156</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31271,7 +31271,7 @@
         <v>45839</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>45841</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31422,7 +31422,7 @@
         <v>45841</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>45841</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>45841</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31641,7 +31641,7 @@
         <v>45841</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31714,7 +31714,7 @@
         <v>45104</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31787,7 +31787,7 @@
         <v>45841</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31860,7 +31860,7 @@
         <v>45121</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>45281</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32006,7 +32006,7 @@
         <v>46162</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>44489</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>45845</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         <v>45845</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>45188</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>45789</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32444,7 +32444,7 @@
         <v>45288</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>45358</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32590,7 +32590,7 @@
         <v>46165</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32668,7 +32668,7 @@
         <v>45370</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>45847</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32814,7 +32814,7 @@
         <v>45631</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>45642</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32960,7 +32960,7 @@
         <v>45734</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33033,7 +33033,7 @@
         <v>45776</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>45807</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>45093</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33252,7 +33252,7 @@
         <v>45849</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33325,7 +33325,7 @@
         <v>45093</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33398,7 +33398,7 @@
         <v>44531</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>45854</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33544,7 +33544,7 @@
         <v>45352</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>45838</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33690,7 +33690,7 @@
         <v>45855</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33763,7 +33763,7 @@
         <v>45855</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33836,7 +33836,7 @@
         <v>45855</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33909,7 +33909,7 @@
         <v>46169</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>45855</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34055,7 +34055,7 @@
         <v>45281</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34128,7 +34128,7 @@
         <v>45862</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34201,7 +34201,7 @@
         <v>44971</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         <v>45867</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34347,7 +34347,7 @@
         <v>46177</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>45251</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>45251</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>45867</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34639,7 +34639,7 @@
         <v>45106</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34717,7 +34717,7 @@
         <v>45106</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34795,7 +34795,7 @@
         <v>46181</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34868,7 +34868,7 @@
         <v>45629</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34941,7 +34941,7 @@
         <v>44928</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35014,7 +35014,7 @@
         <v>45029</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35087,7 +35087,7 @@
         <v>45029</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>44901</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>44904</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>44869</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>45324</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35452,7 +35452,7 @@
         <v>45358</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>45209</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35598,7 +35598,7 @@
         <v>45580</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35671,7 +35671,7 @@
         <v>45124</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35744,7 +35744,7 @@
         <v>44944</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35817,7 +35817,7 @@
         <v>44901</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35890,7 +35890,7 @@
         <v>45272</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>45127</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>46182</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36109,7 +36109,7 @@
         <v>45076</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>45872</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>44580</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36328,7 +36328,7 @@
         <v>45443</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36401,7 +36401,7 @@
         <v>44869</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36474,7 +36474,7 @@
         <v>44973</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36547,7 +36547,7 @@
         <v>44998</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36620,7 +36620,7 @@
         <v>44607</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36693,7 +36693,7 @@
         <v>45629</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36766,7 +36766,7 @@
         <v>46189</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>45568</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36912,7 +36912,7 @@
         <v>44804</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36985,7 +36985,7 @@
         <v>44599</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>44585</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37136,7 +37136,7 @@
         <v>46190</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37209,7 +37209,7 @@
         <v>45316</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37282,7 +37282,7 @@
         <v>45821</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37355,7 +37355,7 @@
         <v>45875</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37428,7 +37428,7 @@
         <v>45356</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37501,7 +37501,7 @@
         <v>45356</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37574,7 +37574,7 @@
         <v>46191</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37647,7 +37647,7 @@
         <v>46190</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37720,7 +37720,7 @@
         <v>45555</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
         <v>46195</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>46195</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37939,7 +37939,7 @@
         <v>45875</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38012,7 +38012,7 @@
         <v>45875</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>46195</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38158,7 +38158,7 @@
         <v>45332</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>46195</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38304,7 +38304,7 @@
         <v>45875</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38377,7 +38377,7 @@
         <v>46195</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38450,7 +38450,7 @@
         <v>46195</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38523,7 +38523,7 @@
         <v>45188</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38596,7 +38596,7 @@
         <v>45631</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38669,7 +38669,7 @@
         <v>44588</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38742,7 +38742,7 @@
         <v>45880</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>45189</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38888,7 +38888,7 @@
         <v>46199</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38966,7 +38966,7 @@
         <v>46198</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         <v>44648</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39112,7 +39112,7 @@
         <v>46203</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39185,7 +39185,7 @@
         <v>44798</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>45225</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39336,7 +39336,7 @@
         <v>45884</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>46204</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39482,7 +39482,7 @@
         <v>45373</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39555,7 +39555,7 @@
         <v>45076</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39628,7 +39628,7 @@
         <v>45763</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39701,7 +39701,7 @@
         <v>45194</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39774,7 +39774,7 @@
         <v>45236</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>45070</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39920,7 +39920,7 @@
         <v>45098</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39993,7 +39993,7 @@
         <v>45098</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>45572</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>46211</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40212,7 +40212,7 @@
         <v>45231</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>44734</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40358,7 +40358,7 @@
         <v>44624</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40431,7 +40431,7 @@
         <v>45713</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>45154</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40577,7 +40577,7 @@
         <v>45568</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40650,7 +40650,7 @@
         <v>45183</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40723,7 +40723,7 @@
         <v>44838</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40796,7 +40796,7 @@
         <v>45137</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40869,7 +40869,7 @@
         <v>46216</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40942,7 +40942,7 @@
         <v>46259</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41015,7 +41015,7 @@
         <v>45244</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41088,7 +41088,7 @@
         <v>46195</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>44715</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41234,7 +41234,7 @@
         <v>45422</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>46195</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>45474</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41458,7 +41458,7 @@
         <v>45251</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41531,7 +41531,7 @@
         <v>45299</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41604,7 +41604,7 @@
         <v>45373</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>44935</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>46269</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41823,7 +41823,7 @@
         <v>45750</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41896,7 +41896,7 @@
         <v>44888</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41969,7 +41969,7 @@
         <v>45379</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>46273</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>45763</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>46231</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42266,7 +42266,7 @@
         <v>46274</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42339,7 +42339,7 @@
         <v>45356</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42412,7 +42412,7 @@
         <v>46273</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42485,7 +42485,7 @@
         <v>45755</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42558,7 +42558,7 @@
         <v>45755</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>46274</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42704,7 +42704,7 @@
         <v>44987</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42777,7 +42777,7 @@
         <v>46233</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>45281</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45264</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>46232</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43074,7 +43074,7 @@
         <v>45251</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43147,7 +43147,7 @@
         <v>46233</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>46276</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>46275</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43366,7 +43366,7 @@
         <v>45684</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43439,7 +43439,7 @@
         <v>46237</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43512,7 +43512,7 @@
         <v>46237</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43585,7 +43585,7 @@
         <v>46233</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>45343</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>45397</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43804,7 +43804,7 @@
         <v>46279</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43877,7 +43877,7 @@
         <v>46237</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43950,7 +43950,7 @@
         <v>46237</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44023,7 +44023,7 @@
         <v>45254</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44096,7 +44096,7 @@
         <v>46233</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44169,7 +44169,7 @@
         <v>45230</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45428</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44315,7 +44315,7 @@
         <v>45137</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>46282</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>46281</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44534,7 +44534,7 @@
         <v>46283</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44607,7 +44607,7 @@
         <v>46286</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44680,7 +44680,7 @@
         <v>45552</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         <v>44897</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44826,7 +44826,7 @@
         <v>44935</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44899,7 +44899,7 @@
         <v>46283</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44972,7 +44972,7 @@
         <v>44610</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45045,7 +45045,7 @@
         <v>45432</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45123,7 +45123,7 @@
         <v>44603</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45196,7 +45196,7 @@
         <v>44615</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>45369</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>45475</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45415,7 +45415,7 @@
         <v>44588</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45488,7 +45488,7 @@
         <v>44588</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45561,7 +45561,7 @@
         <v>45147</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45634,7 +45634,7 @@
         <v>44937</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45707,7 +45707,7 @@
         <v>45710</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45780,7 +45780,7 @@
         <v>45332</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45853,7 +45853,7 @@
         <v>45898</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45926,7 +45926,7 @@
         <v>45595</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45999,7 +45999,7 @@
         <v>44760</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46072,7 +46072,7 @@
         <v>44631</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46145,7 +46145,7 @@
         <v>44994</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>44652</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46291,7 +46291,7 @@
         <v>44715</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>44982</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>45688</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46510,7 +46510,7 @@
         <v>45755</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
         <v>44630</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46661,7 +46661,7 @@
         <v>44978</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>45370</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46807,7 +46807,7 @@
         <v>44963</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>45474</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46953,7 +46953,7 @@
         <v>45134</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47026,7 +47026,7 @@
         <v>45224</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>45540</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47172,7 +47172,7 @@
         <v>45686</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47245,7 +47245,7 @@
         <v>45377</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45442</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>45204</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47469,7 +47469,7 @@
         <v>45154</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47542,7 +47542,7 @@
         <v>44950</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>44712</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47688,7 +47688,7 @@
         <v>45244</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47761,7 +47761,7 @@
         <v>45534</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>45484</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47907,7 +47907,7 @@
         <v>45016</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47980,7 +47980,7 @@
         <v>45342</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48053,7 +48053,7 @@
         <v>44803</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48126,7 +48126,7 @@
         <v>45526</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48199,7 +48199,7 @@
         <v>45202</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48272,7 +48272,7 @@
         <v>45021</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48345,7 +48345,7 @@
         <v>45611</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48418,7 +48418,7 @@
         <v>45611</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45342</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48564,7 +48564,7 @@
         <v>45210</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48637,7 +48637,7 @@
         <v>44813</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48710,7 +48710,7 @@
         <v>44813</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48783,7 +48783,7 @@
         <v>45680</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48856,7 +48856,7 @@
         <v>45355</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48929,7 +48929,7 @@
         <v>45264</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49002,7 +49002,7 @@
         <v>45474</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49080,7 +49080,7 @@
         <v>45604</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49153,7 +49153,7 @@
         <v>44632</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49226,7 +49226,7 @@
         <v>44994</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49299,7 +49299,7 @@
         <v>45030</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>44579</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49455,7 +49455,7 @@
         <v>45219</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49528,7 +49528,7 @@
         <v>44810</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49601,7 +49601,7 @@
         <v>45477</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49674,7 +49674,7 @@
         <v>45359</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49747,7 +49747,7 @@
         <v>45359</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49820,7 +49820,7 @@
         <v>44982</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49893,7 +49893,7 @@
         <v>45092</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49966,7 +49966,7 @@
         <v>45077</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50039,7 +50039,7 @@
         <v>45378</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50112,7 +50112,7 @@
         <v>45332</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50185,7 +50185,7 @@
         <v>45343</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50258,7 +50258,7 @@
         <v>45349</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50331,7 +50331,7 @@
         <v>45490</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50404,7 +50404,7 @@
         <v>45358</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50477,7 +50477,7 @@
         <v>45631</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>45629</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50623,7 +50623,7 @@
         <v>45301</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50696,7 +50696,7 @@
         <v>45779</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50769,7 +50769,7 @@
         <v>45784</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50842,7 +50842,7 @@
         <v>45443</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50915,7 +50915,7 @@
         <v>45784</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50988,7 +50988,7 @@
         <v>45443</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51066,7 +51066,7 @@
         <v>44586</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51139,7 +51139,7 @@
         <v>45672</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51212,7 +51212,7 @@
         <v>45713</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51285,7 +51285,7 @@
         <v>45418</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51358,7 +51358,7 @@
         <v>45434</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51431,7 +51431,7 @@
         <v>45724</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51504,7 +51504,7 @@
         <v>45792</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51577,7 +51577,7 @@
         <v>45792</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51650,7 +51650,7 @@
         <v>45721</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51721,7 +51721,7 @@
         <v>44088</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51794,7 +51794,7 @@
         <v>44711</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51867,7 +51867,7 @@
         <v>44470</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51940,7 +51940,7 @@
         <v>44966</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52018,7 +52018,7 @@
         <v>45343</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52091,7 +52091,7 @@
         <v>44966</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52169,7 +52169,7 @@
         <v>45785</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52242,7 +52242,7 @@
         <v>45839</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52320,7 +52320,7 @@
         <v>45841</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52393,7 +52393,7 @@
         <v>45705</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52466,7 +52466,7 @@
         <v>45261</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52539,7 +52539,7 @@
         <v>45022</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52612,7 +52612,7 @@
         <v>46042</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52685,7 +52685,7 @@
         <v>46107</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52758,7 +52758,7 @@
         <v>46132</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52831,7 +52831,7 @@
         <v>46258</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>

--- a/Översikt MARK.xlsx
+++ b/Översikt MARK.xlsx
@@ -601,7 +601,7 @@
         <v>45497</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45617</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45222</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>45137</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>45348</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>45285</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>44482</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>45001</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>46006</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>45973</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>45638</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>45342</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>46001</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>45154</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>45137</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>46273</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45618</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>44950</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>45673</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>46266</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>44792</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>44846</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>46027</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>45896</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>45792</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45091</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>45412</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45191</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>45306</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>45169</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>45841</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>45810</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>45271</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>46203</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>45134</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>45324</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>45849</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>46233</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>46268</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>45936</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>45288</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>45596</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>45751</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>44908</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         <v>45786</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>46048</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>46107</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>44881</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>44474</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>44843</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>44531</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>44750</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>44518</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>44764</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>44523</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>44720</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>44696</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>44764</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>44607</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>44811</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>44714</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>44722</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>44510</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>44816</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>44474</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>44684</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>44725</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>44874</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>44564</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>44564</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>44696</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>44615</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>44733</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44725</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>44609</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>44609</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>44580</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>44840</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>44497</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>44533</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>44680</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         <v>44784</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         <v>44699</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>44473</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>44491</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>44652</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>44781</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         <v>44571</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>44473</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>44473</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>44539</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>44622</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>44725</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44692</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>45342</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>44982</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>45475</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44902</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44585</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>45359</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
         <v>45568</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
         <v>44631</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>45030</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>44630</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>45093</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>45106</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>45093</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>45681</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
         <v>44937</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>44632</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10255,7 +10255,7 @@
         <v>45684</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>45183</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>44715</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>45428</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>44599</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>45745</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>45434</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>45443</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>45713</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>46000</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>45798</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
         <v>45672</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>45294</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         <v>45855</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11287,7 +11287,7 @@
         <v>45855</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>44473</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>45376</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>46007</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>46006</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>46006</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>45373</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>44607</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>46008</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>45631</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>45059</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>46009</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>45724</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>46013</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>45137</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>46013</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         <v>44810</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
         <v>45721</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>45611</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>45884</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>45724</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>45022</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>45707</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>45714</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>45714</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>45713</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>45839</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>45238</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>45693</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>45709</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>45691</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>44798</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         <v>45406</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>45888</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>44935</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13852,7 +13852,7 @@
         <v>45888</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>45889</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45891</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>45189</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>45895</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>45358</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>45896</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>44987</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>45604</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>45896</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>45896</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>45332</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>45332</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14801,7 +14801,7 @@
         <v>46030</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>45898</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>46030</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>45897</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         <v>46034</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>45135</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>45901</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>45604</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>46034</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>46034</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>46037</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>46037</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         <v>44474</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>44950</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>45016</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15896,7 +15896,7 @@
         <v>46037</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15969,7 +15969,7 @@
         <v>46037</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>46038</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>45905</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>45231</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>46038</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>45422</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>45909</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>45792</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>45792</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>44610</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>44971</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>45624</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16850,7 +16850,7 @@
         <v>45624</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16923,7 +16923,7 @@
         <v>44734</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>46048</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>45587</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>46048</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>46048</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17288,7 +17288,7 @@
         <v>46046</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>45799</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>46048</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>45916</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>45799</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>44982</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>45343</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17804,7 +17804,7 @@
         <v>45244</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>45805</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>45807</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>44760</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>45751</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>45923</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>45923</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>44762</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18388,7 +18388,7 @@
         <v>46055</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>45925</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>45925</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>45925</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>45925</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>46052</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>46055</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18904,7 +18904,7 @@
         <v>45925</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>45925</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>46056</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>45924</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>46057</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>46056</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>46058</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>44973</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>46062</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>45931</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>45244</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>46064</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>44574</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>45030</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>45937</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>45937</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
         <v>45937</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>45261</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>44588</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>44588</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20379,7 +20379,7 @@
         <v>45922</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20452,7 +20452,7 @@
         <v>45611</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>45922</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20598,7 +20598,7 @@
         <v>45943</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20671,7 +20671,7 @@
         <v>45355</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20744,7 +20744,7 @@
         <v>44896</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20817,7 +20817,7 @@
         <v>45943</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>45397</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20963,7 +20963,7 @@
         <v>44580</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21036,7 +21036,7 @@
         <v>45699</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21109,7 +21109,7 @@
         <v>46084</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
         <v>45953</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>46084</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>46084</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21401,7 +21401,7 @@
         <v>45953</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>45750</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>46045</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>45471</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>46084</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>46085</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>45959</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>45959</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21990,7 +21990,7 @@
         <v>45098</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22063,7 +22063,7 @@
         <v>45098</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>45631</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22209,7 +22209,7 @@
         <v>45183</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22282,7 +22282,7 @@
         <v>44685</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22355,7 +22355,7 @@
         <v>45686</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>45574</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>45212</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>46092</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22647,7 +22647,7 @@
         <v>45965</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>45964</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22793,7 +22793,7 @@
         <v>44882</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22866,7 +22866,7 @@
         <v>46097</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>46100</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23012,7 +23012,7 @@
         <v>45397</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>45978</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>45819</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>45978</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23304,7 +23304,7 @@
         <v>45629</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23377,7 +23377,7 @@
         <v>45751</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>45281</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>45749</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23596,7 +23596,7 @@
         <v>45980</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23669,7 +23669,7 @@
         <v>45818</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>45021</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         <v>45104</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>45982</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23961,7 +23961,7 @@
         <v>45637</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24034,7 +24034,7 @@
         <v>45775</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
         <v>45986</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>46114</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24253,7 +24253,7 @@
         <v>44615</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>45202</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>44982</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>45721</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24545,7 +24545,7 @@
         <v>45719</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>45716</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>45397</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>45743</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24842,7 +24842,7 @@
         <v>45743</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>45737</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>44764</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>45160</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25134,7 +25134,7 @@
         <v>45728</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>45911</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25280,7 +25280,7 @@
         <v>45490</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>45490</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>45490</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>45999</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>45743</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>45826</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25723,7 +25723,7 @@
         <v>45737</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>45740</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25869,7 +25869,7 @@
         <v>45743</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>45996</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26015,7 +26015,7 @@
         <v>46127</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26088,7 +26088,7 @@
         <v>45741</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26166,7 +26166,7 @@
         <v>46000</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26239,7 +26239,7 @@
         <v>46001</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26312,7 +26312,7 @@
         <v>46001</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26385,7 +26385,7 @@
         <v>46000</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26458,7 +26458,7 @@
         <v>45121</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26531,7 +26531,7 @@
         <v>45831</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>46000</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26677,7 +26677,7 @@
         <v>45455</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>45091</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>45833</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>44994</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26969,7 +26969,7 @@
         <v>45833</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>46134</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>44715</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>45343</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27261,7 +27261,7 @@
         <v>45834</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>45197</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27407,7 +27407,7 @@
         <v>45356</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27480,7 +27480,7 @@
         <v>45356</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>45825</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>45838</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27699,7 +27699,7 @@
         <v>45839</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27777,7 +27777,7 @@
         <v>45838</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27850,7 +27850,7 @@
         <v>45637</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27923,7 +27923,7 @@
         <v>45841</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27996,7 +27996,7 @@
         <v>44501</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28069,7 +28069,7 @@
         <v>45819</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28142,7 +28142,7 @@
         <v>45791</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28215,7 +28215,7 @@
         <v>45841</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28288,7 +28288,7 @@
         <v>45322</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28361,7 +28361,7 @@
         <v>45841</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>45841</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28507,7 +28507,7 @@
         <v>45841</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28580,7 +28580,7 @@
         <v>45841</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28653,7 +28653,7 @@
         <v>45450</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28726,7 +28726,7 @@
         <v>45370</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28799,7 +28799,7 @@
         <v>44624</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>45540</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>45281</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29018,7 +29018,7 @@
         <v>45188</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29091,7 +29091,7 @@
         <v>45477</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29164,7 +29164,7 @@
         <v>45845</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29237,7 +29237,7 @@
         <v>45789</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29310,7 +29310,7 @@
         <v>45631</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29383,7 +29383,7 @@
         <v>45847</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29456,7 +29456,7 @@
         <v>45595</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29529,7 +29529,7 @@
         <v>45845</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29602,7 +29602,7 @@
         <v>45642</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29675,7 +29675,7 @@
         <v>45849</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29748,7 +29748,7 @@
         <v>45684</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
         <v>45063</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>45817</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29967,7 +29967,7 @@
         <v>44978</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30040,7 +30040,7 @@
         <v>45335</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30113,7 +30113,7 @@
         <v>45807</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30186,7 +30186,7 @@
         <v>44971</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30259,7 +30259,7 @@
         <v>45734</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>45855</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30405,7 +30405,7 @@
         <v>45855</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>45854</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30551,7 +30551,7 @@
         <v>44694</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30624,7 +30624,7 @@
         <v>45855</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30697,7 +30697,7 @@
         <v>44531</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30770,7 +30770,7 @@
         <v>45137</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30843,7 +30843,7 @@
         <v>45855</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30916,7 +30916,7 @@
         <v>45075</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30989,7 +30989,7 @@
         <v>45629</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31062,7 +31062,7 @@
         <v>44648</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31135,7 +31135,7 @@
         <v>45811</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31208,7 +31208,7 @@
         <v>44834</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31281,7 +31281,7 @@
         <v>45838</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31354,7 +31354,7 @@
         <v>45868</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31427,7 +31427,7 @@
         <v>44928</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>44838</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31573,7 +31573,7 @@
         <v>45106</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31651,7 +31651,7 @@
         <v>45106</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31729,7 +31729,7 @@
         <v>44713</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31802,7 +31802,7 @@
         <v>45680</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>45862</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31948,7 +31948,7 @@
         <v>45755</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32021,7 +32021,7 @@
         <v>45755</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32094,7 +32094,7 @@
         <v>45755</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32167,7 +32167,7 @@
         <v>45867</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>45349</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32313,7 +32313,7 @@
         <v>45918</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32386,7 +32386,7 @@
         <v>45867</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32459,7 +32459,7 @@
         <v>44935</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32532,7 +32532,7 @@
         <v>45484</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32605,7 +32605,7 @@
         <v>45224</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32678,7 +32678,7 @@
         <v>45568</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32751,7 +32751,7 @@
         <v>45124</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32824,7 +32824,7 @@
         <v>45127</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32897,7 +32897,7 @@
         <v>45194</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32970,7 +32970,7 @@
         <v>44804</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33043,7 +33043,7 @@
         <v>44901</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33116,7 +33116,7 @@
         <v>44928</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33189,7 +33189,7 @@
         <v>45272</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33262,7 +33262,7 @@
         <v>45076</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>44869</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33408,7 +33408,7 @@
         <v>45264</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33481,7 +33481,7 @@
         <v>45264</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33554,7 +33554,7 @@
         <v>44901</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33627,7 +33627,7 @@
         <v>45580</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33700,7 +33700,7 @@
         <v>44714</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33773,7 +33773,7 @@
         <v>44998</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>45821</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>46146</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33992,7 +33992,7 @@
         <v>44950</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>46147</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34143,7 +34143,7 @@
         <v>45029</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>45029</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34289,7 +34289,7 @@
         <v>45324</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>45555</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34435,7 +34435,7 @@
         <v>45419</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34508,7 +34508,7 @@
         <v>44944</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>45358</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34654,7 +34654,7 @@
         <v>44904</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>45872</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34800,7 +34800,7 @@
         <v>44869</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34873,7 +34873,7 @@
         <v>45316</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34946,7 +34946,7 @@
         <v>46153</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>45137</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35092,7 +35092,7 @@
         <v>45209</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35165,7 +35165,7 @@
         <v>45442</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>44712</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35311,7 +35311,7 @@
         <v>45268</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>45414</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35462,7 +35462,7 @@
         <v>45875</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>45288</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35608,7 +35608,7 @@
         <v>45392</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35681,7 +35681,7 @@
         <v>45490</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35754,7 +35754,7 @@
         <v>45750</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35827,7 +35827,7 @@
         <v>46120</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35900,7 +35900,7 @@
         <v>45342</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>45875</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36046,7 +36046,7 @@
         <v>45776</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36119,7 +36119,7 @@
         <v>45875</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36192,7 +36192,7 @@
         <v>45875</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36265,7 +36265,7 @@
         <v>46162</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36338,7 +36338,7 @@
         <v>45629</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36411,7 +36411,7 @@
         <v>45432</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36489,7 +36489,7 @@
         <v>45419</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36562,7 +36562,7 @@
         <v>44768</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36635,7 +36635,7 @@
         <v>45342</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36708,7 +36708,7 @@
         <v>46165</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36786,7 +36786,7 @@
         <v>45533</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36859,7 +36859,7 @@
         <v>45140</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36932,7 +36932,7 @@
         <v>45667</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37005,7 +37005,7 @@
         <v>45776</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>45356</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37151,7 +37151,7 @@
         <v>45880</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37224,7 +37224,7 @@
         <v>46169</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37297,7 +37297,7 @@
         <v>46177</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37370,7 +37370,7 @@
         <v>45855</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37443,7 +37443,7 @@
         <v>45884</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37516,7 +37516,7 @@
         <v>45134</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37589,7 +37589,7 @@
         <v>44803</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37662,7 +37662,7 @@
         <v>44489</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37735,7 +37735,7 @@
         <v>44971</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37808,7 +37808,7 @@
         <v>45260</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37881,7 +37881,7 @@
         <v>46182</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37954,7 +37954,7 @@
         <v>46181</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38027,7 +38027,7 @@
         <v>44834</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38100,7 +38100,7 @@
         <v>44806</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38173,7 +38173,7 @@
         <v>45154</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38246,7 +38246,7 @@
         <v>44896</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38319,7 +38319,7 @@
         <v>46190</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38392,7 +38392,7 @@
         <v>46189</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38465,7 +38465,7 @@
         <v>46190</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38538,7 +38538,7 @@
         <v>45552</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38611,7 +38611,7 @@
         <v>46191</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38684,7 +38684,7 @@
         <v>46195</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38757,7 +38757,7 @@
         <v>46195</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38830,7 +38830,7 @@
         <v>45076</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38903,7 +38903,7 @@
         <v>46195</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38976,7 +38976,7 @@
         <v>45137</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39049,7 +39049,7 @@
         <v>46195</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39122,7 +39122,7 @@
         <v>45264</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39195,7 +39195,7 @@
         <v>46195</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39268,7 +39268,7 @@
         <v>46195</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39341,7 +39341,7 @@
         <v>44952</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39414,7 +39414,7 @@
         <v>46198</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         <v>45443</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39560,7 +39560,7 @@
         <v>45526</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39633,7 +39633,7 @@
         <v>46199</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39711,7 +39711,7 @@
         <v>45236</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>45154</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39857,7 +39857,7 @@
         <v>44660</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39930,7 +39930,7 @@
         <v>45301</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40003,7 +40003,7 @@
         <v>46203</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40076,7 +40076,7 @@
         <v>44588</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40149,7 +40149,7 @@
         <v>44732</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40222,7 +40222,7 @@
         <v>45021</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40295,7 +40295,7 @@
         <v>46204</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40368,7 +40368,7 @@
         <v>45275</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
         <v>45275</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40514,7 +40514,7 @@
         <v>44978</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45386</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40660,7 +40660,7 @@
         <v>46211</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40733,7 +40733,7 @@
         <v>44963</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40806,7 +40806,7 @@
         <v>46216</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40879,7 +40879,7 @@
         <v>46259</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>44902</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41025,7 +41025,7 @@
         <v>45379</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41098,7 +41098,7 @@
         <v>46195</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41171,7 +41171,7 @@
         <v>46195</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41244,7 +41244,7 @@
         <v>45251</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41317,7 +41317,7 @@
         <v>45251</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41390,7 +41390,7 @@
         <v>45135</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41463,7 +41463,7 @@
         <v>45251</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>45686</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41609,7 +41609,7 @@
         <v>45119</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41682,7 +41682,7 @@
         <v>44813</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41755,7 +41755,7 @@
         <v>45518</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41833,7 +41833,7 @@
         <v>46269</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41906,7 +41906,7 @@
         <v>44909</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>46273</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42052,7 +42052,7 @@
         <v>46273</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42125,7 +42125,7 @@
         <v>45672</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42198,7 +42198,7 @@
         <v>45672</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42271,7 +42271,7 @@
         <v>44637</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42344,7 +42344,7 @@
         <v>45230</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42417,7 +42417,7 @@
         <v>46274</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42490,7 +42490,7 @@
         <v>46231</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42568,7 +42568,7 @@
         <v>46233</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42641,7 +42641,7 @@
         <v>45210</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42714,7 +42714,7 @@
         <v>45218</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42787,7 +42787,7 @@
         <v>46275</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42860,7 +42860,7 @@
         <v>45204</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42933,7 +42933,7 @@
         <v>46274</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43006,7 +43006,7 @@
         <v>46233</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43079,7 +43079,7 @@
         <v>46232</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43157,7 +43157,7 @@
         <v>46233</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43230,7 +43230,7 @@
         <v>46276</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43303,7 +43303,7 @@
         <v>46233</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43376,7 +43376,7 @@
         <v>45233</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43454,7 +43454,7 @@
         <v>46279</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43527,7 +43527,7 @@
         <v>45233</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>46237</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43673,7 +43673,7 @@
         <v>46237</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43746,7 +43746,7 @@
         <v>45107</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43819,7 +43819,7 @@
         <v>45225</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43892,7 +43892,7 @@
         <v>45378</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43965,7 +43965,7 @@
         <v>45523</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44038,7 +44038,7 @@
         <v>46237</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44111,7 +44111,7 @@
         <v>46237</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44184,7 +44184,7 @@
         <v>44813</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44257,7 +44257,7 @@
         <v>46283</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44330,7 +44330,7 @@
         <v>46283</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44403,7 +44403,7 @@
         <v>46282</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44476,7 +44476,7 @@
         <v>46281</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44549,7 +44549,7 @@
         <v>44531</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44622,7 +44622,7 @@
         <v>46286</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>45254</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44768,7 +44768,7 @@
         <v>44994</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>45373</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44914,7 +44914,7 @@
         <v>45070</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44987,7 +44987,7 @@
         <v>45264</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45060,7 +45060,7 @@
         <v>44588</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45133,7 +45133,7 @@
         <v>45370</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
         <v>45710</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>45352</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45352,7 +45352,7 @@
         <v>44897</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45425,7 +45425,7 @@
         <v>45202</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45498,7 +45498,7 @@
         <v>44881</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45571,7 +45571,7 @@
         <v>45156</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45644,7 +45644,7 @@
         <v>45898</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>45369</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45790,7 +45790,7 @@
         <v>44673</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45629</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45936,7 +45936,7 @@
         <v>45281</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46009,7 +46009,7 @@
         <v>45358</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46082,7 +46082,7 @@
         <v>45134</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46155,7 +46155,7 @@
         <v>45099</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46228,7 +46228,7 @@
         <v>45474</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46306,7 +46306,7 @@
         <v>45569</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>45415</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>46295</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46525,7 +46525,7 @@
         <v>46294</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45264</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46671,7 +46671,7 @@
         <v>46294</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46744,7 +46744,7 @@
         <v>45188</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45093</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46890,7 +46890,7 @@
         <v>44869</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46963,7 +46963,7 @@
         <v>44589</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47036,7 +47036,7 @@
         <v>45030</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47109,7 +47109,7 @@
         <v>45379</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>45475</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47255,7 +47255,7 @@
         <v>44652</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>45274</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47401,7 +47401,7 @@
         <v>46297</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>45370</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>44888</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47620,7 +47620,7 @@
         <v>45092</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45359</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47766,7 +47766,7 @@
         <v>45359</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         <v>45763</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47912,7 +47912,7 @@
         <v>45763</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>46296</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48058,7 +48058,7 @@
         <v>45763</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48131,7 +48131,7 @@
         <v>45490</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48204,7 +48204,7 @@
         <v>45077</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48277,7 +48277,7 @@
         <v>45534</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48350,7 +48350,7 @@
         <v>44924</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48423,7 +48423,7 @@
         <v>45631</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>45251</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48569,7 +48569,7 @@
         <v>45119</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45565</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48715,7 +48715,7 @@
         <v>45332</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48788,7 +48788,7 @@
         <v>45210</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48861,7 +48861,7 @@
         <v>44897</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48934,7 +48934,7 @@
         <v>45219</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49007,7 +49007,7 @@
         <v>45299</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49080,7 +49080,7 @@
         <v>45490</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49153,7 +49153,7 @@
         <v>45147</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49226,7 +49226,7 @@
         <v>45261</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49299,7 +49299,7 @@
         <v>45474</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49372,7 +49372,7 @@
         <v>45611</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49445,7 +49445,7 @@
         <v>45093</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49518,7 +49518,7 @@
         <v>45688</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49591,7 +49591,7 @@
         <v>44936</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49664,7 +49664,7 @@
         <v>44603</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49737,7 +49737,7 @@
         <v>45147</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49810,7 +49810,7 @@
         <v>45740</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49883,7 +49883,7 @@
         <v>44720</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49956,7 +49956,7 @@
         <v>44579</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50034,7 +50034,7 @@
         <v>44973</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50107,7 +50107,7 @@
         <v>45474</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50185,7 +50185,7 @@
         <v>44603</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50258,7 +50258,7 @@
         <v>45306</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50331,7 +50331,7 @@
         <v>44596</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50404,7 +50404,7 @@
         <v>44790</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50477,7 +50477,7 @@
         <v>45646</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>44993</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50623,7 +50623,7 @@
         <v>45572</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50696,7 +50696,7 @@
         <v>45377</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50774,7 +50774,7 @@
         <v>45254</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50847,7 +50847,7 @@
         <v>45713</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50920,7 +50920,7 @@
         <v>45056</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50993,7 +50993,7 @@
         <v>45534</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51066,7 +51066,7 @@
         <v>44950</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51139,7 +51139,7 @@
         <v>45763</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51212,7 +51212,7 @@
         <v>45779</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51285,7 +51285,7 @@
         <v>45784</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51358,7 +51358,7 @@
         <v>44586</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51431,7 +51431,7 @@
         <v>45443</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51504,7 +51504,7 @@
         <v>45784</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51577,7 +51577,7 @@
         <v>45418</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51648,7 +51648,7 @@
         <v>44088</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51721,7 +51721,7 @@
         <v>44711</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51794,7 +51794,7 @@
         <v>44966</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51872,7 +51872,7 @@
         <v>45343</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51945,7 +51945,7 @@
         <v>44966</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52023,7 +52023,7 @@
         <v>45785</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52096,7 +52096,7 @@
         <v>45839</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52174,7 +52174,7 @@
         <v>45841</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52247,7 +52247,7 @@
         <v>45705</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52320,7 +52320,7 @@
         <v>45261</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52393,7 +52393,7 @@
         <v>45022</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52466,7 +52466,7 @@
         <v>46042</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52539,7 +52539,7 @@
         <v>46107</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52612,7 +52612,7 @@
         <v>46132</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52685,7 +52685,7 @@
         <v>46258</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>

--- a/Översikt MARK.xlsx
+++ b/Översikt MARK.xlsx
@@ -601,7 +601,7 @@
         <v>45497</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45617</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45222</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>45137</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>45348</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>45285</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>44482</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>45001</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>46006</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>45973</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>45638</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>45342</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>46001</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>45154</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>45137</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>46273</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45618</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>44950</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>45673</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>46266</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>44792</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>44846</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>46027</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>45896</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>45792</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45091</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>45412</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45191</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>45306</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>45169</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>45841</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>45810</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>45271</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>46203</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>45134</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>45324</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>45849</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>46233</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>46268</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>45936</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>45288</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>45596</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>45751</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>44908</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         <v>45786</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>46048</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>46107</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>44881</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>44474</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>44843</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>44531</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>44750</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>44518</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>44764</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>44523</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>44720</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>44696</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>44764</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>44607</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>44811</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>44714</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>44722</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>44510</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>44816</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>44474</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>44684</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>44725</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>44874</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>44564</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>44564</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>44696</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>44615</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>44733</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44725</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>44609</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>44609</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>44580</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>44840</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>44497</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>44533</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>44680</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         <v>44784</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         <v>44699</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>44473</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>44491</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>44652</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>44781</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         <v>44571</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>44473</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>44473</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>44539</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>44622</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>44725</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44692</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>45342</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>44982</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>45475</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44902</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44585</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>45359</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
         <v>45568</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
         <v>44631</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>45030</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>44630</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>45093</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>45106</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>45093</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>45681</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
         <v>44937</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>44632</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10255,7 +10255,7 @@
         <v>45684</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>45183</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>44715</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>45428</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>44599</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>45745</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>45434</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>45443</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>45713</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>46000</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>45798</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
         <v>45672</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>45294</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         <v>45855</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11287,7 +11287,7 @@
         <v>45855</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>44473</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>45376</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>46007</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>46006</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>46006</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>45373</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>44607</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>46008</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>45631</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>45059</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>46009</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>45724</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>46013</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>45137</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>46013</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         <v>44810</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
         <v>45721</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>45611</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>45884</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>45724</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>45022</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>45707</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>45714</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>45714</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>45713</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>45839</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>45238</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>45693</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>45709</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>45691</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>44798</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         <v>45406</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>45888</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>44935</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13852,7 +13852,7 @@
         <v>45888</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>45889</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45891</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>45189</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>45895</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>45358</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>45896</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>44987</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>45604</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>45896</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>45896</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>45332</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>45332</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14801,7 +14801,7 @@
         <v>46030</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>45898</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>46030</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>45897</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         <v>46034</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>45135</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>45901</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>45604</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>46034</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>46034</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>46037</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>46037</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         <v>44474</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>44950</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>45016</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15896,7 +15896,7 @@
         <v>46037</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15969,7 +15969,7 @@
         <v>46037</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>46038</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>45905</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>45231</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>46038</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>45422</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>45909</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>45792</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>45792</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>44610</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>44971</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>45624</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16850,7 +16850,7 @@
         <v>45624</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16923,7 +16923,7 @@
         <v>44734</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>46048</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>45587</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>46048</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>46048</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17288,7 +17288,7 @@
         <v>46046</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>45799</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>46048</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>45916</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>45799</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>44982</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>45343</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17804,7 +17804,7 @@
         <v>45244</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>45805</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>45807</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>44760</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>45751</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>45923</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>45923</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>44762</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18388,7 +18388,7 @@
         <v>46055</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>45925</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>45925</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>45925</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>45925</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>46052</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>46055</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18904,7 +18904,7 @@
         <v>45925</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>45925</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>46056</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>45924</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>46057</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>46056</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>46058</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>44973</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>46062</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>45931</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>45244</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>46064</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>44574</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>45030</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>45937</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>45937</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
         <v>45937</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>45261</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>44588</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>44588</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20379,7 +20379,7 @@
         <v>45922</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20452,7 +20452,7 @@
         <v>45611</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>45922</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20598,7 +20598,7 @@
         <v>45943</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20671,7 +20671,7 @@
         <v>45355</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20744,7 +20744,7 @@
         <v>44896</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20817,7 +20817,7 @@
         <v>45943</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>45397</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20963,7 +20963,7 @@
         <v>44580</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21036,7 +21036,7 @@
         <v>45699</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21109,7 +21109,7 @@
         <v>46084</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
         <v>45953</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>46084</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>46084</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21401,7 +21401,7 @@
         <v>45953</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>45750</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>46045</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>45471</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>46084</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>46085</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>45959</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>45959</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21990,7 +21990,7 @@
         <v>45098</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22063,7 +22063,7 @@
         <v>45098</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>45631</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22209,7 +22209,7 @@
         <v>45183</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22282,7 +22282,7 @@
         <v>44685</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22355,7 +22355,7 @@
         <v>45686</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>45574</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>45212</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>46092</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22647,7 +22647,7 @@
         <v>45965</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>45964</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22793,7 +22793,7 @@
         <v>44882</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22866,7 +22866,7 @@
         <v>46097</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>46100</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23012,7 +23012,7 @@
         <v>45397</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>45978</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>45819</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>45978</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23304,7 +23304,7 @@
         <v>45629</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23377,7 +23377,7 @@
         <v>45751</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>45281</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>45749</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23596,7 +23596,7 @@
         <v>45980</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23669,7 +23669,7 @@
         <v>45818</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>45021</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         <v>45104</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>45982</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23961,7 +23961,7 @@
         <v>45637</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24034,7 +24034,7 @@
         <v>45775</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
         <v>45986</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>46114</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24253,7 +24253,7 @@
         <v>44615</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>45202</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>44982</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>45721</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24545,7 +24545,7 @@
         <v>45719</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>45716</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>45397</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>45743</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24842,7 +24842,7 @@
         <v>45743</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>45737</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>44764</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>45160</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25134,7 +25134,7 @@
         <v>45728</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>45911</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25280,7 +25280,7 @@
         <v>45490</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>45490</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>45490</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>45999</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>45743</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>45826</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25723,7 +25723,7 @@
         <v>45737</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>45740</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25869,7 +25869,7 @@
         <v>45743</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>45996</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26015,7 +26015,7 @@
         <v>46127</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26088,7 +26088,7 @@
         <v>45741</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26166,7 +26166,7 @@
         <v>46000</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26239,7 +26239,7 @@
         <v>46001</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26312,7 +26312,7 @@
         <v>46001</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26385,7 +26385,7 @@
         <v>46000</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26458,7 +26458,7 @@
         <v>45121</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26531,7 +26531,7 @@
         <v>45831</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>46000</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26677,7 +26677,7 @@
         <v>45455</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>45091</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>45833</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>44994</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26969,7 +26969,7 @@
         <v>45833</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>46134</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>44715</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>45343</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27261,7 +27261,7 @@
         <v>45834</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>45197</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27407,7 +27407,7 @@
         <v>45356</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27480,7 +27480,7 @@
         <v>45356</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>45825</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>45838</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27699,7 +27699,7 @@
         <v>45839</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27777,7 +27777,7 @@
         <v>45838</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27850,7 +27850,7 @@
         <v>45637</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27923,7 +27923,7 @@
         <v>45841</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27996,7 +27996,7 @@
         <v>44501</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28069,7 +28069,7 @@
         <v>45819</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28142,7 +28142,7 @@
         <v>45791</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28215,7 +28215,7 @@
         <v>45841</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28288,7 +28288,7 @@
         <v>45322</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28361,7 +28361,7 @@
         <v>45841</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>45841</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28507,7 +28507,7 @@
         <v>45841</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28580,7 +28580,7 @@
         <v>45841</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28653,7 +28653,7 @@
         <v>45450</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28726,7 +28726,7 @@
         <v>45370</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28799,7 +28799,7 @@
         <v>44624</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>45540</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>45281</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29018,7 +29018,7 @@
         <v>45188</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29091,7 +29091,7 @@
         <v>45477</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29164,7 +29164,7 @@
         <v>45845</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29237,7 +29237,7 @@
         <v>45789</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29310,7 +29310,7 @@
         <v>45631</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29383,7 +29383,7 @@
         <v>45847</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29456,7 +29456,7 @@
         <v>45595</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29529,7 +29529,7 @@
         <v>45845</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29602,7 +29602,7 @@
         <v>45642</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29675,7 +29675,7 @@
         <v>45849</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29748,7 +29748,7 @@
         <v>45684</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
         <v>45063</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>45817</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29967,7 +29967,7 @@
         <v>44978</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30040,7 +30040,7 @@
         <v>45335</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30113,7 +30113,7 @@
         <v>45807</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30186,7 +30186,7 @@
         <v>44971</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30259,7 +30259,7 @@
         <v>45734</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>45855</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30405,7 +30405,7 @@
         <v>45855</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>45854</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30551,7 +30551,7 @@
         <v>44694</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30624,7 +30624,7 @@
         <v>45855</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30697,7 +30697,7 @@
         <v>44531</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30770,7 +30770,7 @@
         <v>45137</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30843,7 +30843,7 @@
         <v>45855</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30916,7 +30916,7 @@
         <v>45075</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30989,7 +30989,7 @@
         <v>45629</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31062,7 +31062,7 @@
         <v>44648</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31135,7 +31135,7 @@
         <v>45811</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31208,7 +31208,7 @@
         <v>44834</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31281,7 +31281,7 @@
         <v>45838</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31354,7 +31354,7 @@
         <v>45868</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31427,7 +31427,7 @@
         <v>44928</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>44838</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31573,7 +31573,7 @@
         <v>45106</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31651,7 +31651,7 @@
         <v>45106</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31729,7 +31729,7 @@
         <v>44713</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31802,7 +31802,7 @@
         <v>45680</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>45862</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31948,7 +31948,7 @@
         <v>45755</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32021,7 +32021,7 @@
         <v>45755</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32094,7 +32094,7 @@
         <v>45755</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32167,7 +32167,7 @@
         <v>45867</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>45349</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32313,7 +32313,7 @@
         <v>45918</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32386,7 +32386,7 @@
         <v>45867</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32459,7 +32459,7 @@
         <v>44935</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32532,7 +32532,7 @@
         <v>45484</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32605,7 +32605,7 @@
         <v>45224</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32678,7 +32678,7 @@
         <v>45568</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32751,7 +32751,7 @@
         <v>45124</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32824,7 +32824,7 @@
         <v>45127</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32897,7 +32897,7 @@
         <v>45194</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32970,7 +32970,7 @@
         <v>44804</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33043,7 +33043,7 @@
         <v>44901</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33116,7 +33116,7 @@
         <v>44928</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33189,7 +33189,7 @@
         <v>45272</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33262,7 +33262,7 @@
         <v>45076</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>44869</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33408,7 +33408,7 @@
         <v>45264</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33481,7 +33481,7 @@
         <v>45264</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33554,7 +33554,7 @@
         <v>44901</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33627,7 +33627,7 @@
         <v>45580</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33700,7 +33700,7 @@
         <v>44714</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33773,7 +33773,7 @@
         <v>44998</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>45821</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>46146</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33992,7 +33992,7 @@
         <v>44950</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>46147</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34143,7 +34143,7 @@
         <v>45029</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>45029</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34289,7 +34289,7 @@
         <v>45324</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>45555</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34435,7 +34435,7 @@
         <v>45419</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34508,7 +34508,7 @@
         <v>44944</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>45358</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34654,7 +34654,7 @@
         <v>44904</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>45872</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34800,7 +34800,7 @@
         <v>44869</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34873,7 +34873,7 @@
         <v>45316</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34946,7 +34946,7 @@
         <v>46153</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>45137</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35092,7 +35092,7 @@
         <v>45209</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35165,7 +35165,7 @@
         <v>45442</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>44712</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35311,7 +35311,7 @@
         <v>45268</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>45414</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35462,7 +35462,7 @@
         <v>45875</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>45288</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35608,7 +35608,7 @@
         <v>45392</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35681,7 +35681,7 @@
         <v>45490</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35754,7 +35754,7 @@
         <v>45750</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35827,7 +35827,7 @@
         <v>46120</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35900,7 +35900,7 @@
         <v>45342</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>45875</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36046,7 +36046,7 @@
         <v>45776</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36119,7 +36119,7 @@
         <v>45875</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36192,7 +36192,7 @@
         <v>45875</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36265,7 +36265,7 @@
         <v>46162</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36338,7 +36338,7 @@
         <v>45629</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36411,7 +36411,7 @@
         <v>45432</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36489,7 +36489,7 @@
         <v>45419</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36562,7 +36562,7 @@
         <v>44768</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36635,7 +36635,7 @@
         <v>45342</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36708,7 +36708,7 @@
         <v>46165</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36786,7 +36786,7 @@
         <v>45533</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36859,7 +36859,7 @@
         <v>45140</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36932,7 +36932,7 @@
         <v>45667</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37005,7 +37005,7 @@
         <v>45776</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>45356</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37151,7 +37151,7 @@
         <v>45880</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37224,7 +37224,7 @@
         <v>46169</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37297,7 +37297,7 @@
         <v>46177</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37370,7 +37370,7 @@
         <v>45855</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37443,7 +37443,7 @@
         <v>45884</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37516,7 +37516,7 @@
         <v>45134</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37589,7 +37589,7 @@
         <v>44803</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37662,7 +37662,7 @@
         <v>44489</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37735,7 +37735,7 @@
         <v>44971</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37808,7 +37808,7 @@
         <v>45260</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37881,7 +37881,7 @@
         <v>46182</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37954,7 +37954,7 @@
         <v>46181</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38027,7 +38027,7 @@
         <v>44834</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38100,7 +38100,7 @@
         <v>44806</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38173,7 +38173,7 @@
         <v>45154</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38246,7 +38246,7 @@
         <v>44896</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38319,7 +38319,7 @@
         <v>46190</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38392,7 +38392,7 @@
         <v>46189</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38465,7 +38465,7 @@
         <v>46190</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38538,7 +38538,7 @@
         <v>45552</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38611,7 +38611,7 @@
         <v>46191</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38684,7 +38684,7 @@
         <v>46195</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38757,7 +38757,7 @@
         <v>46195</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38830,7 +38830,7 @@
         <v>45076</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38903,7 +38903,7 @@
         <v>46195</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38976,7 +38976,7 @@
         <v>45137</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39049,7 +39049,7 @@
         <v>46195</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39122,7 +39122,7 @@
         <v>45264</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39195,7 +39195,7 @@
         <v>46195</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39268,7 +39268,7 @@
         <v>46195</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39341,7 +39341,7 @@
         <v>44952</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39414,7 +39414,7 @@
         <v>46198</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         <v>45443</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39560,7 +39560,7 @@
         <v>45526</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39633,7 +39633,7 @@
         <v>46199</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39711,7 +39711,7 @@
         <v>45236</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>45154</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39857,7 +39857,7 @@
         <v>44660</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39930,7 +39930,7 @@
         <v>45301</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40003,7 +40003,7 @@
         <v>46203</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40076,7 +40076,7 @@
         <v>44588</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40149,7 +40149,7 @@
         <v>44732</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40222,7 +40222,7 @@
         <v>45021</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40295,7 +40295,7 @@
         <v>46204</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40368,7 +40368,7 @@
         <v>45275</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
         <v>45275</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40514,7 +40514,7 @@
         <v>44978</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45386</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40660,7 +40660,7 @@
         <v>46211</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40733,7 +40733,7 @@
         <v>44963</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40806,7 +40806,7 @@
         <v>46216</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40879,7 +40879,7 @@
         <v>46259</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>44902</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41025,7 +41025,7 @@
         <v>45379</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41098,7 +41098,7 @@
         <v>46195</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41171,7 +41171,7 @@
         <v>46195</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41244,7 +41244,7 @@
         <v>45251</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41317,7 +41317,7 @@
         <v>45251</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41390,7 +41390,7 @@
         <v>45135</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41463,7 +41463,7 @@
         <v>45251</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>45686</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41609,7 +41609,7 @@
         <v>45119</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41682,7 +41682,7 @@
         <v>44813</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41755,7 +41755,7 @@
         <v>45518</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41833,7 +41833,7 @@
         <v>46269</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41906,7 +41906,7 @@
         <v>44909</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>46273</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42052,7 +42052,7 @@
         <v>46273</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42125,7 +42125,7 @@
         <v>45672</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42198,7 +42198,7 @@
         <v>45672</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42271,7 +42271,7 @@
         <v>44637</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42344,7 +42344,7 @@
         <v>45230</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42417,7 +42417,7 @@
         <v>46274</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42490,7 +42490,7 @@
         <v>46231</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42568,7 +42568,7 @@
         <v>46233</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42641,7 +42641,7 @@
         <v>45210</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42714,7 +42714,7 @@
         <v>45218</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42787,7 +42787,7 @@
         <v>46275</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42860,7 +42860,7 @@
         <v>45204</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42933,7 +42933,7 @@
         <v>46274</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43006,7 +43006,7 @@
         <v>46233</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43079,7 +43079,7 @@
         <v>46232</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43157,7 +43157,7 @@
         <v>46233</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43230,7 +43230,7 @@
         <v>46276</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43303,7 +43303,7 @@
         <v>46233</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43376,7 +43376,7 @@
         <v>45233</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43454,7 +43454,7 @@
         <v>46279</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43527,7 +43527,7 @@
         <v>45233</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>46237</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43673,7 +43673,7 @@
         <v>46237</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43746,7 +43746,7 @@
         <v>45107</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43819,7 +43819,7 @@
         <v>45225</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43892,7 +43892,7 @@
         <v>45378</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43965,7 +43965,7 @@
         <v>45523</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44038,7 +44038,7 @@
         <v>46237</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44111,7 +44111,7 @@
         <v>46237</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44184,7 +44184,7 @@
         <v>44813</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44257,7 +44257,7 @@
         <v>46283</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44330,7 +44330,7 @@
         <v>46283</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44403,7 +44403,7 @@
         <v>46282</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44476,7 +44476,7 @@
         <v>46281</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44549,7 +44549,7 @@
         <v>44531</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44622,7 +44622,7 @@
         <v>46286</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>45254</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44768,7 +44768,7 @@
         <v>44994</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>45373</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44914,7 +44914,7 @@
         <v>45070</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44987,7 +44987,7 @@
         <v>45264</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45060,7 +45060,7 @@
         <v>44588</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45133,7 +45133,7 @@
         <v>45370</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
         <v>45710</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>45352</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45352,7 +45352,7 @@
         <v>44897</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45425,7 +45425,7 @@
         <v>45202</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45498,7 +45498,7 @@
         <v>44881</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45571,7 +45571,7 @@
         <v>45156</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45644,7 +45644,7 @@
         <v>45898</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>45369</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45790,7 +45790,7 @@
         <v>44673</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45629</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45936,7 +45936,7 @@
         <v>45281</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46009,7 +46009,7 @@
         <v>45358</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46082,7 +46082,7 @@
         <v>45134</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46155,7 +46155,7 @@
         <v>45099</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46228,7 +46228,7 @@
         <v>45474</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46306,7 +46306,7 @@
         <v>45569</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>45415</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>46295</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46525,7 +46525,7 @@
         <v>46294</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45264</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46671,7 +46671,7 @@
         <v>46294</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46744,7 +46744,7 @@
         <v>45188</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45093</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46890,7 +46890,7 @@
         <v>44869</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46963,7 +46963,7 @@
         <v>44589</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47036,7 +47036,7 @@
         <v>45030</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47109,7 +47109,7 @@
         <v>45379</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>45475</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47255,7 +47255,7 @@
         <v>44652</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>45274</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47401,7 +47401,7 @@
         <v>46297</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>45370</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>44888</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47620,7 +47620,7 @@
         <v>45092</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45359</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47766,7 +47766,7 @@
         <v>45359</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         <v>45763</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47912,7 +47912,7 @@
         <v>45763</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>46296</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48058,7 +48058,7 @@
         <v>45763</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48131,7 +48131,7 @@
         <v>45490</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48204,7 +48204,7 @@
         <v>45077</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48277,7 +48277,7 @@
         <v>45534</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48350,7 +48350,7 @@
         <v>44924</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48423,7 +48423,7 @@
         <v>45631</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>45251</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48569,7 +48569,7 @@
         <v>45119</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45565</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48715,7 +48715,7 @@
         <v>45332</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48788,7 +48788,7 @@
         <v>45210</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48861,7 +48861,7 @@
         <v>44897</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48934,7 +48934,7 @@
         <v>45219</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49007,7 +49007,7 @@
         <v>45299</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49080,7 +49080,7 @@
         <v>45490</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49153,7 +49153,7 @@
         <v>45147</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49226,7 +49226,7 @@
         <v>45261</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49299,7 +49299,7 @@
         <v>45474</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49372,7 +49372,7 @@
         <v>45611</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49445,7 +49445,7 @@
         <v>45093</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49518,7 +49518,7 @@
         <v>45688</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49591,7 +49591,7 @@
         <v>44936</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49664,7 +49664,7 @@
         <v>44603</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49737,7 +49737,7 @@
         <v>45147</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49810,7 +49810,7 @@
         <v>45740</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49883,7 +49883,7 @@
         <v>44720</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49956,7 +49956,7 @@
         <v>44579</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50034,7 +50034,7 @@
         <v>44973</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50107,7 +50107,7 @@
         <v>45474</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50185,7 +50185,7 @@
         <v>44603</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50258,7 +50258,7 @@
         <v>45306</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50331,7 +50331,7 @@
         <v>44596</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50404,7 +50404,7 @@
         <v>44790</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50477,7 +50477,7 @@
         <v>45646</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>44993</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50623,7 +50623,7 @@
         <v>45572</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50696,7 +50696,7 @@
         <v>45377</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50774,7 +50774,7 @@
         <v>45254</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50847,7 +50847,7 @@
         <v>45713</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50920,7 +50920,7 @@
         <v>45056</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50993,7 +50993,7 @@
         <v>45534</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51066,7 +51066,7 @@
         <v>44950</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51139,7 +51139,7 @@
         <v>45763</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51212,7 +51212,7 @@
         <v>45779</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51285,7 +51285,7 @@
         <v>45784</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51358,7 +51358,7 @@
         <v>44586</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51431,7 +51431,7 @@
         <v>45443</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51504,7 +51504,7 @@
         <v>45784</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51577,7 +51577,7 @@
         <v>45418</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51648,7 +51648,7 @@
         <v>44088</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51721,7 +51721,7 @@
         <v>44711</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51794,7 +51794,7 @@
         <v>44966</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51872,7 +51872,7 @@
         <v>45343</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51945,7 +51945,7 @@
         <v>44966</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52023,7 +52023,7 @@
         <v>45785</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52096,7 +52096,7 @@
         <v>45839</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52174,7 +52174,7 @@
         <v>45841</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52247,7 +52247,7 @@
         <v>45705</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52320,7 +52320,7 @@
         <v>45261</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52393,7 +52393,7 @@
         <v>45022</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52466,7 +52466,7 @@
         <v>46042</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52539,7 +52539,7 @@
         <v>46107</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52612,7 +52612,7 @@
         <v>46132</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52685,7 +52685,7 @@
         <v>46258</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>

--- a/Översikt MARK.xlsx
+++ b/Översikt MARK.xlsx
@@ -601,7 +601,7 @@
         <v>45497</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45617</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45137</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>45222</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>45348</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>45285</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>44482</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>45342</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>45154</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>45673</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>44950</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45638</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>45618</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>45973</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>45137</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>46001</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>45001</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>46006</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>46273</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>46266</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>44792</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>44846</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>45091</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>45751</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>45412</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>45271</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>45896</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>44908</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>45191</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>45792</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>45169</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>45324</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>45134</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>45596</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>45288</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>45306</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>45810</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>46027</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>45841</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>46203</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>45849</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>46233</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>46268</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>45936</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         <v>45786</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>46048</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>46107</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>44881</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>44843</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>44531</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>44764</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>44750</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>44518</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>44523</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>44720</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>44696</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>44764</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>44607</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>44811</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>44714</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>44722</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>44510</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>44816</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>44684</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>44725</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>44874</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>44564</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>44652</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>44781</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>44564</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>44571</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>44533</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>44696</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44491</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>44680</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         <v>44615</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         <v>44784</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         <v>44733</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         <v>44725</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>44609</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>44609</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         <v>44580</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         <v>44497</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>44699</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>44840</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>44539</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>44622</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         <v>44725</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>45763</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>45763</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>45204</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>45154</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>44950</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44712</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>45244</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>45534</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44692</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>45135</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>45137</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>45106</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>45419</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>44713</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>44714</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>44637</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>45484</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>45016</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>45260</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>45414</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>45342</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>45745</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>45406</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>45093</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>44803</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>45740</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>44588</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>45233</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
         <v>45218</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>45160</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         <v>45056</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         <v>45397</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>45156</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>44882</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>44768</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>45471</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         <v>45376</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>45450</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>45233</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>45526</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>45093</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>45202</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>45386</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>44902</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         <v>45021</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>45104</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         <v>45210</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>44834</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>45202</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>44790</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>45121</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>45611</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>45611</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
         <v>45342</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>44489</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>45210</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>44813</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>44813</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>45254</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12956,7 +12956,7 @@
         <v>45415</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>45288</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>45212</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>45335</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         <v>45358</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         <v>45680</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>44798</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>45355</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
         <v>45370</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>45093</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>45264</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>45093</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>45352</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         <v>45322</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>45884</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>45490</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>45490</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>45490</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>45474</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>45533</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>45373</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>45147</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>45134</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>45604</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>44632</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>45884</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         <v>44994</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>45030</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>44579</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         <v>45059</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>45219</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>44810</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>45281</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>45135</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>45119</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>45888</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>45888</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         <v>45342</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>45477</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>45855</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15896,7 +15896,7 @@
         <v>45855</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15969,7 +15969,7 @@
         <v>45855</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>45798</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>45359</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>45359</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>44982</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>44952</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>45092</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>45077</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>45889</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         <v>45378</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>44971</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>45891</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>45896</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>45895</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>45896</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>45896</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>45897</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>45275</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>45275</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>45898</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>45332</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>45343</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>45349</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17648,7 +17648,7 @@
         <v>45490</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17721,7 +17721,7 @@
         <v>45358</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>44978</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>45631</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17940,7 +17940,7 @@
         <v>45629</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18013,7 +18013,7 @@
         <v>44936</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18086,7 +18086,7 @@
         <v>45901</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18159,7 +18159,7 @@
         <v>44971</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
         <v>45251</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>45251</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>45523</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>45301</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>45905</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>44896</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>44531</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>45909</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>45518</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>45106</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>45106</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>45629</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>45779</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19196,7 +19196,7 @@
         <v>45784</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>45443</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>45784</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>45916</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>45021</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>45443</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>44580</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>45443</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>44603</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>44924</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>44973</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         <v>44586</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>45490</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20150,7 +20150,7 @@
         <v>45490</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>45667</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>45672</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>44574</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>44607</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>45713</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20588,7 +20588,7 @@
         <v>45629</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20661,7 +20661,7 @@
         <v>45418</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>45434</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>44599</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20880,7 +20880,7 @@
         <v>45359</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>44585</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>45924</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>45356</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21177,7 +21177,7 @@
         <v>45356</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>45923</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21323,7 +21323,7 @@
         <v>45923</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>45555</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>45925</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21542,7 +21542,7 @@
         <v>45925</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21615,7 +21615,7 @@
         <v>45379</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21688,7 +21688,7 @@
         <v>44902</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         <v>45925</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>45332</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>45264</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>45264</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22053,7 +22053,7 @@
         <v>45188</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44896</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>45569</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>45370</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>45925</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22418,7 +22418,7 @@
         <v>45925</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22491,7 +22491,7 @@
         <v>45925</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22564,7 +22564,7 @@
         <v>44950</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>45631</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>45261</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>45565</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>45724</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22934,7 +22934,7 @@
         <v>45792</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23007,7 +23007,7 @@
         <v>45792</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>45721</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23153,7 +23153,7 @@
         <v>44588</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         <v>44971</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>45189</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>45587</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
         <v>45534</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23518,7 +23518,7 @@
         <v>44950</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         <v>44660</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>45931</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>44648</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>44596</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23883,7 +23883,7 @@
         <v>45419</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>44673</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>44732</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>45261</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24175,7 +24175,7 @@
         <v>45799</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24248,7 +24248,7 @@
         <v>44589</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>45799</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         <v>44982</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>45225</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24540,7 +24540,7 @@
         <v>45937</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24613,7 +24613,7 @@
         <v>45392</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>45076</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>45268</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>45763</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>45937</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>45805</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25051,7 +25051,7 @@
         <v>45194</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>45236</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
         <v>44993</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25270,7 +25270,7 @@
         <v>44897</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25343,7 +25343,7 @@
         <v>45070</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>45098</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>45098</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25562,7 +25562,7 @@
         <v>45611</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25635,7 +25635,7 @@
         <v>45807</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25708,7 +25708,7 @@
         <v>45943</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25781,7 +25781,7 @@
         <v>45943</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>45572</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25927,7 +25927,7 @@
         <v>45922</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>45231</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>45922</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>44734</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>45075</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>45274</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>44834</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>44624</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>45294</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>44685</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26657,7 +26657,7 @@
         <v>45749</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         <v>45397</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>45818</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>45751</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>45574</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>44909</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>45713</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>45819</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27241,7 +27241,7 @@
         <v>45775</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27314,7 +27314,7 @@
         <v>45154</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>45624</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         <v>45624</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>45826</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27611,7 +27611,7 @@
         <v>45568</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>45740</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>45721</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>45741</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>45183</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>45743</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>45728</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>45743</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28200,7 +28200,7 @@
         <v>45716</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>45743</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>45743</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28419,7 +28419,7 @@
         <v>44838</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28492,7 +28492,7 @@
         <v>45831</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28565,7 +28565,7 @@
         <v>45137</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>45953</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>45953</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>45959</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28857,7 +28857,7 @@
         <v>45959</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>45833</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29003,7 +29003,7 @@
         <v>45834</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         <v>45244</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>45833</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29222,7 +29222,7 @@
         <v>45672</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>45672</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>45838</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>44973</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>45964</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>45838</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>44715</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>44881</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29806,7 +29806,7 @@
         <v>45422</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>45119</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29952,7 +29952,7 @@
         <v>45839</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30030,7 +30030,7 @@
         <v>45646</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>45965</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30176,7 +30176,7 @@
         <v>45841</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>45137</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30322,7 +30322,7 @@
         <v>45474</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30400,7 +30400,7 @@
         <v>45841</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30473,7 +30473,7 @@
         <v>45841</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30546,7 +30546,7 @@
         <v>45841</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>45841</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30692,7 +30692,7 @@
         <v>45841</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30765,7 +30765,7 @@
         <v>45684</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30843,7 +30843,7 @@
         <v>45631</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30916,7 +30916,7 @@
         <v>45629</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30989,7 +30989,7 @@
         <v>44720</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31062,7 +31062,7 @@
         <v>45681</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31135,7 +31135,7 @@
         <v>45281</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31208,7 +31208,7 @@
         <v>45845</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31281,7 +31281,7 @@
         <v>45845</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31354,7 +31354,7 @@
         <v>45099</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31427,7 +31427,7 @@
         <v>45188</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>44694</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31573,7 +31573,7 @@
         <v>45789</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31646,7 +31646,7 @@
         <v>45030</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31719,7 +31719,7 @@
         <v>45847</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31792,7 +31792,7 @@
         <v>45631</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>45642</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31938,7 +31938,7 @@
         <v>45734</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32011,7 +32011,7 @@
         <v>45807</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32084,7 +32084,7 @@
         <v>45849</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32157,7 +32157,7 @@
         <v>44531</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32230,7 +32230,7 @@
         <v>45854</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32303,7 +32303,7 @@
         <v>45030</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32376,7 +32376,7 @@
         <v>45978</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         <v>45838</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32522,7 +32522,7 @@
         <v>45251</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32595,7 +32595,7 @@
         <v>45855</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32668,7 +32668,7 @@
         <v>45855</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>45855</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32814,7 +32814,7 @@
         <v>45855</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>44762</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32960,7 +32960,7 @@
         <v>45140</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33033,7 +33033,7 @@
         <v>45183</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>45299</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>45862</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33252,7 +33252,7 @@
         <v>45373</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33325,7 +33325,7 @@
         <v>44806</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33398,7 +33398,7 @@
         <v>45867</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>45978</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33544,7 +33544,7 @@
         <v>44935</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>45867</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33690,7 +33690,7 @@
         <v>45091</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33763,7 +33763,7 @@
         <v>44928</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33836,7 +33836,7 @@
         <v>45029</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33909,7 +33909,7 @@
         <v>45029</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>44901</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34055,7 +34055,7 @@
         <v>44904</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34128,7 +34128,7 @@
         <v>44869</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34201,7 +34201,7 @@
         <v>45324</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         <v>45358</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34347,7 +34347,7 @@
         <v>45750</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>44888</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>45209</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>45580</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34639,7 +34639,7 @@
         <v>45124</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>44944</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>44901</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34858,7 +34858,7 @@
         <v>45272</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>45379</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35004,7 +35004,7 @@
         <v>45127</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35077,7 +35077,7 @@
         <v>45637</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35150,7 +35150,7 @@
         <v>45076</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>45872</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35296,7 +35296,7 @@
         <v>44869</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35369,7 +35369,7 @@
         <v>45763</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35442,7 +35442,7 @@
         <v>45719</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35520,7 +35520,7 @@
         <v>44998</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35593,7 +35593,7 @@
         <v>45568</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>44804</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35739,7 +35739,7 @@
         <v>45316</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35812,7 +35812,7 @@
         <v>45980</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>45821</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35958,7 +35958,7 @@
         <v>45875</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36031,7 +36031,7 @@
         <v>45875</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36104,7 +36104,7 @@
         <v>45875</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36177,7 +36177,7 @@
         <v>45875</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36250,7 +36250,7 @@
         <v>45356</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36323,7 +36323,7 @@
         <v>45755</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36396,7 +36396,7 @@
         <v>45755</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36469,7 +36469,7 @@
         <v>45880</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36542,7 +36542,7 @@
         <v>44987</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36615,7 +36615,7 @@
         <v>45281</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36688,7 +36688,7 @@
         <v>45264</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36761,7 +36761,7 @@
         <v>45251</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>46097</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36907,7 +36907,7 @@
         <v>45982</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36980,7 +36980,7 @@
         <v>45750</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37053,7 +37053,7 @@
         <v>45684</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37126,7 +37126,7 @@
         <v>45022</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37199,7 +37199,7 @@
         <v>45107</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>45343</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37345,7 +37345,7 @@
         <v>45397</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>46100</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37491,7 +37491,7 @@
         <v>45254</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37564,7 +37564,7 @@
         <v>45751</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37637,7 +37637,7 @@
         <v>45230</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>45986</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37783,7 +37783,7 @@
         <v>45306</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37856,7 +37856,7 @@
         <v>45475</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37929,7 +37929,7 @@
         <v>45264</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38002,7 +38002,7 @@
         <v>45428</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38075,7 +38075,7 @@
         <v>45137</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>44928</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38221,7 +38221,7 @@
         <v>45552</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>44897</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38367,7 +38367,7 @@
         <v>44935</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38440,7 +38440,7 @@
         <v>45996</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38513,7 +38513,7 @@
         <v>44764</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38586,7 +38586,7 @@
         <v>45999</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>46000</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38732,7 +38732,7 @@
         <v>46000</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38805,7 +38805,7 @@
         <v>46127</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38878,7 +38878,7 @@
         <v>44610</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38951,7 +38951,7 @@
         <v>45432</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39029,7 +39029,7 @@
         <v>46000</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39102,7 +39102,7 @@
         <v>46001</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>46000</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39248,7 +39248,7 @@
         <v>44603</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39321,7 +39321,7 @@
         <v>46001</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39394,7 +39394,7 @@
         <v>45911</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39467,7 +39467,7 @@
         <v>44615</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39540,7 +39540,7 @@
         <v>46006</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>45369</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39686,7 +39686,7 @@
         <v>46006</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39759,7 +39759,7 @@
         <v>45475</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39832,7 +39832,7 @@
         <v>45455</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>46134</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39978,7 +39978,7 @@
         <v>44588</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40051,7 +40051,7 @@
         <v>44588</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40124,7 +40124,7 @@
         <v>45147</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40197,7 +40197,7 @@
         <v>46008</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>46007</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>45197</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>44937</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>46009</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40562,7 +40562,7 @@
         <v>45332</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40635,7 +40635,7 @@
         <v>45714</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>45238</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40781,7 +40781,7 @@
         <v>45839</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40859,7 +40859,7 @@
         <v>45709</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40932,7 +40932,7 @@
         <v>45595</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>46013</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41078,7 +41078,7 @@
         <v>46013</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41151,7 +41151,7 @@
         <v>45724</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41224,7 +41224,7 @@
         <v>45714</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41297,7 +41297,7 @@
         <v>45707</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41370,7 +41370,7 @@
         <v>45691</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41443,7 +41443,7 @@
         <v>45713</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41516,7 +41516,7 @@
         <v>45693</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41589,7 +41589,7 @@
         <v>45063</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>44760</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41735,7 +41735,7 @@
         <v>44631</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>46030</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41881,7 +41881,7 @@
         <v>45817</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>44994</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42027,7 +42027,7 @@
         <v>45791</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42100,7 +42100,7 @@
         <v>46034</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>46034</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>44501</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>44652</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42392,7 +42392,7 @@
         <v>46030</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42465,7 +42465,7 @@
         <v>46034</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>44715</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42611,7 +42611,7 @@
         <v>45604</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>44982</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42757,7 +42757,7 @@
         <v>45819</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>45688</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42903,7 +42903,7 @@
         <v>46037</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42976,7 +42976,7 @@
         <v>46038</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43054,7 +43054,7 @@
         <v>46037</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43127,7 +43127,7 @@
         <v>46037</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43200,7 +43200,7 @@
         <v>46037</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43273,7 +43273,7 @@
         <v>46038</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43346,7 +43346,7 @@
         <v>45868</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43419,7 +43419,7 @@
         <v>45637</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43492,7 +43492,7 @@
         <v>45811</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45825</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43638,7 +43638,7 @@
         <v>45755</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43711,7 +43711,7 @@
         <v>44630</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43789,7 +43789,7 @@
         <v>45918</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
         <v>44978</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43935,7 +43935,7 @@
         <v>45370</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44008,7 +44008,7 @@
         <v>45474</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44081,7 +44081,7 @@
         <v>46048</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44154,7 +44154,7 @@
         <v>45134</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44227,7 +44227,7 @@
         <v>45224</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44300,7 +44300,7 @@
         <v>46048</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44373,7 +44373,7 @@
         <v>46048</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>45540</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
         <v>46048</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44597,7 +44597,7 @@
         <v>45686</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44670,7 +44670,7 @@
         <v>46046</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44743,7 +44743,7 @@
         <v>45377</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44821,7 +44821,7 @@
         <v>45442</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44894,7 +44894,7 @@
         <v>46052</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44972,7 +44972,7 @@
         <v>46055</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45045,7 +45045,7 @@
         <v>46055</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45118,7 +45118,7 @@
         <v>46056</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45196,7 +45196,7 @@
         <v>46056</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>46058</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>46057</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45415,7 +45415,7 @@
         <v>46062</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45493,7 +45493,7 @@
         <v>46064</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45566,7 +45566,7 @@
         <v>46146</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45639,7 +45639,7 @@
         <v>46147</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45712,7 +45712,7 @@
         <v>46153</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45785,7 +45785,7 @@
         <v>45699</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45858,7 +45858,7 @@
         <v>46084</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>46045</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46004,7 +46004,7 @@
         <v>46084</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>46084</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46150,7 +46150,7 @@
         <v>46084</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46223,7 +46223,7 @@
         <v>46085</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46301,7 +46301,7 @@
         <v>45686</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46374,7 +46374,7 @@
         <v>45776</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46447,7 +46447,7 @@
         <v>46120</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>46092</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46593,7 +46593,7 @@
         <v>46162</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46666,7 +46666,7 @@
         <v>46165</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46744,7 +46744,7 @@
         <v>45776</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>46169</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46890,7 +46890,7 @@
         <v>46181</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46963,7 +46963,7 @@
         <v>46182</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47036,7 +47036,7 @@
         <v>46189</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47109,7 +47109,7 @@
         <v>46190</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>46191</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47255,7 +47255,7 @@
         <v>46195</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>46195</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47401,7 +47401,7 @@
         <v>46195</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>46195</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>46195</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47620,7 +47620,7 @@
         <v>46195</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>46199</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47771,7 +47771,7 @@
         <v>46198</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47844,7 +47844,7 @@
         <v>46203</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47917,7 +47917,7 @@
         <v>46204</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47990,7 +47990,7 @@
         <v>46211</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48063,7 +48063,7 @@
         <v>46216</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48136,7 +48136,7 @@
         <v>46195</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48209,7 +48209,7 @@
         <v>46195</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48282,7 +48282,7 @@
         <v>46269</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48355,7 +48355,7 @@
         <v>46273</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48428,7 +48428,7 @@
         <v>46231</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48506,7 +48506,7 @@
         <v>46274</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>46273</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48652,7 +48652,7 @@
         <v>46274</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48725,7 +48725,7 @@
         <v>46233</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48798,7 +48798,7 @@
         <v>46232</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48876,7 +48876,7 @@
         <v>46233</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48949,7 +48949,7 @@
         <v>46276</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49022,7 +49022,7 @@
         <v>46275</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49095,7 +49095,7 @@
         <v>46237</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49168,7 +49168,7 @@
         <v>46237</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49241,7 +49241,7 @@
         <v>46233</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49314,7 +49314,7 @@
         <v>46279</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49387,7 +49387,7 @@
         <v>46237</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>46237</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49533,7 +49533,7 @@
         <v>46233</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49606,7 +49606,7 @@
         <v>46282</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49679,7 +49679,7 @@
         <v>46281</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49752,7 +49752,7 @@
         <v>46283</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49825,7 +49825,7 @@
         <v>46286</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49898,7 +49898,7 @@
         <v>46283</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49971,7 +49971,7 @@
         <v>45710</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50044,7 +50044,7 @@
         <v>45898</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50117,7 +50117,7 @@
         <v>46294</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50190,7 +50190,7 @@
         <v>46294</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50263,7 +50263,7 @@
         <v>46296</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50336,7 +50336,7 @@
         <v>46295</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50409,7 +50409,7 @@
         <v>46114</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50482,7 +50482,7 @@
         <v>44869</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50555,7 +50555,7 @@
         <v>46297</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50628,7 +50628,7 @@
         <v>46259</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50701,7 +50701,7 @@
         <v>46302</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50772,7 +50772,7 @@
         <v>44088</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50845,7 +50845,7 @@
         <v>44711</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50918,7 +50918,7 @@
         <v>44966</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50996,7 +50996,7 @@
         <v>45343</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51069,7 +51069,7 @@
         <v>44966</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51147,7 +51147,7 @@
         <v>45785</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51220,7 +51220,7 @@
         <v>45839</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51298,7 +51298,7 @@
         <v>45841</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51371,7 +51371,7 @@
         <v>45705</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51444,7 +51444,7 @@
         <v>45261</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51517,7 +51517,7 @@
         <v>45022</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51590,7 +51590,7 @@
         <v>46042</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51663,7 +51663,7 @@
         <v>46107</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51736,7 +51736,7 @@
         <v>46132</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51809,7 +51809,7 @@
         <v>46258</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>

--- a/Översikt MARK.xlsx
+++ b/Översikt MARK.xlsx
@@ -601,7 +601,7 @@
         <v>45497</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45617</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45137</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>45222</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>45348</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>45285</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>44482</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>45342</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>45154</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>45673</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>44950</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45638</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>45618</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>45973</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>45137</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>46001</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>45001</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>46006</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>46273</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>46266</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>44792</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>44846</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>45091</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>45751</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>45412</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>45271</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>45896</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>44908</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>45191</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>45792</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>45169</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>45324</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>45134</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>45596</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>45288</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>45306</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>45810</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>46027</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>45841</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>46203</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>45849</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>46233</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>46268</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>45936</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         <v>45786</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>46048</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>46107</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>44881</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>44843</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>44531</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>44764</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>44750</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>44518</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>44523</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>44720</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>44696</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>44764</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>44607</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>44811</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>44714</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>44722</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>44510</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>44816</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>44684</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>44725</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>44874</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>44564</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>44652</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>44781</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>44564</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>44571</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>44533</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>44696</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44491</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>44680</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         <v>44615</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         <v>44784</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         <v>44733</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         <v>44725</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>44609</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>44609</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         <v>44580</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         <v>44497</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>44699</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>44840</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>44539</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>44622</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         <v>44725</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>45763</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>45763</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>45204</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>45154</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>44950</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44712</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>45244</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>45534</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44692</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>45135</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>45137</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>45106</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>45419</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>44713</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>44714</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>44637</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>45484</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>45016</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>45260</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>45414</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>45342</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>45745</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>45406</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>45093</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>44803</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>45740</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>44588</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>45233</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
         <v>45218</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>45160</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         <v>45056</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         <v>45397</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>45156</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>44882</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>44768</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>45471</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         <v>45376</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>45450</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>45233</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>45526</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>45093</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>45202</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>45386</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>44902</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         <v>45021</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>45104</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         <v>45210</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>44834</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>45202</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>44790</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>45121</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>45611</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>45611</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
         <v>45342</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>44489</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>45210</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>44813</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>44813</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>45254</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12956,7 +12956,7 @@
         <v>45415</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>45288</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>45212</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>45335</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         <v>45358</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         <v>45680</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>44798</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>45355</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
         <v>45370</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>45093</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>45264</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>45093</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>45352</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         <v>45322</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>45884</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>45490</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>45490</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>45490</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>45474</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>45533</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>45373</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>45147</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>45134</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>45604</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>44632</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>45884</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         <v>44994</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>45030</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>44579</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         <v>45059</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>45219</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>44810</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>45281</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>45135</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>45119</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>45888</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>45888</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         <v>45342</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>45477</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>45855</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15896,7 +15896,7 @@
         <v>45855</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15969,7 +15969,7 @@
         <v>45855</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>45798</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>45359</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>45359</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>44982</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>44952</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>45092</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>45077</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>45889</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         <v>45378</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>44971</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>45891</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>45896</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>45895</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>45896</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>45896</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>45897</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>45275</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>45275</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>45898</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>45332</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>45343</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>45349</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17648,7 +17648,7 @@
         <v>45490</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17721,7 +17721,7 @@
         <v>45358</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>44978</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>45631</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17940,7 +17940,7 @@
         <v>45629</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18013,7 +18013,7 @@
         <v>44936</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18086,7 +18086,7 @@
         <v>45901</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18159,7 +18159,7 @@
         <v>44971</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
         <v>45251</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>45251</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>45523</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>45301</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>45905</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>44896</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>44531</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>45909</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>45518</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>45106</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>45106</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>45629</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>45779</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19196,7 +19196,7 @@
         <v>45784</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>45443</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>45784</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>45916</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>45021</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>45443</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>44580</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>45443</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>44603</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>44924</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>44973</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         <v>44586</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>45490</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20150,7 +20150,7 @@
         <v>45490</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>45667</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>45672</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>44574</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>44607</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>45713</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20588,7 +20588,7 @@
         <v>45629</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20661,7 +20661,7 @@
         <v>45418</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>45434</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>44599</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20880,7 +20880,7 @@
         <v>45359</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>44585</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>45924</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>45356</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21177,7 +21177,7 @@
         <v>45356</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>45923</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21323,7 +21323,7 @@
         <v>45923</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>45555</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>45925</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21542,7 +21542,7 @@
         <v>45925</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21615,7 +21615,7 @@
         <v>45379</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21688,7 +21688,7 @@
         <v>44902</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         <v>45925</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>45332</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>45264</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>45264</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22053,7 +22053,7 @@
         <v>45188</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44896</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>45569</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>45370</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>45925</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22418,7 +22418,7 @@
         <v>45925</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22491,7 +22491,7 @@
         <v>45925</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22564,7 +22564,7 @@
         <v>44950</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>45631</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>45261</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>45565</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>45724</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22934,7 +22934,7 @@
         <v>45792</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23007,7 +23007,7 @@
         <v>45792</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>45721</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23153,7 +23153,7 @@
         <v>44588</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         <v>44971</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>45189</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>45587</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
         <v>45534</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23518,7 +23518,7 @@
         <v>44950</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         <v>44660</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>45931</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>44648</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>44596</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23883,7 +23883,7 @@
         <v>45419</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>44673</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>44732</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>45261</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24175,7 +24175,7 @@
         <v>45799</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24248,7 +24248,7 @@
         <v>44589</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>45799</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         <v>44982</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>45225</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24540,7 +24540,7 @@
         <v>45937</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24613,7 +24613,7 @@
         <v>45392</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>45076</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>45268</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>45763</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>45937</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>45805</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25051,7 +25051,7 @@
         <v>45194</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>45236</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
         <v>44993</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25270,7 +25270,7 @@
         <v>44897</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25343,7 +25343,7 @@
         <v>45070</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>45098</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>45098</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25562,7 +25562,7 @@
         <v>45611</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25635,7 +25635,7 @@
         <v>45807</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25708,7 +25708,7 @@
         <v>45943</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25781,7 +25781,7 @@
         <v>45943</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>45572</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25927,7 +25927,7 @@
         <v>45922</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>45231</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>45922</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>44734</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>45075</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>45274</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>44834</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>44624</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>45294</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>44685</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26657,7 +26657,7 @@
         <v>45749</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         <v>45397</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>45818</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>45751</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>45574</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>44909</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>45713</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>45819</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27241,7 +27241,7 @@
         <v>45775</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27314,7 +27314,7 @@
         <v>45154</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>45624</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         <v>45624</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>45826</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27611,7 +27611,7 @@
         <v>45568</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>45740</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>45721</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>45741</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>45183</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>45743</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>45728</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>45743</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28200,7 +28200,7 @@
         <v>45716</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>45743</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>45743</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28419,7 +28419,7 @@
         <v>44838</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28492,7 +28492,7 @@
         <v>45831</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28565,7 +28565,7 @@
         <v>45137</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>45953</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>45953</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>45959</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28857,7 +28857,7 @@
         <v>45959</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>45833</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29003,7 +29003,7 @@
         <v>45834</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         <v>45244</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>45833</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29222,7 +29222,7 @@
         <v>45672</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>45672</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>45838</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>44973</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>45964</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>45838</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>44715</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>44881</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29806,7 +29806,7 @@
         <v>45422</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>45119</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29952,7 +29952,7 @@
         <v>45839</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30030,7 +30030,7 @@
         <v>45646</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>45965</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30176,7 +30176,7 @@
         <v>45841</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>45137</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30322,7 +30322,7 @@
         <v>45474</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30400,7 +30400,7 @@
         <v>45841</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30473,7 +30473,7 @@
         <v>45841</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30546,7 +30546,7 @@
         <v>45841</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>45841</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30692,7 +30692,7 @@
         <v>45841</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30765,7 +30765,7 @@
         <v>45684</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30843,7 +30843,7 @@
         <v>45631</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30916,7 +30916,7 @@
         <v>45629</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30989,7 +30989,7 @@
         <v>44720</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31062,7 +31062,7 @@
         <v>45681</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31135,7 +31135,7 @@
         <v>45281</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31208,7 +31208,7 @@
         <v>45845</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31281,7 +31281,7 @@
         <v>45845</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31354,7 +31354,7 @@
         <v>45099</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31427,7 +31427,7 @@
         <v>45188</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>44694</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31573,7 +31573,7 @@
         <v>45789</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31646,7 +31646,7 @@
         <v>45030</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31719,7 +31719,7 @@
         <v>45847</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31792,7 +31792,7 @@
         <v>45631</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>45642</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31938,7 +31938,7 @@
         <v>45734</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32011,7 +32011,7 @@
         <v>45807</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32084,7 +32084,7 @@
         <v>45849</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32157,7 +32157,7 @@
         <v>44531</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32230,7 +32230,7 @@
         <v>45854</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32303,7 +32303,7 @@
         <v>45030</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32376,7 +32376,7 @@
         <v>45978</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         <v>45838</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32522,7 +32522,7 @@
         <v>45251</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32595,7 +32595,7 @@
         <v>45855</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32668,7 +32668,7 @@
         <v>45855</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>45855</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32814,7 +32814,7 @@
         <v>45855</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>44762</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32960,7 +32960,7 @@
         <v>45140</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33033,7 +33033,7 @@
         <v>45183</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>45299</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>45862</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33252,7 +33252,7 @@
         <v>45373</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33325,7 +33325,7 @@
         <v>44806</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33398,7 +33398,7 @@
         <v>45867</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>45978</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33544,7 +33544,7 @@
         <v>44935</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>45867</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33690,7 +33690,7 @@
         <v>45091</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33763,7 +33763,7 @@
         <v>44928</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33836,7 +33836,7 @@
         <v>45029</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33909,7 +33909,7 @@
         <v>45029</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>44901</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34055,7 +34055,7 @@
         <v>44904</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34128,7 +34128,7 @@
         <v>44869</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34201,7 +34201,7 @@
         <v>45324</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         <v>45358</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34347,7 +34347,7 @@
         <v>45750</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>44888</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>45209</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>45580</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34639,7 +34639,7 @@
         <v>45124</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>44944</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>44901</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34858,7 +34858,7 @@
         <v>45272</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>45379</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35004,7 +35004,7 @@
         <v>45127</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35077,7 +35077,7 @@
         <v>45637</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35150,7 +35150,7 @@
         <v>45076</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>45872</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35296,7 +35296,7 @@
         <v>44869</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35369,7 +35369,7 @@
         <v>45763</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35442,7 +35442,7 @@
         <v>45719</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35520,7 +35520,7 @@
         <v>44998</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35593,7 +35593,7 @@
         <v>45568</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>44804</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35739,7 +35739,7 @@
         <v>45316</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35812,7 +35812,7 @@
         <v>45980</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>45821</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35958,7 +35958,7 @@
         <v>45875</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36031,7 +36031,7 @@
         <v>45875</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36104,7 +36104,7 @@
         <v>45875</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36177,7 +36177,7 @@
         <v>45875</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36250,7 +36250,7 @@
         <v>45356</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36323,7 +36323,7 @@
         <v>45755</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36396,7 +36396,7 @@
         <v>45755</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36469,7 +36469,7 @@
         <v>45880</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36542,7 +36542,7 @@
         <v>44987</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36615,7 +36615,7 @@
         <v>45281</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36688,7 +36688,7 @@
         <v>45264</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36761,7 +36761,7 @@
         <v>45251</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>46097</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36907,7 +36907,7 @@
         <v>45982</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36980,7 +36980,7 @@
         <v>45750</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37053,7 +37053,7 @@
         <v>45684</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37126,7 +37126,7 @@
         <v>45022</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37199,7 +37199,7 @@
         <v>45107</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>45343</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37345,7 +37345,7 @@
         <v>45397</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>46100</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37491,7 +37491,7 @@
         <v>45254</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37564,7 +37564,7 @@
         <v>45751</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37637,7 +37637,7 @@
         <v>45230</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>45986</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37783,7 +37783,7 @@
         <v>45306</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37856,7 +37856,7 @@
         <v>45475</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37929,7 +37929,7 @@
         <v>45264</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38002,7 +38002,7 @@
         <v>45428</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38075,7 +38075,7 @@
         <v>45137</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>44928</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38221,7 +38221,7 @@
         <v>45552</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>44897</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38367,7 +38367,7 @@
         <v>44935</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38440,7 +38440,7 @@
         <v>45996</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38513,7 +38513,7 @@
         <v>44764</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38586,7 +38586,7 @@
         <v>45999</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>46000</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38732,7 +38732,7 @@
         <v>46000</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38805,7 +38805,7 @@
         <v>46127</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38878,7 +38878,7 @@
         <v>44610</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38951,7 +38951,7 @@
         <v>45432</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39029,7 +39029,7 @@
         <v>46000</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39102,7 +39102,7 @@
         <v>46001</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>46000</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39248,7 +39248,7 @@
         <v>44603</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39321,7 +39321,7 @@
         <v>46001</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39394,7 +39394,7 @@
         <v>45911</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39467,7 +39467,7 @@
         <v>44615</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39540,7 +39540,7 @@
         <v>46006</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>45369</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39686,7 +39686,7 @@
         <v>46006</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39759,7 +39759,7 @@
         <v>45475</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39832,7 +39832,7 @@
         <v>45455</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>46134</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39978,7 +39978,7 @@
         <v>44588</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40051,7 +40051,7 @@
         <v>44588</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40124,7 +40124,7 @@
         <v>45147</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40197,7 +40197,7 @@
         <v>46008</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>46007</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>45197</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>44937</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>46009</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40562,7 +40562,7 @@
         <v>45332</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40635,7 +40635,7 @@
         <v>45714</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>45238</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40781,7 +40781,7 @@
         <v>45839</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40859,7 +40859,7 @@
         <v>45709</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40932,7 +40932,7 @@
         <v>45595</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>46013</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41078,7 +41078,7 @@
         <v>46013</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41151,7 +41151,7 @@
         <v>45724</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41224,7 +41224,7 @@
         <v>45714</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41297,7 +41297,7 @@
         <v>45707</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41370,7 +41370,7 @@
         <v>45691</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41443,7 +41443,7 @@
         <v>45713</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41516,7 +41516,7 @@
         <v>45693</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41589,7 +41589,7 @@
         <v>45063</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>44760</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41735,7 +41735,7 @@
         <v>44631</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>46030</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41881,7 +41881,7 @@
         <v>45817</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>44994</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42027,7 +42027,7 @@
         <v>45791</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42100,7 +42100,7 @@
         <v>46034</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>46034</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>44501</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>44652</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42392,7 +42392,7 @@
         <v>46030</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42465,7 +42465,7 @@
         <v>46034</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>44715</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42611,7 +42611,7 @@
         <v>45604</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>44982</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42757,7 +42757,7 @@
         <v>45819</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>45688</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42903,7 +42903,7 @@
         <v>46037</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42976,7 +42976,7 @@
         <v>46038</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43054,7 +43054,7 @@
         <v>46037</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43127,7 +43127,7 @@
         <v>46037</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43200,7 +43200,7 @@
         <v>46037</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43273,7 +43273,7 @@
         <v>46038</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43346,7 +43346,7 @@
         <v>45868</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43419,7 +43419,7 @@
         <v>45637</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43492,7 +43492,7 @@
         <v>45811</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45825</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43638,7 +43638,7 @@
         <v>45755</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43711,7 +43711,7 @@
         <v>44630</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43789,7 +43789,7 @@
         <v>45918</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
         <v>44978</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43935,7 +43935,7 @@
         <v>45370</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44008,7 +44008,7 @@
         <v>45474</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44081,7 +44081,7 @@
         <v>46048</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44154,7 +44154,7 @@
         <v>45134</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44227,7 +44227,7 @@
         <v>45224</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44300,7 +44300,7 @@
         <v>46048</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44373,7 +44373,7 @@
         <v>46048</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>45540</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
         <v>46048</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44597,7 +44597,7 @@
         <v>45686</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44670,7 +44670,7 @@
         <v>46046</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44743,7 +44743,7 @@
         <v>45377</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44821,7 +44821,7 @@
         <v>45442</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44894,7 +44894,7 @@
         <v>46052</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44972,7 +44972,7 @@
         <v>46055</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45045,7 +45045,7 @@
         <v>46055</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45118,7 +45118,7 @@
         <v>46056</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45196,7 +45196,7 @@
         <v>46056</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>46058</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>46057</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45415,7 +45415,7 @@
         <v>46062</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45493,7 +45493,7 @@
         <v>46064</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45566,7 +45566,7 @@
         <v>46146</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45639,7 +45639,7 @@
         <v>46147</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45712,7 +45712,7 @@
         <v>46153</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45785,7 +45785,7 @@
         <v>45699</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45858,7 +45858,7 @@
         <v>46084</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>46045</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46004,7 +46004,7 @@
         <v>46084</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>46084</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46150,7 +46150,7 @@
         <v>46084</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46223,7 +46223,7 @@
         <v>46085</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46301,7 +46301,7 @@
         <v>45686</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46374,7 +46374,7 @@
         <v>45776</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46447,7 +46447,7 @@
         <v>46120</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>46092</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46593,7 +46593,7 @@
         <v>46162</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46666,7 +46666,7 @@
         <v>46165</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46744,7 +46744,7 @@
         <v>45776</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>46169</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46890,7 +46890,7 @@
         <v>46181</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46963,7 +46963,7 @@
         <v>46182</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47036,7 +47036,7 @@
         <v>46189</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47109,7 +47109,7 @@
         <v>46190</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>46191</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47255,7 +47255,7 @@
         <v>46195</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>46195</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47401,7 +47401,7 @@
         <v>46195</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>46195</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>46195</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47620,7 +47620,7 @@
         <v>46195</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>46199</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47771,7 +47771,7 @@
         <v>46198</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47844,7 +47844,7 @@
         <v>46203</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47917,7 +47917,7 @@
         <v>46204</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47990,7 +47990,7 @@
         <v>46211</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48063,7 +48063,7 @@
         <v>46216</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48136,7 +48136,7 @@
         <v>46195</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48209,7 +48209,7 @@
         <v>46195</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48282,7 +48282,7 @@
         <v>46269</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48355,7 +48355,7 @@
         <v>46273</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48428,7 +48428,7 @@
         <v>46231</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48506,7 +48506,7 @@
         <v>46274</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>46273</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48652,7 +48652,7 @@
         <v>46274</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48725,7 +48725,7 @@
         <v>46233</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48798,7 +48798,7 @@
         <v>46232</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48876,7 +48876,7 @@
         <v>46233</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48949,7 +48949,7 @@
         <v>46276</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49022,7 +49022,7 @@
         <v>46275</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49095,7 +49095,7 @@
         <v>46237</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49168,7 +49168,7 @@
         <v>46237</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49241,7 +49241,7 @@
         <v>46233</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49314,7 +49314,7 @@
         <v>46279</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49387,7 +49387,7 @@
         <v>46237</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>46237</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49533,7 +49533,7 @@
         <v>46233</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49606,7 +49606,7 @@
         <v>46282</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49679,7 +49679,7 @@
         <v>46281</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49752,7 +49752,7 @@
         <v>46283</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49825,7 +49825,7 @@
         <v>46286</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49898,7 +49898,7 @@
         <v>46283</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49971,7 +49971,7 @@
         <v>45710</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50044,7 +50044,7 @@
         <v>45898</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50117,7 +50117,7 @@
         <v>46294</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50190,7 +50190,7 @@
         <v>46294</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50263,7 +50263,7 @@
         <v>46296</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50336,7 +50336,7 @@
         <v>46295</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50409,7 +50409,7 @@
         <v>46114</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50482,7 +50482,7 @@
         <v>44869</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50555,7 +50555,7 @@
         <v>46297</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50628,7 +50628,7 @@
         <v>46259</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50701,7 +50701,7 @@
         <v>46302</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50772,7 +50772,7 @@
         <v>44088</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50845,7 +50845,7 @@
         <v>44711</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50918,7 +50918,7 @@
         <v>44966</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50996,7 +50996,7 @@
         <v>45343</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51069,7 +51069,7 @@
         <v>44966</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51147,7 +51147,7 @@
         <v>45785</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51220,7 +51220,7 @@
         <v>45839</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51298,7 +51298,7 @@
         <v>45841</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51371,7 +51371,7 @@
         <v>45705</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51444,7 +51444,7 @@
         <v>45261</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51517,7 +51517,7 @@
         <v>45022</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51590,7 +51590,7 @@
         <v>46042</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51663,7 +51663,7 @@
         <v>46107</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51736,7 +51736,7 @@
         <v>46132</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51809,7 +51809,7 @@
         <v>46258</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>

--- a/Översikt MARK.xlsx
+++ b/Översikt MARK.xlsx
@@ -601,7 +601,7 @@
         <v>45497</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45617</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45222</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>45137</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>45348</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>45285</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>45001</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>45638</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>45342</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>45973</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>45154</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>46001</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>46006</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>45137</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45618</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>46273</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>44950</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>45673</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         <v>46266</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>44792</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>44846</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>45091</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>45412</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>45191</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>45810</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>45896</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>45169</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>46001</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>45271</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>46027</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>45134</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>45306</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>45324</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>45841</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>46203</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>45288</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>45849</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>46233</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>45596</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>45751</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>45936</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>44908</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>45792</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>46268</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>45786</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>46048</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         <v>46107</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>44881</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>44843</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>44531</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>44764</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>44518</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>44750</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44720</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>44696</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>44523</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44764</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>44607</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>44811</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>44714</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>44722</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>44510</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>44816</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>44684</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         <v>44725</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>44874</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>44564</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>44564</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         <v>44696</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>44615</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>44733</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>44725</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         <v>44609</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>44609</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>44580</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>44497</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7753,7 +7753,7 @@
         <v>44840</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         <v>44533</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>44680</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>44784</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>44699</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         <v>44491</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>44652</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>44781</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>44571</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>44539</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>44622</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>44725</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>44692</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>44902</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>44982</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>44585</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>45342</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>45359</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>45475</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>45030</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>45568</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>45093</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44631</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>45093</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>45106</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>44630</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>44937</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>45681</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>44632</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         <v>45684</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>45183</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>45428</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
         <v>45745</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>44715</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10255,7 +10255,7 @@
         <v>44599</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>45376</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10401,7 +10401,7 @@
         <v>44607</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>45631</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10547,7 +10547,7 @@
         <v>45294</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10620,7 +10620,7 @@
         <v>44810</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>45406</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         <v>45611</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>44935</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10912,7 +10912,7 @@
         <v>45022</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10985,7 +10985,7 @@
         <v>45137</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>44987</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>45604</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>45189</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>45358</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>45332</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>45332</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>45135</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>44950</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>45016</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>45231</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>44734</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         <v>45422</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>44610</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         <v>45624</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>45624</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>45587</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>44982</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>45244</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>44762</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>45343</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
         <v>44760</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>45751</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>44973</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>44574</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>45030</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>45261</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>44588</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         <v>44588</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
         <v>45355</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13180,7 +13180,7 @@
         <v>45397</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13253,7 +13253,7 @@
         <v>44896</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13326,7 +13326,7 @@
         <v>44580</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13399,7 +13399,7 @@
         <v>45750</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>45471</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
         <v>45183</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>45098</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>45098</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>45631</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>45212</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         <v>45244</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>44882</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>45629</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>45104</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>45281</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>45637</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
         <v>45021</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>45373</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         <v>45059</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>44615</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>45202</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
         <v>45063</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>45817</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>44982</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14932,7 +14932,7 @@
         <v>45855</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         <v>45719</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>45397</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         <v>45884</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>44798</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>45160</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15380,7 +15380,7 @@
         <v>45888</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         <v>45490</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>45490</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>45490</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>45811</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>45888</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>45889</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>45884</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>45891</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>45134</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>45895</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>45121</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>45896</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>45091</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>45896</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>45896</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         <v>45798</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>45855</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>45855</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45898</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>45868</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>45897</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>44994</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>45918</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>44715</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>45343</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>45356</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17351,7 +17351,7 @@
         <v>45356</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17424,7 +17424,7 @@
         <v>45905</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         <v>45909</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
         <v>45322</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>45450</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>45370</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>46146</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>44624</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>45540</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>46147</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>45916</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>45477</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>45923</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18300,7 +18300,7 @@
         <v>45923</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>45595</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>45684</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>45925</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>45925</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>45925</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>45925</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         <v>45925</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>45925</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>45924</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19030,7 +19030,7 @@
         <v>44978</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>45335</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
         <v>44971</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         <v>44694</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>46153</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19395,7 +19395,7 @@
         <v>45931</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19468,7 +19468,7 @@
         <v>45137</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>45075</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>45629</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>44648</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>45937</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
         <v>45937</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>44834</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19979,7 +19979,7 @@
         <v>45922</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20052,7 +20052,7 @@
         <v>45922</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20125,7 +20125,7 @@
         <v>45943</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>44928</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20271,7 +20271,7 @@
         <v>45943</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>44838</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20417,7 +20417,7 @@
         <v>45106</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>45106</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>44713</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>45680</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20719,7 +20719,7 @@
         <v>45953</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         <v>45755</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         <v>45755</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         <v>45755</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21011,7 +21011,7 @@
         <v>45953</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
         <v>45349</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44935</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21230,7 +21230,7 @@
         <v>45484</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>45959</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>45959</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21449,7 +21449,7 @@
         <v>45224</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21522,7 +21522,7 @@
         <v>45194</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21595,7 +21595,7 @@
         <v>45965</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21668,7 +21668,7 @@
         <v>45964</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21741,7 +21741,7 @@
         <v>46120</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21814,7 +21814,7 @@
         <v>45264</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21887,7 +21887,7 @@
         <v>45264</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21960,7 +21960,7 @@
         <v>44714</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22033,7 +22033,7 @@
         <v>45776</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22106,7 +22106,7 @@
         <v>44950</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22184,7 +22184,7 @@
         <v>46162</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
         <v>45978</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>45555</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22403,7 +22403,7 @@
         <v>45419</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>45978</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>45137</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
         <v>45442</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>44712</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>45268</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>46165</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>45980</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>45414</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>45982</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>45288</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>45986</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>45392</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>45490</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23435,7 +23435,7 @@
         <v>45750</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>45342</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>45776</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>45629</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>45432</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23805,7 +23805,7 @@
         <v>45419</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23878,7 +23878,7 @@
         <v>45999</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>44768</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24024,7 +24024,7 @@
         <v>45996</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24097,7 +24097,7 @@
         <v>46169</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>45342</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24243,7 +24243,7 @@
         <v>46000</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24316,7 +24316,7 @@
         <v>45533</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24389,7 +24389,7 @@
         <v>46001</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24462,7 +24462,7 @@
         <v>46000</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24535,7 +24535,7 @@
         <v>46000</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>46000</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24681,7 +24681,7 @@
         <v>45140</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>45667</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24827,7 +24827,7 @@
         <v>46007</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24900,7 +24900,7 @@
         <v>46006</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>45356</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>46006</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
         <v>46008</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25192,7 +25192,7 @@
         <v>46013</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25265,7 +25265,7 @@
         <v>46013</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>45724</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>45707</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>45714</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>45714</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>45713</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>45839</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25781,7 +25781,7 @@
         <v>45238</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>45693</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25927,7 +25927,7 @@
         <v>45709</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>45691</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>44803</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>44489</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>44971</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>45260</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>46030</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>46030</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>46034</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>45604</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26657,7 +26657,7 @@
         <v>46034</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         <v>44834</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>46034</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>46037</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>46037</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>46037</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>46037</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>46038</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27241,7 +27241,7 @@
         <v>44806</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27314,7 +27314,7 @@
         <v>46038</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>45154</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>44896</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27538,7 +27538,7 @@
         <v>46048</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27611,7 +27611,7 @@
         <v>45552</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>46048</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>46048</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>46046</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>45076</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>45137</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>46055</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>46182</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28195,7 +28195,7 @@
         <v>45264</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>46052</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>46055</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28419,7 +28419,7 @@
         <v>46056</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>46057</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28570,7 +28570,7 @@
         <v>44952</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28643,7 +28643,7 @@
         <v>46181</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>46056</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28789,7 +28789,7 @@
         <v>45443</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28862,7 +28862,7 @@
         <v>46058</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>45526</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29008,7 +29008,7 @@
         <v>46062</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29086,7 +29086,7 @@
         <v>46064</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29159,7 +29159,7 @@
         <v>45236</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29232,7 +29232,7 @@
         <v>45154</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29305,7 +29305,7 @@
         <v>44660</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         <v>45301</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>44588</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29524,7 +29524,7 @@
         <v>44732</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29597,7 +29597,7 @@
         <v>45021</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>45275</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29743,7 +29743,7 @@
         <v>45275</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29816,7 +29816,7 @@
         <v>45699</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29889,7 +29889,7 @@
         <v>46084</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>46084</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30035,7 +30035,7 @@
         <v>46084</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30108,7 +30108,7 @@
         <v>44978</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30181,7 +30181,7 @@
         <v>46045</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30254,7 +30254,7 @@
         <v>46084</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30327,7 +30327,7 @@
         <v>46085</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30405,7 +30405,7 @@
         <v>46190</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>46189</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30551,7 +30551,7 @@
         <v>45686</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30624,7 +30624,7 @@
         <v>45386</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30697,7 +30697,7 @@
         <v>46092</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30770,7 +30770,7 @@
         <v>46191</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30843,7 +30843,7 @@
         <v>46097</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30916,7 +30916,7 @@
         <v>46195</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30989,7 +30989,7 @@
         <v>46195</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31062,7 +31062,7 @@
         <v>46195</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31135,7 +31135,7 @@
         <v>46100</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31208,7 +31208,7 @@
         <v>44902</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31281,7 +31281,7 @@
         <v>46195</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31354,7 +31354,7 @@
         <v>45379</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31427,7 +31427,7 @@
         <v>46195</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>46195</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31573,7 +31573,7 @@
         <v>45251</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31646,7 +31646,7 @@
         <v>45251</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31719,7 +31719,7 @@
         <v>45135</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31792,7 +31792,7 @@
         <v>46199</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31870,7 +31870,7 @@
         <v>45251</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31943,7 +31943,7 @@
         <v>45686</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32016,7 +32016,7 @@
         <v>45119</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32089,7 +32089,7 @@
         <v>44813</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32162,7 +32162,7 @@
         <v>45518</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>44764</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32313,7 +32313,7 @@
         <v>45911</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32386,7 +32386,7 @@
         <v>44909</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32459,7 +32459,7 @@
         <v>46127</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32532,7 +32532,7 @@
         <v>45672</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32605,7 +32605,7 @@
         <v>45672</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32678,7 +32678,7 @@
         <v>45455</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32751,7 +32751,7 @@
         <v>44637</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32824,7 +32824,7 @@
         <v>45230</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32897,7 +32897,7 @@
         <v>46203</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32970,7 +32970,7 @@
         <v>46134</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33043,7 +33043,7 @@
         <v>45210</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33116,7 +33116,7 @@
         <v>45218</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33189,7 +33189,7 @@
         <v>45204</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33262,7 +33262,7 @@
         <v>45197</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>45233</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33413,7 +33413,7 @@
         <v>45825</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33486,7 +33486,7 @@
         <v>46204</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33559,7 +33559,7 @@
         <v>45233</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33632,7 +33632,7 @@
         <v>45107</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33705,7 +33705,7 @@
         <v>45225</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>45378</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33851,7 +33851,7 @@
         <v>45523</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33924,7 +33924,7 @@
         <v>45637</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>44501</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>45819</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34143,7 +34143,7 @@
         <v>45791</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>44813</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34289,7 +34289,7 @@
         <v>44531</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>46211</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34435,7 +34435,7 @@
         <v>46216</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34508,7 +34508,7 @@
         <v>46195</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>46195</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34654,7 +34654,7 @@
         <v>45254</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>44994</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34800,7 +34800,7 @@
         <v>45373</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34873,7 +34873,7 @@
         <v>45070</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34946,7 +34946,7 @@
         <v>46273</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>45264</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35092,7 +35092,7 @@
         <v>46273</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35165,7 +35165,7 @@
         <v>44588</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>45370</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35311,7 +35311,7 @@
         <v>45352</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>44897</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>46274</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35530,7 +35530,7 @@
         <v>46231</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35608,7 +35608,7 @@
         <v>46233</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35681,7 +35681,7 @@
         <v>46275</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35754,7 +35754,7 @@
         <v>45202</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35827,7 +35827,7 @@
         <v>46274</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35900,7 +35900,7 @@
         <v>44881</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>45156</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36046,7 +36046,7 @@
         <v>46233</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36119,7 +36119,7 @@
         <v>45369</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36192,7 +36192,7 @@
         <v>44673</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36265,7 +36265,7 @@
         <v>46232</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36343,7 +36343,7 @@
         <v>46233</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36416,7 +36416,7 @@
         <v>45629</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36489,7 +36489,7 @@
         <v>45281</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36562,7 +36562,7 @@
         <v>45358</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36635,7 +36635,7 @@
         <v>46276</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36708,7 +36708,7 @@
         <v>45134</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>45099</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36854,7 +36854,7 @@
         <v>46233</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36927,7 +36927,7 @@
         <v>45474</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37005,7 +37005,7 @@
         <v>45569</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>46279</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37151,7 +37151,7 @@
         <v>45415</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37224,7 +37224,7 @@
         <v>46237</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37297,7 +37297,7 @@
         <v>46237</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37370,7 +37370,7 @@
         <v>45264</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37443,7 +37443,7 @@
         <v>45188</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37516,7 +37516,7 @@
         <v>45093</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37589,7 +37589,7 @@
         <v>46237</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37662,7 +37662,7 @@
         <v>46237</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37735,7 +37735,7 @@
         <v>44589</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37808,7 +37808,7 @@
         <v>45030</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37881,7 +37881,7 @@
         <v>45379</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37954,7 +37954,7 @@
         <v>45475</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38027,7 +38027,7 @@
         <v>44652</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38100,7 +38100,7 @@
         <v>45274</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38173,7 +38173,7 @@
         <v>46283</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38246,7 +38246,7 @@
         <v>46283</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38319,7 +38319,7 @@
         <v>45370</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38392,7 +38392,7 @@
         <v>44888</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38465,7 +38465,7 @@
         <v>46282</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38538,7 +38538,7 @@
         <v>45092</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38611,7 +38611,7 @@
         <v>46281</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38684,7 +38684,7 @@
         <v>45359</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38757,7 +38757,7 @@
         <v>45359</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38830,7 +38830,7 @@
         <v>45763</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38903,7 +38903,7 @@
         <v>45763</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38976,7 +38976,7 @@
         <v>45763</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39049,7 +39049,7 @@
         <v>45490</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39122,7 +39122,7 @@
         <v>45077</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39195,7 +39195,7 @@
         <v>45534</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39268,7 +39268,7 @@
         <v>44924</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39341,7 +39341,7 @@
         <v>45631</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39414,7 +39414,7 @@
         <v>45251</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         <v>45119</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39560,7 +39560,7 @@
         <v>45565</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39633,7 +39633,7 @@
         <v>45332</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>46286</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39779,7 +39779,7 @@
         <v>45210</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>44897</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>45219</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39998,7 +39998,7 @@
         <v>45299</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40071,7 +40071,7 @@
         <v>45490</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>45147</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40217,7 +40217,7 @@
         <v>45261</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40290,7 +40290,7 @@
         <v>45474</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40363,7 +40363,7 @@
         <v>45611</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40436,7 +40436,7 @@
         <v>45093</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>45688</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40582,7 +40582,7 @@
         <v>44936</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40655,7 +40655,7 @@
         <v>44603</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40728,7 +40728,7 @@
         <v>45147</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40801,7 +40801,7 @@
         <v>45710</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40874,7 +40874,7 @@
         <v>45740</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40947,7 +40947,7 @@
         <v>44720</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41020,7 +41020,7 @@
         <v>44579</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41098,7 +41098,7 @@
         <v>45898</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41171,7 +41171,7 @@
         <v>44973</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41244,7 +41244,7 @@
         <v>45474</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41322,7 +41322,7 @@
         <v>44603</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41395,7 +41395,7 @@
         <v>45306</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41468,7 +41468,7 @@
         <v>44596</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41541,7 +41541,7 @@
         <v>44790</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41614,7 +41614,7 @@
         <v>45646</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41687,7 +41687,7 @@
         <v>44993</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41760,7 +41760,7 @@
         <v>45572</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41833,7 +41833,7 @@
         <v>46295</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41906,7 +41906,7 @@
         <v>46294</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>46294</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42052,7 +42052,7 @@
         <v>45377</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42130,7 +42130,7 @@
         <v>45254</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42203,7 +42203,7 @@
         <v>44869</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42276,7 +42276,7 @@
         <v>45713</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42349,7 +42349,7 @@
         <v>46297</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42422,7 +42422,7 @@
         <v>46296</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42495,7 +42495,7 @@
         <v>45056</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42568,7 +42568,7 @@
         <v>45534</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42641,7 +42641,7 @@
         <v>44950</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42714,7 +42714,7 @@
         <v>45763</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42787,7 +42787,7 @@
         <v>45779</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42860,7 +42860,7 @@
         <v>46114</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42933,7 +42933,7 @@
         <v>45784</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43006,7 +43006,7 @@
         <v>44586</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43079,7 +43079,7 @@
         <v>45443</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43152,7 +43152,7 @@
         <v>45784</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>45418</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43298,7 +43298,7 @@
         <v>46302</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>45434</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>45443</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43522,7 +43522,7 @@
         <v>45713</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43595,7 +43595,7 @@
         <v>45672</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43668,7 +43668,7 @@
         <v>45724</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>45721</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43814,7 +43814,7 @@
         <v>46259</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43887,7 +43887,7 @@
         <v>45580</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43960,7 +43960,7 @@
         <v>45792</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44033,7 +44033,7 @@
         <v>45792</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>46009</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44179,7 +44179,7 @@
         <v>44971</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44252,7 +44252,7 @@
         <v>45799</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44325,7 +44325,7 @@
         <v>45799</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44398,7 +44398,7 @@
         <v>45819</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44471,7 +44471,7 @@
         <v>45805</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44544,7 +44544,7 @@
         <v>45807</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44617,7 +44617,7 @@
         <v>45611</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44690,7 +44690,7 @@
         <v>44685</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44763,7 +44763,7 @@
         <v>45574</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44836,7 +44836,7 @@
         <v>45397</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44909,7 +44909,7 @@
         <v>45751</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44982,7 +44982,7 @@
         <v>45749</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         <v>45818</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45128,7 +45128,7 @@
         <v>46269</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45201,7 +45201,7 @@
         <v>45775</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45274,7 +45274,7 @@
         <v>45721</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45347,7 +45347,7 @@
         <v>45716</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45743</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45493,7 +45493,7 @@
         <v>45743</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45566,7 +45566,7 @@
         <v>45728</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45639,7 +45639,7 @@
         <v>45743</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45712,7 +45712,7 @@
         <v>45826</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45790,7 +45790,7 @@
         <v>45740</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45743</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45936,7 +45936,7 @@
         <v>45741</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46014,7 +46014,7 @@
         <v>45831</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46087,7 +46087,7 @@
         <v>45833</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45833</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46233,7 +46233,7 @@
         <v>45834</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46306,7 +46306,7 @@
         <v>45838</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>45839</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46457,7 +46457,7 @@
         <v>45838</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46530,7 +46530,7 @@
         <v>45841</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46603,7 +46603,7 @@
         <v>45841</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46676,7 +46676,7 @@
         <v>45841</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>45841</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46822,7 +46822,7 @@
         <v>45841</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46895,7 +46895,7 @@
         <v>45841</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46968,7 +46968,7 @@
         <v>45281</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47041,7 +47041,7 @@
         <v>45188</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47114,7 +47114,7 @@
         <v>45845</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47187,7 +47187,7 @@
         <v>45789</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47260,7 +47260,7 @@
         <v>45631</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47333,7 +47333,7 @@
         <v>45847</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47406,7 +47406,7 @@
         <v>45845</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47479,7 +47479,7 @@
         <v>45642</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47552,7 +47552,7 @@
         <v>45849</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47625,7 +47625,7 @@
         <v>45807</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47698,7 +47698,7 @@
         <v>45734</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47771,7 +47771,7 @@
         <v>45855</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47844,7 +47844,7 @@
         <v>45855</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47917,7 +47917,7 @@
         <v>45854</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47990,7 +47990,7 @@
         <v>45855</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48063,7 +48063,7 @@
         <v>44531</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48136,7 +48136,7 @@
         <v>45855</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48209,7 +48209,7 @@
         <v>45838</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48282,7 +48282,7 @@
         <v>45862</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48355,7 +48355,7 @@
         <v>45867</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48428,7 +48428,7 @@
         <v>45867</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48501,7 +48501,7 @@
         <v>45568</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48574,7 +48574,7 @@
         <v>45124</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48647,7 +48647,7 @@
         <v>45127</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48720,7 +48720,7 @@
         <v>44804</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48793,7 +48793,7 @@
         <v>44901</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48866,7 +48866,7 @@
         <v>44928</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>45272</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49012,7 +49012,7 @@
         <v>45076</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49085,7 +49085,7 @@
         <v>44869</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>44901</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>44998</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49304,7 +49304,7 @@
         <v>45821</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45029</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49450,7 +49450,7 @@
         <v>45029</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49523,7 +49523,7 @@
         <v>45324</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49596,7 +49596,7 @@
         <v>44944</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49669,7 +49669,7 @@
         <v>45358</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49742,7 +49742,7 @@
         <v>44904</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49815,7 +49815,7 @@
         <v>45872</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49888,7 +49888,7 @@
         <v>44869</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45316</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50034,7 +50034,7 @@
         <v>45209</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50107,7 +50107,7 @@
         <v>45875</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50180,7 +50180,7 @@
         <v>45875</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50253,7 +50253,7 @@
         <v>45875</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50326,7 +50326,7 @@
         <v>45875</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50399,7 +50399,7 @@
         <v>45880</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50470,7 +50470,7 @@
         <v>44088</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50543,7 +50543,7 @@
         <v>44711</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50616,7 +50616,7 @@
         <v>44966</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50694,7 +50694,7 @@
         <v>45343</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50767,7 +50767,7 @@
         <v>44966</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50845,7 +50845,7 @@
         <v>45785</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50918,7 +50918,7 @@
         <v>45839</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50996,7 +50996,7 @@
         <v>45841</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51069,7 +51069,7 @@
         <v>45705</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51142,7 +51142,7 @@
         <v>45261</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>45022</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51288,7 +51288,7 @@
         <v>46042</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51361,7 +51361,7 @@
         <v>46107</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51434,7 +51434,7 @@
         <v>46132</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51507,7 +51507,7 @@
         <v>46258</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>

--- a/Översikt MARK.xlsx
+++ b/Översikt MARK.xlsx
@@ -601,7 +601,7 @@
         <v>45497</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45617</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45222</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>45137</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>45348</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>45285</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>45001</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>45638</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>45342</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>45973</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>45154</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>46001</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>46006</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>45137</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45618</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>46273</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>44950</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>45673</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         <v>46266</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>44792</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>44846</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>45091</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>45412</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>45191</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>45810</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>45896</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>45169</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>46001</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>45271</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>46027</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>45134</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>45306</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>45324</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>45841</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>46203</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>45288</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>45849</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>46233</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>45596</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>45751</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>45936</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>44908</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>45792</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>46268</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>45786</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>46048</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         <v>46107</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>44881</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>44843</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>44531</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>44764</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>44518</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>44750</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44720</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>44696</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>44523</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44764</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>44607</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>44811</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>44714</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>44722</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>44510</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>44816</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>44684</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         <v>44725</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>44874</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>44564</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>44564</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         <v>44696</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>44615</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>44733</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>44725</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         <v>44609</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>44609</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>44580</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>44497</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7753,7 +7753,7 @@
         <v>44840</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         <v>44533</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>44680</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>44784</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>44699</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         <v>44491</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>44652</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>44781</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>44571</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>44539</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>44622</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>44725</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>44692</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>44902</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>44982</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>44585</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>45342</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>45359</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>45475</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>45030</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>45568</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>45093</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44631</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>45093</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>45106</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>44630</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>44937</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>45681</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>44632</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         <v>45684</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>45183</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>45428</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
         <v>45745</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>44715</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10255,7 +10255,7 @@
         <v>44599</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>45376</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10401,7 +10401,7 @@
         <v>44607</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>45631</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10547,7 +10547,7 @@
         <v>45294</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10620,7 +10620,7 @@
         <v>44810</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>45406</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         <v>45611</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>44935</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10912,7 +10912,7 @@
         <v>45022</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10985,7 +10985,7 @@
         <v>45137</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>44987</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>45604</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>45189</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>45358</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>45332</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>45332</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>45135</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>44950</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>45016</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>45231</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>44734</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         <v>45422</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>44610</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         <v>45624</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>45624</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>45587</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>44982</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>45244</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>44762</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>45343</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
         <v>44760</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>45751</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>44973</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>44574</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>45030</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>45261</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>44588</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         <v>44588</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
         <v>45355</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13180,7 +13180,7 @@
         <v>45397</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13253,7 +13253,7 @@
         <v>44896</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13326,7 +13326,7 @@
         <v>44580</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13399,7 +13399,7 @@
         <v>45750</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>45471</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
         <v>45183</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>45098</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>45098</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>45631</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>45212</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         <v>45244</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>44882</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>45629</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>45104</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>45281</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>45637</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
         <v>45021</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>45373</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         <v>45059</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>44615</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>45202</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
         <v>45063</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>45817</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>44982</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14932,7 +14932,7 @@
         <v>45855</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         <v>45719</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>45397</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         <v>45884</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>44798</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>45160</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15380,7 +15380,7 @@
         <v>45888</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         <v>45490</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>45490</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>45490</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>45811</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>45888</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>45889</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>45884</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>45891</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>45134</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>45895</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>45121</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>45896</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>45091</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>45896</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>45896</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         <v>45798</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>45855</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>45855</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45898</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>45868</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>45897</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>44994</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>45918</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>44715</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>45343</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>45356</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17351,7 +17351,7 @@
         <v>45356</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17424,7 +17424,7 @@
         <v>45905</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         <v>45909</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
         <v>45322</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>45450</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>45370</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>46146</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>44624</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>45540</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>46147</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>45916</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>45477</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>45923</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18300,7 +18300,7 @@
         <v>45923</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>45595</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>45684</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>45925</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>45925</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>45925</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>45925</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         <v>45925</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>45925</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>45924</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19030,7 +19030,7 @@
         <v>44978</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>45335</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
         <v>44971</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         <v>44694</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>46153</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19395,7 +19395,7 @@
         <v>45931</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19468,7 +19468,7 @@
         <v>45137</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>45075</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>45629</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>44648</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>45937</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
         <v>45937</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>44834</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19979,7 +19979,7 @@
         <v>45922</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20052,7 +20052,7 @@
         <v>45922</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20125,7 +20125,7 @@
         <v>45943</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>44928</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20271,7 +20271,7 @@
         <v>45943</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>44838</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20417,7 +20417,7 @@
         <v>45106</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>45106</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>44713</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>45680</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20719,7 +20719,7 @@
         <v>45953</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         <v>45755</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         <v>45755</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         <v>45755</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21011,7 +21011,7 @@
         <v>45953</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
         <v>45349</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44935</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21230,7 +21230,7 @@
         <v>45484</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>45959</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>45959</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21449,7 +21449,7 @@
         <v>45224</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21522,7 +21522,7 @@
         <v>45194</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21595,7 +21595,7 @@
         <v>45965</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21668,7 +21668,7 @@
         <v>45964</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21741,7 +21741,7 @@
         <v>46120</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21814,7 +21814,7 @@
         <v>45264</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21887,7 +21887,7 @@
         <v>45264</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21960,7 +21960,7 @@
         <v>44714</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22033,7 +22033,7 @@
         <v>45776</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22106,7 +22106,7 @@
         <v>44950</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22184,7 +22184,7 @@
         <v>46162</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
         <v>45978</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>45555</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22403,7 +22403,7 @@
         <v>45419</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>45978</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>45137</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
         <v>45442</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>44712</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>45268</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>46165</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>45980</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>45414</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>45982</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>45288</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>45986</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>45392</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>45490</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23435,7 +23435,7 @@
         <v>45750</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>45342</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>45776</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>45629</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>45432</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23805,7 +23805,7 @@
         <v>45419</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23878,7 +23878,7 @@
         <v>45999</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>44768</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24024,7 +24024,7 @@
         <v>45996</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24097,7 +24097,7 @@
         <v>46169</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>45342</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24243,7 +24243,7 @@
         <v>46000</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24316,7 +24316,7 @@
         <v>45533</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24389,7 +24389,7 @@
         <v>46001</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24462,7 +24462,7 @@
         <v>46000</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24535,7 +24535,7 @@
         <v>46000</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>46000</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24681,7 +24681,7 @@
         <v>45140</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>45667</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24827,7 +24827,7 @@
         <v>46007</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24900,7 +24900,7 @@
         <v>46006</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>45356</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>46006</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
         <v>46008</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25192,7 +25192,7 @@
         <v>46013</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25265,7 +25265,7 @@
         <v>46013</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>45724</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>45707</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>45714</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>45714</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>45713</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>45839</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25781,7 +25781,7 @@
         <v>45238</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>45693</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25927,7 +25927,7 @@
         <v>45709</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>45691</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>44803</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>44489</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>44971</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>45260</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>46030</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>46030</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>46034</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>45604</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26657,7 +26657,7 @@
         <v>46034</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         <v>44834</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>46034</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>46037</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>46037</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>46037</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>46037</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>46038</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27241,7 +27241,7 @@
         <v>44806</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27314,7 +27314,7 @@
         <v>46038</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>45154</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>44896</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27538,7 +27538,7 @@
         <v>46048</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27611,7 +27611,7 @@
         <v>45552</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>46048</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>46048</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>46046</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>45076</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>45137</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>46055</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>46182</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28195,7 +28195,7 @@
         <v>45264</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>46052</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>46055</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28419,7 +28419,7 @@
         <v>46056</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>46057</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28570,7 +28570,7 @@
         <v>44952</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28643,7 +28643,7 @@
         <v>46181</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>46056</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28789,7 +28789,7 @@
         <v>45443</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28862,7 +28862,7 @@
         <v>46058</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>45526</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29008,7 +29008,7 @@
         <v>46062</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29086,7 +29086,7 @@
         <v>46064</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29159,7 +29159,7 @@
         <v>45236</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29232,7 +29232,7 @@
         <v>45154</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29305,7 +29305,7 @@
         <v>44660</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         <v>45301</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>44588</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29524,7 +29524,7 @@
         <v>44732</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29597,7 +29597,7 @@
         <v>45021</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>45275</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29743,7 +29743,7 @@
         <v>45275</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29816,7 +29816,7 @@
         <v>45699</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29889,7 +29889,7 @@
         <v>46084</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>46084</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30035,7 +30035,7 @@
         <v>46084</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30108,7 +30108,7 @@
         <v>44978</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30181,7 +30181,7 @@
         <v>46045</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30254,7 +30254,7 @@
         <v>46084</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30327,7 +30327,7 @@
         <v>46085</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30405,7 +30405,7 @@
         <v>46190</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>46189</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30551,7 +30551,7 @@
         <v>45686</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30624,7 +30624,7 @@
         <v>45386</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30697,7 +30697,7 @@
         <v>46092</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30770,7 +30770,7 @@
         <v>46191</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30843,7 +30843,7 @@
         <v>46097</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30916,7 +30916,7 @@
         <v>46195</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30989,7 +30989,7 @@
         <v>46195</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31062,7 +31062,7 @@
         <v>46195</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31135,7 +31135,7 @@
         <v>46100</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31208,7 +31208,7 @@
         <v>44902</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31281,7 +31281,7 @@
         <v>46195</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31354,7 +31354,7 @@
         <v>45379</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31427,7 +31427,7 @@
         <v>46195</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>46195</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31573,7 +31573,7 @@
         <v>45251</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31646,7 +31646,7 @@
         <v>45251</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31719,7 +31719,7 @@
         <v>45135</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31792,7 +31792,7 @@
         <v>46199</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31870,7 +31870,7 @@
         <v>45251</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31943,7 +31943,7 @@
         <v>45686</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32016,7 +32016,7 @@
         <v>45119</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32089,7 +32089,7 @@
         <v>44813</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32162,7 +32162,7 @@
         <v>45518</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>44764</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32313,7 +32313,7 @@
         <v>45911</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32386,7 +32386,7 @@
         <v>44909</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32459,7 +32459,7 @@
         <v>46127</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32532,7 +32532,7 @@
         <v>45672</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32605,7 +32605,7 @@
         <v>45672</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32678,7 +32678,7 @@
         <v>45455</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32751,7 +32751,7 @@
         <v>44637</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32824,7 +32824,7 @@
         <v>45230</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32897,7 +32897,7 @@
         <v>46203</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32970,7 +32970,7 @@
         <v>46134</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33043,7 +33043,7 @@
         <v>45210</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33116,7 +33116,7 @@
         <v>45218</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33189,7 +33189,7 @@
         <v>45204</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33262,7 +33262,7 @@
         <v>45197</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>45233</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33413,7 +33413,7 @@
         <v>45825</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33486,7 +33486,7 @@
         <v>46204</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33559,7 +33559,7 @@
         <v>45233</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33632,7 +33632,7 @@
         <v>45107</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33705,7 +33705,7 @@
         <v>45225</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>45378</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33851,7 +33851,7 @@
         <v>45523</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33924,7 +33924,7 @@
         <v>45637</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>44501</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>45819</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34143,7 +34143,7 @@
         <v>45791</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>44813</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34289,7 +34289,7 @@
         <v>44531</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>46211</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34435,7 +34435,7 @@
         <v>46216</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34508,7 +34508,7 @@
         <v>46195</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>46195</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34654,7 +34654,7 @@
         <v>45254</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>44994</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34800,7 +34800,7 @@
         <v>45373</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34873,7 +34873,7 @@
         <v>45070</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34946,7 +34946,7 @@
         <v>46273</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>45264</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35092,7 +35092,7 @@
         <v>46273</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35165,7 +35165,7 @@
         <v>44588</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>45370</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35311,7 +35311,7 @@
         <v>45352</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>44897</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>46274</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35530,7 +35530,7 @@
         <v>46231</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35608,7 +35608,7 @@
         <v>46233</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35681,7 +35681,7 @@
         <v>46275</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35754,7 +35754,7 @@
         <v>45202</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35827,7 +35827,7 @@
         <v>46274</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35900,7 +35900,7 @@
         <v>44881</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>45156</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36046,7 +36046,7 @@
         <v>46233</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36119,7 +36119,7 @@
         <v>45369</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36192,7 +36192,7 @@
         <v>44673</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36265,7 +36265,7 @@
         <v>46232</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36343,7 +36343,7 @@
         <v>46233</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36416,7 +36416,7 @@
         <v>45629</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36489,7 +36489,7 @@
         <v>45281</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36562,7 +36562,7 @@
         <v>45358</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36635,7 +36635,7 @@
         <v>46276</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36708,7 +36708,7 @@
         <v>45134</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>45099</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36854,7 +36854,7 @@
         <v>46233</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36927,7 +36927,7 @@
         <v>45474</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37005,7 +37005,7 @@
         <v>45569</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>46279</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37151,7 +37151,7 @@
         <v>45415</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37224,7 +37224,7 @@
         <v>46237</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37297,7 +37297,7 @@
         <v>46237</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37370,7 +37370,7 @@
         <v>45264</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37443,7 +37443,7 @@
         <v>45188</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37516,7 +37516,7 @@
         <v>45093</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37589,7 +37589,7 @@
         <v>46237</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37662,7 +37662,7 @@
         <v>46237</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37735,7 +37735,7 @@
         <v>44589</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37808,7 +37808,7 @@
         <v>45030</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37881,7 +37881,7 @@
         <v>45379</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37954,7 +37954,7 @@
         <v>45475</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38027,7 +38027,7 @@
         <v>44652</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38100,7 +38100,7 @@
         <v>45274</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38173,7 +38173,7 @@
         <v>46283</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38246,7 +38246,7 @@
         <v>46283</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38319,7 +38319,7 @@
         <v>45370</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38392,7 +38392,7 @@
         <v>44888</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38465,7 +38465,7 @@
         <v>46282</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38538,7 +38538,7 @@
         <v>45092</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38611,7 +38611,7 @@
         <v>46281</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38684,7 +38684,7 @@
         <v>45359</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38757,7 +38757,7 @@
         <v>45359</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38830,7 +38830,7 @@
         <v>45763</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38903,7 +38903,7 @@
         <v>45763</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38976,7 +38976,7 @@
         <v>45763</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39049,7 +39049,7 @@
         <v>45490</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39122,7 +39122,7 @@
         <v>45077</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39195,7 +39195,7 @@
         <v>45534</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39268,7 +39268,7 @@
         <v>44924</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39341,7 +39341,7 @@
         <v>45631</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39414,7 +39414,7 @@
         <v>45251</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         <v>45119</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39560,7 +39560,7 @@
         <v>45565</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39633,7 +39633,7 @@
         <v>45332</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>46286</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39779,7 +39779,7 @@
         <v>45210</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>44897</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>45219</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39998,7 +39998,7 @@
         <v>45299</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40071,7 +40071,7 @@
         <v>45490</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>45147</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40217,7 +40217,7 @@
         <v>45261</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40290,7 +40290,7 @@
         <v>45474</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40363,7 +40363,7 @@
         <v>45611</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40436,7 +40436,7 @@
         <v>45093</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>45688</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40582,7 +40582,7 @@
         <v>44936</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40655,7 +40655,7 @@
         <v>44603</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40728,7 +40728,7 @@
         <v>45147</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40801,7 +40801,7 @@
         <v>45710</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40874,7 +40874,7 @@
         <v>45740</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40947,7 +40947,7 @@
         <v>44720</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41020,7 +41020,7 @@
         <v>44579</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41098,7 +41098,7 @@
         <v>45898</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41171,7 +41171,7 @@
         <v>44973</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41244,7 +41244,7 @@
         <v>45474</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41322,7 +41322,7 @@
         <v>44603</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41395,7 +41395,7 @@
         <v>45306</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41468,7 +41468,7 @@
         <v>44596</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41541,7 +41541,7 @@
         <v>44790</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41614,7 +41614,7 @@
         <v>45646</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41687,7 +41687,7 @@
         <v>44993</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41760,7 +41760,7 @@
         <v>45572</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41833,7 +41833,7 @@
         <v>46295</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41906,7 +41906,7 @@
         <v>46294</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>46294</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42052,7 +42052,7 @@
         <v>45377</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42130,7 +42130,7 @@
         <v>45254</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42203,7 +42203,7 @@
         <v>44869</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42276,7 +42276,7 @@
         <v>45713</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42349,7 +42349,7 @@
         <v>46297</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42422,7 +42422,7 @@
         <v>46296</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42495,7 +42495,7 @@
         <v>45056</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42568,7 +42568,7 @@
         <v>45534</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42641,7 +42641,7 @@
         <v>44950</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42714,7 +42714,7 @@
         <v>45763</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42787,7 +42787,7 @@
         <v>45779</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42860,7 +42860,7 @@
         <v>46114</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42933,7 +42933,7 @@
         <v>45784</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43006,7 +43006,7 @@
         <v>44586</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43079,7 +43079,7 @@
         <v>45443</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43152,7 +43152,7 @@
         <v>45784</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>45418</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43298,7 +43298,7 @@
         <v>46302</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>45434</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>45443</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43522,7 +43522,7 @@
         <v>45713</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43595,7 +43595,7 @@
         <v>45672</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43668,7 +43668,7 @@
         <v>45724</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>45721</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43814,7 +43814,7 @@
         <v>46259</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43887,7 +43887,7 @@
         <v>45580</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43960,7 +43960,7 @@
         <v>45792</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44033,7 +44033,7 @@
         <v>45792</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>46009</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44179,7 +44179,7 @@
         <v>44971</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44252,7 +44252,7 @@
         <v>45799</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44325,7 +44325,7 @@
         <v>45799</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44398,7 +44398,7 @@
         <v>45819</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44471,7 +44471,7 @@
         <v>45805</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44544,7 +44544,7 @@
         <v>45807</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44617,7 +44617,7 @@
         <v>45611</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44690,7 +44690,7 @@
         <v>44685</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44763,7 +44763,7 @@
         <v>45574</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44836,7 +44836,7 @@
         <v>45397</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44909,7 +44909,7 @@
         <v>45751</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44982,7 +44982,7 @@
         <v>45749</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         <v>45818</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45128,7 +45128,7 @@
         <v>46269</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45201,7 +45201,7 @@
         <v>45775</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45274,7 +45274,7 @@
         <v>45721</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45347,7 +45347,7 @@
         <v>45716</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45743</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45493,7 +45493,7 @@
         <v>45743</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45566,7 +45566,7 @@
         <v>45728</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45639,7 +45639,7 @@
         <v>45743</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45712,7 +45712,7 @@
         <v>45826</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45790,7 +45790,7 @@
         <v>45740</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45743</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45936,7 +45936,7 @@
         <v>45741</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46014,7 +46014,7 @@
         <v>45831</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46087,7 +46087,7 @@
         <v>45833</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45833</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46233,7 +46233,7 @@
         <v>45834</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46306,7 +46306,7 @@
         <v>45838</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>45839</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46457,7 +46457,7 @@
         <v>45838</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46530,7 +46530,7 @@
         <v>45841</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46603,7 +46603,7 @@
         <v>45841</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46676,7 +46676,7 @@
         <v>45841</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>45841</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46822,7 +46822,7 @@
         <v>45841</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46895,7 +46895,7 @@
         <v>45841</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46968,7 +46968,7 @@
         <v>45281</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47041,7 +47041,7 @@
         <v>45188</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47114,7 +47114,7 @@
         <v>45845</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47187,7 +47187,7 @@
         <v>45789</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47260,7 +47260,7 @@
         <v>45631</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47333,7 +47333,7 @@
         <v>45847</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47406,7 +47406,7 @@
         <v>45845</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47479,7 +47479,7 @@
         <v>45642</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47552,7 +47552,7 @@
         <v>45849</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47625,7 +47625,7 @@
         <v>45807</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47698,7 +47698,7 @@
         <v>45734</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47771,7 +47771,7 @@
         <v>45855</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47844,7 +47844,7 @@
         <v>45855</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47917,7 +47917,7 @@
         <v>45854</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47990,7 +47990,7 @@
         <v>45855</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48063,7 +48063,7 @@
         <v>44531</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48136,7 +48136,7 @@
         <v>45855</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48209,7 +48209,7 @@
         <v>45838</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48282,7 +48282,7 @@
         <v>45862</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48355,7 +48355,7 @@
         <v>45867</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48428,7 +48428,7 @@
         <v>45867</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48501,7 +48501,7 @@
         <v>45568</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48574,7 +48574,7 @@
         <v>45124</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48647,7 +48647,7 @@
         <v>45127</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48720,7 +48720,7 @@
         <v>44804</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48793,7 +48793,7 @@
         <v>44901</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48866,7 +48866,7 @@
         <v>44928</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>45272</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49012,7 +49012,7 @@
         <v>45076</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49085,7 +49085,7 @@
         <v>44869</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>44901</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>44998</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49304,7 +49304,7 @@
         <v>45821</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45029</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49450,7 +49450,7 @@
         <v>45029</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49523,7 +49523,7 @@
         <v>45324</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49596,7 +49596,7 @@
         <v>44944</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49669,7 +49669,7 @@
         <v>45358</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49742,7 +49742,7 @@
         <v>44904</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49815,7 +49815,7 @@
         <v>45872</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49888,7 +49888,7 @@
         <v>44869</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45316</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50034,7 +50034,7 @@
         <v>45209</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50107,7 +50107,7 @@
         <v>45875</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50180,7 +50180,7 @@
         <v>45875</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50253,7 +50253,7 @@
         <v>45875</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50326,7 +50326,7 @@
         <v>45875</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50399,7 +50399,7 @@
         <v>45880</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50470,7 +50470,7 @@
         <v>44088</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50543,7 +50543,7 @@
         <v>44711</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50616,7 +50616,7 @@
         <v>44966</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50694,7 +50694,7 @@
         <v>45343</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50767,7 +50767,7 @@
         <v>44966</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50845,7 +50845,7 @@
         <v>45785</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50918,7 +50918,7 @@
         <v>45839</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50996,7 +50996,7 @@
         <v>45841</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51069,7 +51069,7 @@
         <v>45705</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51142,7 +51142,7 @@
         <v>45261</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>45022</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51288,7 +51288,7 @@
         <v>46042</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51361,7 +51361,7 @@
         <v>46107</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51434,7 +51434,7 @@
         <v>46132</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51507,7 +51507,7 @@
         <v>46258</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>

--- a/Översikt MARK.xlsx
+++ b/Översikt MARK.xlsx
@@ -601,7 +601,7 @@
         <v>45497</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45617</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45222</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>45137</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>45348</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>45285</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>45342</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>45973</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>45154</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>46001</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>46006</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>45673</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>44950</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>46273</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>45618</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>45638</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45137</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>45001</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         <v>46266</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>44792</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>44846</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>45896</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>45091</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>45412</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>46203</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>44908</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>46001</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45849</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>46233</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>46027</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>45792</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>45271</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>45936</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>45306</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>45810</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>46268</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>45841</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>45324</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>45596</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>45751</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>45191</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>45169</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>45134</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>45288</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>45786</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>46048</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         <v>46107</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>44881</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>44843</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>44531</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>44750</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>44764</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>44518</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44523</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>44720</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>44696</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44764</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>44607</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>44811</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>44714</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>44722</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>44510</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>44816</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>44684</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         <v>44725</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>44874</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>44564</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>44564</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         <v>44696</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>44615</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>44733</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>44609</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         <v>44609</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>44580</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>44497</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>44725</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7753,7 +7753,7 @@
         <v>44840</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         <v>44533</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>44680</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>44784</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>44699</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         <v>44652</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>44781</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>44571</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>44622</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>44539</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>44725</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>45475</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>45059</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>44588</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>44588</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>45884</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>45888</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>45888</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>44692</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>45147</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>45373</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>45406</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         <v>45855</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>45855</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>45855</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>45798</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>45160</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>45889</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>45891</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>45896</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>44768</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>45895</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>45896</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>44937</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>45896</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>45897</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>44834</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>45134</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>45332</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>45254</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>45898</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         <v>45415</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>45212</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>45595</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>45335</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         <v>45884</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
         <v>44760</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>44631</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>45905</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>45776</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>46120</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>45909</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>44994</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
         <v>45916</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
         <v>44652</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>46162</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>44715</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>44982</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>46165</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>45688</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12143,7 +12143,7 @@
         <v>45776</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>45924</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>45923</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>45923</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>45925</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         <v>45925</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>45925</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>46169</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>45755</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>45925</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>45925</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>45925</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>45135</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13092,7 +13092,7 @@
         <v>44630</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>45137</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>45106</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>45419</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>44978</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>45370</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>45474</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>45931</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>45134</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>45224</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
         <v>45540</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>45686</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>45414</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         <v>45937</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14124,7 +14124,7 @@
         <v>45937</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>45377</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>45442</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
         <v>45204</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>45154</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         <v>44950</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>45745</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>44712</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
         <v>45943</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>45943</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>45922</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14932,7 +14932,7 @@
         <v>45244</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         <v>45922</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>45534</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15151,7 +15151,7 @@
         <v>45397</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15224,7 +15224,7 @@
         <v>44882</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15297,7 +15297,7 @@
         <v>45484</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>45471</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>45016</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15516,7 +15516,7 @@
         <v>45376</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>45450</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>45233</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15740,7 +15740,7 @@
         <v>45093</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15813,7 +15813,7 @@
         <v>45386</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>44902</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>45342</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>45210</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
         <v>45202</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>44790</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>46181</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16324,7 +16324,7 @@
         <v>44803</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16397,7 +16397,7 @@
         <v>45953</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>45953</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16543,7 +16543,7 @@
         <v>46182</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16616,7 +16616,7 @@
         <v>45526</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16689,7 +16689,7 @@
         <v>45202</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16762,7 +16762,7 @@
         <v>45959</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16835,7 +16835,7 @@
         <v>45959</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16908,7 +16908,7 @@
         <v>45021</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>45964</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17054,7 +17054,7 @@
         <v>45611</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         <v>45611</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17200,7 +17200,7 @@
         <v>46189</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17273,7 +17273,7 @@
         <v>45342</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
         <v>46190</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>45210</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17492,7 +17492,7 @@
         <v>45965</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>44813</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17638,7 +17638,7 @@
         <v>44813</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>46191</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>45680</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>45355</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>46195</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>46195</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>46195</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>46195</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         <v>45264</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>46195</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>46195</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         <v>45474</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>45978</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>45604</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>44632</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>46199</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>44994</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18889,7 +18889,7 @@
         <v>45978</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>45030</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>44579</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>45219</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>44810</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>46203</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>45980</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>45477</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>45322</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>45982</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19629,7 +19629,7 @@
         <v>45359</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45359</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>44982</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>46204</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>45490</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>45490</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20067,7 +20067,7 @@
         <v>45490</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>45092</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>45986</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
         <v>45077</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>45378</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20432,7 +20432,7 @@
         <v>45332</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20505,7 +20505,7 @@
         <v>45343</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>45349</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>45490</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>45358</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>45631</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>45629</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>45533</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>46211</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>45147</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>45996</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>46216</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>45999</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>45301</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>46195</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>46195</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>46000</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>46000</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>46000</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>46000</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>46001</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>46006</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         <v>46006</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>45779</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22184,7 +22184,7 @@
         <v>45784</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
         <v>46231</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>45443</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22408,7 +22408,7 @@
         <v>46008</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         <v>45784</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22554,7 +22554,7 @@
         <v>46233</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22627,7 +22627,7 @@
         <v>46232</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>45443</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22783,7 +22783,7 @@
         <v>46233</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22856,7 +22856,7 @@
         <v>46007</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22929,7 +22929,7 @@
         <v>46237</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>46233</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23075,7 +23075,7 @@
         <v>46279</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23148,7 +23148,7 @@
         <v>45714</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23221,7 +23221,7 @@
         <v>44586</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23294,7 +23294,7 @@
         <v>45238</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23367,7 +23367,7 @@
         <v>45839</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
         <v>45709</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23518,7 +23518,7 @@
         <v>46013</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         <v>46013</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>46237</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>46237</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>45672</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23883,7 +23883,7 @@
         <v>46233</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>45724</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>45714</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>45713</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24175,7 +24175,7 @@
         <v>45707</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24248,7 +24248,7 @@
         <v>45691</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>45713</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         <v>45418</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>45693</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24540,7 +24540,7 @@
         <v>45434</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24613,7 +24613,7 @@
         <v>46030</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>46034</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>46034</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>46282</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>46281</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>46030</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25051,7 +25051,7 @@
         <v>46283</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>46286</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
         <v>46034</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25270,7 +25270,7 @@
         <v>45724</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25343,7 +25343,7 @@
         <v>45792</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>45792</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>45721</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25562,7 +25562,7 @@
         <v>45604</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25635,7 +25635,7 @@
         <v>44971</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25708,7 +25708,7 @@
         <v>46037</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25781,7 +25781,7 @@
         <v>46038</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25859,7 +25859,7 @@
         <v>46037</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25932,7 +25932,7 @@
         <v>46037</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26005,7 +26005,7 @@
         <v>46037</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>46283</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
         <v>46038</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>46048</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>46048</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>46048</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>45799</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>46046</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>45799</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>46052</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>45135</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>45119</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26886,7 +26886,7 @@
         <v>45710</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>45805</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27032,7 +27032,7 @@
         <v>46055</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>46055</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>46056</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>46056</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27329,7 +27329,7 @@
         <v>45898</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
         <v>46058</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>45342</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>46057</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>45611</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27694,7 +27694,7 @@
         <v>45807</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27767,7 +27767,7 @@
         <v>46294</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>46062</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>46064</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27991,7 +27991,7 @@
         <v>46294</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28064,7 +28064,7 @@
         <v>44685</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>45749</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         <v>45397</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28283,7 +28283,7 @@
         <v>45818</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28356,7 +28356,7 @@
         <v>45751</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>45574</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>46296</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28575,7 +28575,7 @@
         <v>45775</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28648,7 +28648,7 @@
         <v>46295</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28721,7 +28721,7 @@
         <v>45826</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28799,7 +28799,7 @@
         <v>45740</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>45721</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>45741</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29023,7 +29023,7 @@
         <v>45743</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>45728</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29169,7 +29169,7 @@
         <v>45743</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29242,7 +29242,7 @@
         <v>45699</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29315,7 +29315,7 @@
         <v>45716</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29388,7 +29388,7 @@
         <v>45743</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29461,7 +29461,7 @@
         <v>45743</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29534,7 +29534,7 @@
         <v>45831</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29607,7 +29607,7 @@
         <v>46084</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29680,7 +29680,7 @@
         <v>46045</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29753,7 +29753,7 @@
         <v>46084</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29826,7 +29826,7 @@
         <v>46084</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29899,7 +29899,7 @@
         <v>46084</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29972,7 +29972,7 @@
         <v>46085</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30050,7 +30050,7 @@
         <v>45833</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30123,7 +30123,7 @@
         <v>46114</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30196,7 +30196,7 @@
         <v>45834</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>45833</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30342,7 +30342,7 @@
         <v>45838</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>45838</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30488,7 +30488,7 @@
         <v>45686</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>46092</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>45839</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30712,7 +30712,7 @@
         <v>44952</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30785,7 +30785,7 @@
         <v>46097</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>45841</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30931,7 +30931,7 @@
         <v>45841</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31004,7 +31004,7 @@
         <v>45841</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31077,7 +31077,7 @@
         <v>45841</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31150,7 +31150,7 @@
         <v>45841</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31223,7 +31223,7 @@
         <v>45841</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31296,7 +31296,7 @@
         <v>44869</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31369,7 +31369,7 @@
         <v>46297</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31442,7 +31442,7 @@
         <v>44971</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31515,7 +31515,7 @@
         <v>46100</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31588,7 +31588,7 @@
         <v>45281</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31661,7 +31661,7 @@
         <v>45845</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31734,7 +31734,7 @@
         <v>45845</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31807,7 +31807,7 @@
         <v>45188</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31880,7 +31880,7 @@
         <v>45789</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31953,7 +31953,7 @@
         <v>45275</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32026,7 +32026,7 @@
         <v>45275</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32099,7 +32099,7 @@
         <v>45847</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32172,7 +32172,7 @@
         <v>45631</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32245,7 +32245,7 @@
         <v>45642</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32318,7 +32318,7 @@
         <v>45734</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32391,7 +32391,7 @@
         <v>45807</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32464,7 +32464,7 @@
         <v>45849</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32537,7 +32537,7 @@
         <v>46259</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32610,7 +32610,7 @@
         <v>44531</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32683,7 +32683,7 @@
         <v>45854</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32756,7 +32756,7 @@
         <v>44978</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32829,7 +32829,7 @@
         <v>45838</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32902,7 +32902,7 @@
         <v>45855</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32975,7 +32975,7 @@
         <v>45855</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33048,7 +33048,7 @@
         <v>45855</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33121,7 +33121,7 @@
         <v>46302</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33194,7 +33194,7 @@
         <v>45855</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33267,7 +33267,7 @@
         <v>44936</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33340,7 +33340,7 @@
         <v>45862</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33413,7 +33413,7 @@
         <v>45867</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33486,7 +33486,7 @@
         <v>45867</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33559,7 +33559,7 @@
         <v>44928</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33632,7 +33632,7 @@
         <v>45029</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33705,7 +33705,7 @@
         <v>45029</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>44901</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33851,7 +33851,7 @@
         <v>44904</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33924,7 +33924,7 @@
         <v>44869</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>45324</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>45358</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34143,7 +34143,7 @@
         <v>45209</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>45124</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34289,7 +34289,7 @@
         <v>44944</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>44901</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34435,7 +34435,7 @@
         <v>45272</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34508,7 +34508,7 @@
         <v>45127</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>45076</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34654,7 +34654,7 @@
         <v>45872</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>44869</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34800,7 +34800,7 @@
         <v>44998</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34873,7 +34873,7 @@
         <v>45568</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34946,7 +34946,7 @@
         <v>44804</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>44764</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35092,7 +35092,7 @@
         <v>45316</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35165,7 +35165,7 @@
         <v>45821</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>46127</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35311,7 +35311,7 @@
         <v>45875</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>45875</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>45875</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35530,7 +35530,7 @@
         <v>45875</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35603,7 +35603,7 @@
         <v>45580</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35676,7 +35676,7 @@
         <v>45880</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35749,7 +35749,7 @@
         <v>45911</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35822,7 +35822,7 @@
         <v>45819</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35895,7 +35895,7 @@
         <v>45523</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35968,7 +35968,7 @@
         <v>44896</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36041,7 +36041,7 @@
         <v>44798</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36119,7 +36119,7 @@
         <v>44531</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36192,7 +36192,7 @@
         <v>45455</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36265,7 +36265,7 @@
         <v>46134</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36338,7 +36338,7 @@
         <v>45518</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36416,7 +36416,7 @@
         <v>46009</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36489,7 +36489,7 @@
         <v>45021</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36562,7 +36562,7 @@
         <v>45197</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36635,7 +36635,7 @@
         <v>44603</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36708,7 +36708,7 @@
         <v>44924</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>45490</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36854,7 +36854,7 @@
         <v>45490</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36927,7 +36927,7 @@
         <v>45667</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37000,7 +37000,7 @@
         <v>44574</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37073,7 +37073,7 @@
         <v>45063</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37146,7 +37146,7 @@
         <v>45817</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>45359</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37292,7 +37292,7 @@
         <v>45791</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37365,7 +37365,7 @@
         <v>44501</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37438,7 +37438,7 @@
         <v>46269</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37511,7 +37511,7 @@
         <v>45379</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37584,7 +37584,7 @@
         <v>44902</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>45264</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37730,7 +37730,7 @@
         <v>45264</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37803,7 +37803,7 @@
         <v>45819</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37876,7 +37876,7 @@
         <v>44896</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37949,7 +37949,7 @@
         <v>45569</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38022,7 +38022,7 @@
         <v>45370</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38095,7 +38095,7 @@
         <v>44950</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38173,7 +38173,7 @@
         <v>45261</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38246,7 +38246,7 @@
         <v>45868</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38319,7 +38319,7 @@
         <v>45637</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38392,7 +38392,7 @@
         <v>45565</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38465,7 +38465,7 @@
         <v>45811</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38538,7 +38538,7 @@
         <v>45825</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38611,7 +38611,7 @@
         <v>46315</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38684,7 +38684,7 @@
         <v>45918</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38757,7 +38757,7 @@
         <v>46315</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38830,7 +38830,7 @@
         <v>46273</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38903,7 +38903,7 @@
         <v>46273</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38976,7 +38976,7 @@
         <v>46274</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39049,7 +39049,7 @@
         <v>45587</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39122,7 +39122,7 @@
         <v>45534</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39195,7 +39195,7 @@
         <v>44950</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39268,7 +39268,7 @@
         <v>44660</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39341,7 +39341,7 @@
         <v>46276</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39414,7 +39414,7 @@
         <v>46317</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         <v>44596</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39560,7 +39560,7 @@
         <v>46275</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39633,7 +39633,7 @@
         <v>45419</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>46274</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39779,7 +39779,7 @@
         <v>44673</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>44732</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>45261</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39998,7 +39998,7 @@
         <v>44589</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40071,7 +40071,7 @@
         <v>44982</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>46146</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40217,7 +40217,7 @@
         <v>45392</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40290,7 +40290,7 @@
         <v>45268</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40363,7 +40363,7 @@
         <v>46147</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40436,7 +40436,7 @@
         <v>46153</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>44993</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40582,7 +40582,7 @@
         <v>44897</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40655,7 +40655,7 @@
         <v>45075</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40728,7 +40728,7 @@
         <v>45274</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40801,7 +40801,7 @@
         <v>44834</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40874,7 +40874,7 @@
         <v>45294</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40947,7 +40947,7 @@
         <v>44909</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41020,7 +41020,7 @@
         <v>45624</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41093,7 +41093,7 @@
         <v>45624</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41166,7 +41166,7 @@
         <v>45672</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41239,7 +41239,7 @@
         <v>45672</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41312,7 +41312,7 @@
         <v>44973</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41385,7 +41385,7 @@
         <v>44881</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41458,7 +41458,7 @@
         <v>45119</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41531,7 +41531,7 @@
         <v>45646</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41604,7 +41604,7 @@
         <v>45137</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>45684</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41755,7 +41755,7 @@
         <v>45631</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41828,7 +41828,7 @@
         <v>45629</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41901,7 +41901,7 @@
         <v>44720</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41974,7 +41974,7 @@
         <v>45681</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42047,7 +42047,7 @@
         <v>45099</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42120,7 +42120,7 @@
         <v>44694</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42193,7 +42193,7 @@
         <v>45030</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42266,7 +42266,7 @@
         <v>45030</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42339,7 +42339,7 @@
         <v>44762</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42412,7 +42412,7 @@
         <v>45140</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42485,7 +42485,7 @@
         <v>45183</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42558,7 +42558,7 @@
         <v>44806</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>45091</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42704,7 +42704,7 @@
         <v>45637</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42777,7 +42777,7 @@
         <v>45719</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45750</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>45022</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43001,7 +43001,7 @@
         <v>45107</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43074,7 +43074,7 @@
         <v>45751</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43147,7 +43147,7 @@
         <v>45306</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>45475</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45264</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43366,7 +43366,7 @@
         <v>44928</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43439,7 +43439,7 @@
         <v>45763</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43512,7 +43512,7 @@
         <v>45763</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43585,7 +43585,7 @@
         <v>44713</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>44714</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>44637</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43804,7 +43804,7 @@
         <v>45260</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43877,7 +43877,7 @@
         <v>45093</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43950,7 +43950,7 @@
         <v>45740</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44023,7 +44023,7 @@
         <v>44588</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44096,7 +44096,7 @@
         <v>45233</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44169,7 +44169,7 @@
         <v>45218</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45056</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44315,7 +44315,7 @@
         <v>45156</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>45104</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>45121</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44534,7 +44534,7 @@
         <v>45288</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44607,7 +44607,7 @@
         <v>45358</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44680,7 +44680,7 @@
         <v>45370</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         <v>45093</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44826,7 +44826,7 @@
         <v>45093</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44899,7 +44899,7 @@
         <v>45352</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44972,7 +44972,7 @@
         <v>45281</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45045,7 +45045,7 @@
         <v>44971</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45118,7 +45118,7 @@
         <v>45251</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45191,7 +45191,7 @@
         <v>45251</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45264,7 +45264,7 @@
         <v>45106</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>45106</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45629</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45493,7 +45493,7 @@
         <v>44580</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45566,7 +45566,7 @@
         <v>45443</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45639,7 +45639,7 @@
         <v>44973</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45712,7 +45712,7 @@
         <v>44607</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45785,7 +45785,7 @@
         <v>45629</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45858,7 +45858,7 @@
         <v>44599</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>44585</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46009,7 +46009,7 @@
         <v>45356</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46082,7 +46082,7 @@
         <v>45356</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46155,7 +46155,7 @@
         <v>45555</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46228,7 +46228,7 @@
         <v>45332</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46301,7 +46301,7 @@
         <v>45188</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46374,7 +46374,7 @@
         <v>45631</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46447,7 +46447,7 @@
         <v>44588</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45189</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46593,7 +46593,7 @@
         <v>44648</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46666,7 +46666,7 @@
         <v>45225</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46739,7 +46739,7 @@
         <v>45076</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46812,7 +46812,7 @@
         <v>45763</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46885,7 +46885,7 @@
         <v>45194</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46958,7 +46958,7 @@
         <v>45236</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47031,7 +47031,7 @@
         <v>45070</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47104,7 +47104,7 @@
         <v>45098</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>45098</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47250,7 +47250,7 @@
         <v>45572</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45231</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>44734</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47469,7 +47469,7 @@
         <v>44624</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47542,7 +47542,7 @@
         <v>45713</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>45154</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47688,7 +47688,7 @@
         <v>45568</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47761,7 +47761,7 @@
         <v>45183</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>44838</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47907,7 +47907,7 @@
         <v>45137</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47980,7 +47980,7 @@
         <v>45244</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48053,7 +48053,7 @@
         <v>44715</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48126,7 +48126,7 @@
         <v>45422</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48199,7 +48199,7 @@
         <v>45474</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48277,7 +48277,7 @@
         <v>45251</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48350,7 +48350,7 @@
         <v>45299</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48423,7 +48423,7 @@
         <v>45373</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>44935</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48569,7 +48569,7 @@
         <v>45750</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>44888</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48715,7 +48715,7 @@
         <v>45379</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48788,7 +48788,7 @@
         <v>45763</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48861,7 +48861,7 @@
         <v>45356</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48934,7 +48934,7 @@
         <v>45755</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49007,7 +49007,7 @@
         <v>45755</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49080,7 +49080,7 @@
         <v>44987</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49153,7 +49153,7 @@
         <v>45281</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49226,7 +49226,7 @@
         <v>45264</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49299,7 +49299,7 @@
         <v>45251</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49372,7 +49372,7 @@
         <v>45684</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49445,7 +49445,7 @@
         <v>45343</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49518,7 +49518,7 @@
         <v>45397</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49591,7 +49591,7 @@
         <v>45254</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49664,7 +49664,7 @@
         <v>45230</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49737,7 +49737,7 @@
         <v>45428</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49810,7 +49810,7 @@
         <v>45137</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49883,7 +49883,7 @@
         <v>45552</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49956,7 +49956,7 @@
         <v>44897</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50029,7 +50029,7 @@
         <v>44935</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50102,7 +50102,7 @@
         <v>44610</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50175,7 +50175,7 @@
         <v>45432</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50253,7 +50253,7 @@
         <v>44603</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50326,7 +50326,7 @@
         <v>44615</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50399,7 +50399,7 @@
         <v>45369</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50470,7 +50470,7 @@
         <v>44088</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50543,7 +50543,7 @@
         <v>44711</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50616,7 +50616,7 @@
         <v>44966</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50694,7 +50694,7 @@
         <v>45343</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50767,7 +50767,7 @@
         <v>44966</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50845,7 +50845,7 @@
         <v>45785</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50918,7 +50918,7 @@
         <v>45839</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50996,7 +50996,7 @@
         <v>45841</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51069,7 +51069,7 @@
         <v>45705</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51142,7 +51142,7 @@
         <v>45261</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>45022</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51288,7 +51288,7 @@
         <v>46042</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51361,7 +51361,7 @@
         <v>46107</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51434,7 +51434,7 @@
         <v>46132</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51507,7 +51507,7 @@
         <v>46258</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>

--- a/Översikt MARK.xlsx
+++ b/Översikt MARK.xlsx
@@ -601,7 +601,7 @@
         <v>45497</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45617</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45222</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>45137</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>45348</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>45285</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>45342</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>45973</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>45154</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>46001</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>46006</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>45673</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>44950</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>46273</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>45618</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>45638</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45137</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>45001</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         <v>46266</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>44792</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>44846</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>45896</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>45091</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>45412</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>46203</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>44908</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>46001</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45849</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>46233</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>46027</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>45792</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>45271</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>45936</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>45306</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>45810</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>46268</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>45841</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>45324</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>45596</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>45751</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>45191</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>45169</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>45134</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>45288</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>45786</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>46048</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         <v>46107</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>44881</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>44843</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>44531</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>44750</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>44764</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>44518</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44523</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>44720</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>44696</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44764</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>44607</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>44811</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>44714</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>44722</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>44510</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>44816</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>44684</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         <v>44725</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>44874</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>44564</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>44564</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         <v>44696</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>44615</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>44733</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>44609</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         <v>44609</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>44580</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>44497</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>44725</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7753,7 +7753,7 @@
         <v>44840</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         <v>44533</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>44680</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>44784</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>44699</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         <v>44652</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>44781</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>44571</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>44622</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>44539</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>44725</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>45475</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>45059</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>44588</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>44588</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>45884</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>45888</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>45888</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>44692</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>45147</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>45373</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>45406</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         <v>45855</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>45855</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>45855</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>45798</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>45160</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>45889</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>45891</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>45896</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>44768</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>45895</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>45896</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>44937</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>45896</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>45897</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>44834</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>45134</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>45332</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>45254</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>45898</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         <v>45415</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>45212</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>45595</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>45335</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         <v>45884</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
         <v>44760</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>44631</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>45905</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>45776</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>46120</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>45909</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>44994</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
         <v>45916</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
         <v>44652</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>46162</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>44715</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>44982</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>46165</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>45688</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12143,7 +12143,7 @@
         <v>45776</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>45924</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>45923</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>45923</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>45925</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         <v>45925</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>45925</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>46169</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>45755</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>45925</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>45925</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>45925</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>45135</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13092,7 +13092,7 @@
         <v>44630</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>45137</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>45106</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>45419</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>44978</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>45370</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>45474</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>45931</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>45134</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>45224</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
         <v>45540</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>45686</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>45414</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         <v>45937</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14124,7 +14124,7 @@
         <v>45937</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>45377</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>45442</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
         <v>45204</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>45154</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         <v>44950</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>45745</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>44712</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
         <v>45943</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>45943</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>45922</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14932,7 +14932,7 @@
         <v>45244</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         <v>45922</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>45534</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15151,7 +15151,7 @@
         <v>45397</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15224,7 +15224,7 @@
         <v>44882</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15297,7 +15297,7 @@
         <v>45484</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>45471</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>45016</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15516,7 +15516,7 @@
         <v>45376</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>45450</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>45233</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15740,7 +15740,7 @@
         <v>45093</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15813,7 +15813,7 @@
         <v>45386</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>44902</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>45342</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>45210</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
         <v>45202</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>44790</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>46181</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16324,7 +16324,7 @@
         <v>44803</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16397,7 +16397,7 @@
         <v>45953</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>45953</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16543,7 +16543,7 @@
         <v>46182</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16616,7 +16616,7 @@
         <v>45526</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16689,7 +16689,7 @@
         <v>45202</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16762,7 +16762,7 @@
         <v>45959</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16835,7 +16835,7 @@
         <v>45959</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16908,7 +16908,7 @@
         <v>45021</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>45964</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17054,7 +17054,7 @@
         <v>45611</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         <v>45611</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17200,7 +17200,7 @@
         <v>46189</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17273,7 +17273,7 @@
         <v>45342</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
         <v>46190</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>45210</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17492,7 +17492,7 @@
         <v>45965</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>44813</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17638,7 +17638,7 @@
         <v>44813</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>46191</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>45680</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>45355</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>46195</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>46195</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>46195</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>46195</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         <v>45264</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>46195</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>46195</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         <v>45474</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>45978</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>45604</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>44632</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>46199</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>44994</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18889,7 +18889,7 @@
         <v>45978</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>45030</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>44579</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>45219</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>44810</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>46203</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>45980</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>45477</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>45322</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>45982</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19629,7 +19629,7 @@
         <v>45359</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45359</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>44982</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>46204</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>45490</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>45490</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20067,7 +20067,7 @@
         <v>45490</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>45092</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>45986</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
         <v>45077</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>45378</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20432,7 +20432,7 @@
         <v>45332</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20505,7 +20505,7 @@
         <v>45343</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>45349</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>45490</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>45358</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>45631</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>45629</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>45533</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>46211</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>45147</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>45996</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>46216</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>45999</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>45301</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>46195</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>46195</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>46000</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>46000</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>46000</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>46000</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>46001</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>46006</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         <v>46006</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>45779</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22184,7 +22184,7 @@
         <v>45784</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
         <v>46231</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>45443</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22408,7 +22408,7 @@
         <v>46008</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         <v>45784</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22554,7 +22554,7 @@
         <v>46233</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22627,7 +22627,7 @@
         <v>46232</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>45443</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22783,7 +22783,7 @@
         <v>46233</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22856,7 +22856,7 @@
         <v>46007</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22929,7 +22929,7 @@
         <v>46237</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>46233</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23075,7 +23075,7 @@
         <v>46279</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23148,7 +23148,7 @@
         <v>45714</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23221,7 +23221,7 @@
         <v>44586</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23294,7 +23294,7 @@
         <v>45238</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23367,7 +23367,7 @@
         <v>45839</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
         <v>45709</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23518,7 +23518,7 @@
         <v>46013</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         <v>46013</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>46237</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>46237</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>45672</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23883,7 +23883,7 @@
         <v>46233</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>45724</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>45714</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>45713</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24175,7 +24175,7 @@
         <v>45707</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24248,7 +24248,7 @@
         <v>45691</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>45713</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         <v>45418</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>45693</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24540,7 +24540,7 @@
         <v>45434</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24613,7 +24613,7 @@
         <v>46030</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>46034</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>46034</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>46282</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>46281</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>46030</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25051,7 +25051,7 @@
         <v>46283</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>46286</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
         <v>46034</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25270,7 +25270,7 @@
         <v>45724</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25343,7 +25343,7 @@
         <v>45792</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>45792</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>45721</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25562,7 +25562,7 @@
         <v>45604</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25635,7 +25635,7 @@
         <v>44971</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25708,7 +25708,7 @@
         <v>46037</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25781,7 +25781,7 @@
         <v>46038</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25859,7 +25859,7 @@
         <v>46037</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25932,7 +25932,7 @@
         <v>46037</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26005,7 +26005,7 @@
         <v>46037</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>46283</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
         <v>46038</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>46048</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>46048</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>46048</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>45799</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>46046</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>45799</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>46052</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>45135</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>45119</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26886,7 +26886,7 @@
         <v>45710</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>45805</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27032,7 +27032,7 @@
         <v>46055</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>46055</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>46056</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>46056</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27329,7 +27329,7 @@
         <v>45898</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
         <v>46058</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>45342</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>46057</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>45611</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27694,7 +27694,7 @@
         <v>45807</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27767,7 +27767,7 @@
         <v>46294</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>46062</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>46064</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27991,7 +27991,7 @@
         <v>46294</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28064,7 +28064,7 @@
         <v>44685</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>45749</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         <v>45397</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28283,7 +28283,7 @@
         <v>45818</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28356,7 +28356,7 @@
         <v>45751</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>45574</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>46296</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28575,7 +28575,7 @@
         <v>45775</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28648,7 +28648,7 @@
         <v>46295</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28721,7 +28721,7 @@
         <v>45826</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28799,7 +28799,7 @@
         <v>45740</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>45721</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>45741</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29023,7 +29023,7 @@
         <v>45743</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>45728</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29169,7 +29169,7 @@
         <v>45743</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29242,7 +29242,7 @@
         <v>45699</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29315,7 +29315,7 @@
         <v>45716</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29388,7 +29388,7 @@
         <v>45743</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29461,7 +29461,7 @@
         <v>45743</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29534,7 +29534,7 @@
         <v>45831</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29607,7 +29607,7 @@
         <v>46084</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29680,7 +29680,7 @@
         <v>46045</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29753,7 +29753,7 @@
         <v>46084</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29826,7 +29826,7 @@
         <v>46084</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29899,7 +29899,7 @@
         <v>46084</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29972,7 +29972,7 @@
         <v>46085</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30050,7 +30050,7 @@
         <v>45833</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30123,7 +30123,7 @@
         <v>46114</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30196,7 +30196,7 @@
         <v>45834</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>45833</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30342,7 +30342,7 @@
         <v>45838</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>45838</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30488,7 +30488,7 @@
         <v>45686</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>46092</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>45839</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30712,7 +30712,7 @@
         <v>44952</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30785,7 +30785,7 @@
         <v>46097</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>45841</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30931,7 +30931,7 @@
         <v>45841</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31004,7 +31004,7 @@
         <v>45841</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31077,7 +31077,7 @@
         <v>45841</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31150,7 +31150,7 @@
         <v>45841</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31223,7 +31223,7 @@
         <v>45841</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31296,7 +31296,7 @@
         <v>44869</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31369,7 +31369,7 @@
         <v>46297</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31442,7 +31442,7 @@
         <v>44971</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31515,7 +31515,7 @@
         <v>46100</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31588,7 +31588,7 @@
         <v>45281</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31661,7 +31661,7 @@
         <v>45845</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31734,7 +31734,7 @@
         <v>45845</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31807,7 +31807,7 @@
         <v>45188</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31880,7 +31880,7 @@
         <v>45789</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31953,7 +31953,7 @@
         <v>45275</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32026,7 +32026,7 @@
         <v>45275</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32099,7 +32099,7 @@
         <v>45847</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32172,7 +32172,7 @@
         <v>45631</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32245,7 +32245,7 @@
         <v>45642</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32318,7 +32318,7 @@
         <v>45734</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32391,7 +32391,7 @@
         <v>45807</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32464,7 +32464,7 @@
         <v>45849</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32537,7 +32537,7 @@
         <v>46259</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32610,7 +32610,7 @@
         <v>44531</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32683,7 +32683,7 @@
         <v>45854</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32756,7 +32756,7 @@
         <v>44978</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32829,7 +32829,7 @@
         <v>45838</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32902,7 +32902,7 @@
         <v>45855</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32975,7 +32975,7 @@
         <v>45855</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33048,7 +33048,7 @@
         <v>45855</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33121,7 +33121,7 @@
         <v>46302</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33194,7 +33194,7 @@
         <v>45855</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33267,7 +33267,7 @@
         <v>44936</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33340,7 +33340,7 @@
         <v>45862</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33413,7 +33413,7 @@
         <v>45867</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33486,7 +33486,7 @@
         <v>45867</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33559,7 +33559,7 @@
         <v>44928</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33632,7 +33632,7 @@
         <v>45029</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33705,7 +33705,7 @@
         <v>45029</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>44901</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33851,7 +33851,7 @@
         <v>44904</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33924,7 +33924,7 @@
         <v>44869</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>45324</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>45358</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34143,7 +34143,7 @@
         <v>45209</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>45124</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34289,7 +34289,7 @@
         <v>44944</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>44901</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34435,7 +34435,7 @@
         <v>45272</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34508,7 +34508,7 @@
         <v>45127</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>45076</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34654,7 +34654,7 @@
         <v>45872</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>44869</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34800,7 +34800,7 @@
         <v>44998</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34873,7 +34873,7 @@
         <v>45568</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34946,7 +34946,7 @@
         <v>44804</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>44764</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35092,7 +35092,7 @@
         <v>45316</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35165,7 +35165,7 @@
         <v>45821</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>46127</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35311,7 +35311,7 @@
         <v>45875</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>45875</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>45875</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35530,7 +35530,7 @@
         <v>45875</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35603,7 +35603,7 @@
         <v>45580</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35676,7 +35676,7 @@
         <v>45880</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35749,7 +35749,7 @@
         <v>45911</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35822,7 +35822,7 @@
         <v>45819</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35895,7 +35895,7 @@
         <v>45523</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35968,7 +35968,7 @@
         <v>44896</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36041,7 +36041,7 @@
         <v>44798</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36119,7 +36119,7 @@
         <v>44531</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36192,7 +36192,7 @@
         <v>45455</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36265,7 +36265,7 @@
         <v>46134</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36338,7 +36338,7 @@
         <v>45518</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36416,7 +36416,7 @@
         <v>46009</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36489,7 +36489,7 @@
         <v>45021</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36562,7 +36562,7 @@
         <v>45197</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36635,7 +36635,7 @@
         <v>44603</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36708,7 +36708,7 @@
         <v>44924</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>45490</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36854,7 +36854,7 @@
         <v>45490</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36927,7 +36927,7 @@
         <v>45667</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37000,7 +37000,7 @@
         <v>44574</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37073,7 +37073,7 @@
         <v>45063</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37146,7 +37146,7 @@
         <v>45817</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>45359</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37292,7 +37292,7 @@
         <v>45791</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37365,7 +37365,7 @@
         <v>44501</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37438,7 +37438,7 @@
         <v>46269</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37511,7 +37511,7 @@
         <v>45379</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37584,7 +37584,7 @@
         <v>44902</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>45264</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37730,7 +37730,7 @@
         <v>45264</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37803,7 +37803,7 @@
         <v>45819</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37876,7 +37876,7 @@
         <v>44896</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37949,7 +37949,7 @@
         <v>45569</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38022,7 +38022,7 @@
         <v>45370</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38095,7 +38095,7 @@
         <v>44950</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38173,7 +38173,7 @@
         <v>45261</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38246,7 +38246,7 @@
         <v>45868</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38319,7 +38319,7 @@
         <v>45637</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38392,7 +38392,7 @@
         <v>45565</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38465,7 +38465,7 @@
         <v>45811</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38538,7 +38538,7 @@
         <v>45825</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38611,7 +38611,7 @@
         <v>46315</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38684,7 +38684,7 @@
         <v>45918</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38757,7 +38757,7 @@
         <v>46315</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38830,7 +38830,7 @@
         <v>46273</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38903,7 +38903,7 @@
         <v>46273</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38976,7 +38976,7 @@
         <v>46274</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39049,7 +39049,7 @@
         <v>45587</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39122,7 +39122,7 @@
         <v>45534</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39195,7 +39195,7 @@
         <v>44950</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39268,7 +39268,7 @@
         <v>44660</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39341,7 +39341,7 @@
         <v>46276</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39414,7 +39414,7 @@
         <v>46317</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         <v>44596</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39560,7 +39560,7 @@
         <v>46275</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39633,7 +39633,7 @@
         <v>45419</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>46274</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39779,7 +39779,7 @@
         <v>44673</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>44732</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>45261</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39998,7 +39998,7 @@
         <v>44589</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40071,7 +40071,7 @@
         <v>44982</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>46146</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40217,7 +40217,7 @@
         <v>45392</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40290,7 +40290,7 @@
         <v>45268</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40363,7 +40363,7 @@
         <v>46147</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40436,7 +40436,7 @@
         <v>46153</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>44993</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40582,7 +40582,7 @@
         <v>44897</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40655,7 +40655,7 @@
         <v>45075</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40728,7 +40728,7 @@
         <v>45274</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40801,7 +40801,7 @@
         <v>44834</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40874,7 +40874,7 @@
         <v>45294</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40947,7 +40947,7 @@
         <v>44909</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41020,7 +41020,7 @@
         <v>45624</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41093,7 +41093,7 @@
         <v>45624</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41166,7 +41166,7 @@
         <v>45672</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41239,7 +41239,7 @@
         <v>45672</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41312,7 +41312,7 @@
         <v>44973</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41385,7 +41385,7 @@
         <v>44881</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41458,7 +41458,7 @@
         <v>45119</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41531,7 +41531,7 @@
         <v>45646</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41604,7 +41604,7 @@
         <v>45137</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>45684</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41755,7 +41755,7 @@
         <v>45631</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41828,7 +41828,7 @@
         <v>45629</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41901,7 +41901,7 @@
         <v>44720</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41974,7 +41974,7 @@
         <v>45681</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42047,7 +42047,7 @@
         <v>45099</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42120,7 +42120,7 @@
         <v>44694</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42193,7 +42193,7 @@
         <v>45030</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42266,7 +42266,7 @@
         <v>45030</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42339,7 +42339,7 @@
         <v>44762</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42412,7 +42412,7 @@
         <v>45140</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42485,7 +42485,7 @@
         <v>45183</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42558,7 +42558,7 @@
         <v>44806</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>45091</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42704,7 +42704,7 @@
         <v>45637</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42777,7 +42777,7 @@
         <v>45719</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45750</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>45022</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43001,7 +43001,7 @@
         <v>45107</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43074,7 +43074,7 @@
         <v>45751</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43147,7 +43147,7 @@
         <v>45306</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>45475</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45264</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43366,7 +43366,7 @@
         <v>44928</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43439,7 +43439,7 @@
         <v>45763</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43512,7 +43512,7 @@
         <v>45763</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43585,7 +43585,7 @@
         <v>44713</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>44714</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>44637</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43804,7 +43804,7 @@
         <v>45260</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43877,7 +43877,7 @@
         <v>45093</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43950,7 +43950,7 @@
         <v>45740</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44023,7 +44023,7 @@
         <v>44588</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44096,7 +44096,7 @@
         <v>45233</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44169,7 +44169,7 @@
         <v>45218</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45056</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44315,7 +44315,7 @@
         <v>45156</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>45104</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>45121</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44534,7 +44534,7 @@
         <v>45288</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44607,7 +44607,7 @@
         <v>45358</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44680,7 +44680,7 @@
         <v>45370</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         <v>45093</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44826,7 +44826,7 @@
         <v>45093</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44899,7 +44899,7 @@
         <v>45352</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44972,7 +44972,7 @@
         <v>45281</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45045,7 +45045,7 @@
         <v>44971</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45118,7 +45118,7 @@
         <v>45251</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45191,7 +45191,7 @@
         <v>45251</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45264,7 +45264,7 @@
         <v>45106</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>45106</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45629</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45493,7 +45493,7 @@
         <v>44580</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45566,7 +45566,7 @@
         <v>45443</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45639,7 +45639,7 @@
         <v>44973</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45712,7 +45712,7 @@
         <v>44607</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45785,7 +45785,7 @@
         <v>45629</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45858,7 +45858,7 @@
         <v>44599</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>44585</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46009,7 +46009,7 @@
         <v>45356</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46082,7 +46082,7 @@
         <v>45356</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46155,7 +46155,7 @@
         <v>45555</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46228,7 +46228,7 @@
         <v>45332</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46301,7 +46301,7 @@
         <v>45188</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46374,7 +46374,7 @@
         <v>45631</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46447,7 +46447,7 @@
         <v>44588</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45189</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46593,7 +46593,7 @@
         <v>44648</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46666,7 +46666,7 @@
         <v>45225</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46739,7 +46739,7 @@
         <v>45076</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46812,7 +46812,7 @@
         <v>45763</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46885,7 +46885,7 @@
         <v>45194</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46958,7 +46958,7 @@
         <v>45236</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47031,7 +47031,7 @@
         <v>45070</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47104,7 +47104,7 @@
         <v>45098</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>45098</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47250,7 +47250,7 @@
         <v>45572</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45231</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>44734</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47469,7 +47469,7 @@
         <v>44624</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47542,7 +47542,7 @@
         <v>45713</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>45154</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47688,7 +47688,7 @@
         <v>45568</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47761,7 +47761,7 @@
         <v>45183</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>44838</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47907,7 +47907,7 @@
         <v>45137</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47980,7 +47980,7 @@
         <v>45244</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48053,7 +48053,7 @@
         <v>44715</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48126,7 +48126,7 @@
         <v>45422</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48199,7 +48199,7 @@
         <v>45474</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48277,7 +48277,7 @@
         <v>45251</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48350,7 +48350,7 @@
         <v>45299</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48423,7 +48423,7 @@
         <v>45373</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>44935</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48569,7 +48569,7 @@
         <v>45750</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>44888</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48715,7 +48715,7 @@
         <v>45379</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48788,7 +48788,7 @@
         <v>45763</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48861,7 +48861,7 @@
         <v>45356</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48934,7 +48934,7 @@
         <v>45755</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49007,7 +49007,7 @@
         <v>45755</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49080,7 +49080,7 @@
         <v>44987</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49153,7 +49153,7 @@
         <v>45281</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49226,7 +49226,7 @@
         <v>45264</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49299,7 +49299,7 @@
         <v>45251</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49372,7 +49372,7 @@
         <v>45684</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49445,7 +49445,7 @@
         <v>45343</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49518,7 +49518,7 @@
         <v>45397</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49591,7 +49591,7 @@
         <v>45254</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49664,7 +49664,7 @@
         <v>45230</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49737,7 +49737,7 @@
         <v>45428</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49810,7 +49810,7 @@
         <v>45137</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49883,7 +49883,7 @@
         <v>45552</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49956,7 +49956,7 @@
         <v>44897</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50029,7 +50029,7 @@
         <v>44935</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50102,7 +50102,7 @@
         <v>44610</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50175,7 +50175,7 @@
         <v>45432</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50253,7 +50253,7 @@
         <v>44603</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50326,7 +50326,7 @@
         <v>44615</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50399,7 +50399,7 @@
         <v>45369</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50470,7 +50470,7 @@
         <v>44088</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50543,7 +50543,7 @@
         <v>44711</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50616,7 +50616,7 @@
         <v>44966</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50694,7 +50694,7 @@
         <v>45343</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50767,7 +50767,7 @@
         <v>44966</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50845,7 +50845,7 @@
         <v>45785</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50918,7 +50918,7 @@
         <v>45839</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50996,7 +50996,7 @@
         <v>45841</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51069,7 +51069,7 @@
         <v>45705</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51142,7 +51142,7 @@
         <v>45261</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>45022</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51288,7 +51288,7 @@
         <v>46042</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51361,7 +51361,7 @@
         <v>46107</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51434,7 +51434,7 @@
         <v>46132</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51507,7 +51507,7 @@
         <v>46258</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
